--- a/tame_output/ON/bt/strategyON_20240709.xlsx
+++ b/tame_output/ON/bt/strategyON_20240709.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>12.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.5%</t>
+          <t>-72.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.0%</t>
+          <t>110.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.0%</t>
+          <t>125.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-50.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.3%</t>
+          <t>-69.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.2%</t>
+          <t>453.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-503.6%</t>
+          <t>-500.1%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,37 +1140,37 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.4%</t>
+          <t>-36.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-19.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-156.6%</t>
+          <t>-155.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.6%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-29.3%</t>
+          <t>-27.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>81.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-73.4%</t>
+          <t>-119.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-166.3%</t>
+          <t>-162.3%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>74.8%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-24.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-18.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-54.9%</t>
+          <t>-52.5%</t>
         </is>
       </c>
     </row>
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.341180881541048</v>
+        <v>-5.201231710485734</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8406165694030152</v>
+        <v>0.8965962378251406</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.5166151562034768</v>
+        <v>-0.3766659851481636</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.667476252611096</v>
+        <v>2.751445755244283</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.229754122215128</v>
+        <v>-5.089804951159814</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8663815319171788</v>
+        <v>0.9223612003393042</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.5166151562034768</v>
+        <v>-0.3766659851481636</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.648670511394891</v>
+        <v>2.732640014028079</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.989323625410267</v>
+        <v>-4.849374454354954</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9642968072640004</v>
+        <v>1.020276475686126</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.2761846593986165</v>
+        <v>-0.1362354883433033</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.794671886102685</v>
+        <v>2.878641388735873</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.917081057239073</v>
+        <v>-4.777131886183759</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9971231483672984</v>
+        <v>1.053102816789424</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.2761846593986165</v>
+        <v>-0.1362354883433033</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.798601199937505</v>
+        <v>2.882570702570693</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.864082734957685</v>
+        <v>-4.724133563902371</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.019001061197194</v>
+        <v>1.074980729619319</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.2208484003966776</v>
+        <v>-0.08089922934136451</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.832481539256008</v>
+        <v>2.916451041889196</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.755277849477958</v>
+        <v>-4.615328678422644</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.059521086609078</v>
+        <v>1.115500755031203</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.2208484003966776</v>
+        <v>-0.08089922934136451</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.829479610476002</v>
+        <v>2.91344911310919</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.535257051440947</v>
+        <v>-4.395307880385634</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.149108442834496</v>
+        <v>1.205088111256622</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.07962855532869739</v>
+        <v>0.06032061572661573</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.915790554527404</v>
+        <v>2.999760057160592</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.40238936237767</v>
+        <v>-4.262440191322356</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.218149701261631</v>
+        <v>1.274129369683756</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.07962855532869739</v>
+        <v>0.06032061572661573</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.931684737329228</v>
+        <v>3.015654239962415</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.282216279013171</v>
+        <v>-4.142267107957857</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.267364779047732</v>
+        <v>1.323344447469857</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.04054452803580155</v>
+        <v>0.1804936990911147</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.004934431788229</v>
+        <v>3.088903934421417</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.137544133913433</v>
+        <v>-3.99759496285812</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.335321739649067</v>
+        <v>1.391301408071192</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.185216673135539</v>
+        <v>0.3251658441908521</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.101825821409511</v>
+        <v>3.185795324042699</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.197418961271126</v>
+        <v>-4.057469790215812</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.297409300107416</v>
+        <v>1.353388968529541</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.1253418457778468</v>
+        <v>0.26529101683316</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.051938416396322</v>
+        <v>3.135907919029509</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.077598730360289</v>
+        <v>-3.937649559304975</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.360626561705959</v>
+        <v>1.416606230128085</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.1253418457778468</v>
+        <v>0.26529101683316</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.06722758563053</v>
+        <v>3.151197088263718</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.080068436822095</v>
+        <v>-3.940119265766781</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.267282878443678</v>
+        <v>1.323262546865804</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.1228721393160407</v>
+        <v>0.2628213103713538</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.973389961075888</v>
+        <v>3.057359463709076</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.148438623146105</v>
+        <v>-4.008489452090791</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.159196665399375</v>
+        <v>1.215176333821501</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.2720970094075688</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.898217241982918</v>
+        <v>2.982186744616106</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.162226675993152</v>
+        <v>-4.022277504937837</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.144118152892448</v>
+        <v>1.200097821314574</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.2720970094075688</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.88865395061481</v>
+        <v>2.972623453247998</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.193219835321857</v>
+        <v>-4.053270664266543</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9564304542013529</v>
+        <v>1.012410122623479</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.2720970094075688</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.713363515655197</v>
+        <v>2.797333018288384</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.017745575529387</v>
+        <v>-3.877796404474073</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.031187390110128</v>
+        <v>1.087167058532254</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.2720970094075688</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.717930747646984</v>
+        <v>2.801900250280172</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.128681828170636</v>
+        <v>-3.988732657115322</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.962554917814836</v>
+        <v>1.018534586236962</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.1321478383522556</v>
+        <v>0.2720970094075688</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.693672776408191</v>
+        <v>2.77764227904138</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.095018282698354</v>
+        <v>-3.95506911164304</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9791517212236545</v>
+        <v>1.03513138964578</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.1658113838245375</v>
+        <v>0.3057605548798506</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.717002288911466</v>
+        <v>2.800971791544654</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.035165663494631</v>
+        <v>-3.895216492439317</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.013265155337276</v>
+        <v>1.069244823759402</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.1658113838245375</v>
+        <v>0.3057605548798506</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.727174675343599</v>
+        <v>2.811144177976786</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.948922200468253</v>
+        <v>-3.80897302941294</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.042708811121687</v>
+        <v>1.098688479543813</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.1658113838245375</v>
+        <v>0.3057605548798506</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.722120945917459</v>
+        <v>2.806090448550647</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.994229019867233</v>
+        <v>-3.854279848811919</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.016361858806621</v>
+        <v>1.072341527228746</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.1250012208153067</v>
+        <v>0.2649503918706198</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.689410623556446</v>
+        <v>2.773380126189634</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.023262124569534</v>
+        <v>-3.883312953514221</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.005300489958802</v>
+        <v>1.061280158380927</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.1250012208153067</v>
+        <v>0.2649503918706198</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.689962496589547</v>
+        <v>2.773931999222735</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.930451643118675</v>
+        <v>-3.790502472063362</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9716973744305115</v>
+        <v>1.027677042852637</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.217811702266166</v>
+        <v>0.3577608733214792</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.674921477351428</v>
+        <v>2.758890979984617</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.974841112448102</v>
+        <v>-3.834891941392789</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9558150626233413</v>
+        <v>1.011794731045466</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.1734222329367384</v>
+        <v>0.3133714039920515</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.650161271678373</v>
+        <v>2.734130774311561</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.862169894211852</v>
+        <v>-3.722220723156539</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9959592584295645</v>
+        <v>1.05193892685169</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.2860934511729886</v>
+        <v>0.4260426222283017</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.712839711131846</v>
+        <v>2.796809213765034</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.74979289302918</v>
+        <v>-3.609843721973867</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.046401354733301</v>
+        <v>1.102381023155426</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.2860934511729886</v>
+        <v>0.4260426222283017</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.718331006962513</v>
+        <v>2.802300509595701</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.777573290930533</v>
+        <v>-3.63762411987522</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.046786397341299</v>
+        <v>1.102766065763424</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.2583130532716355</v>
+        <v>0.3982622243269486</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.71315996999024</v>
+        <v>2.797129472623428</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.860574571955812</v>
+        <v>-3.720625400900499</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8519416049318402</v>
+        <v>0.9079212733539654</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.2397421687444617</v>
+        <v>0.3796913397997749</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.540373159274589</v>
+        <v>2.624342661907777</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.969188650399143</v>
+        <v>-3.82923947934383</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9286456342737133</v>
+        <v>0.9846253026958385</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.2397421687444617</v>
+        <v>0.3796913397997749</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.660522819993795</v>
+        <v>2.744492322626983</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.933779612151</v>
+        <v>-3.793830441095687</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9573222756752935</v>
+        <v>1.013301944097419</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.2397421687444617</v>
+        <v>0.3796913397997749</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.675035846096118</v>
+        <v>2.759005348729306</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.895395949592849</v>
+        <v>-3.755446778537536</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9700951820409225</v>
+        <v>1.026074850463048</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.2781258313026129</v>
+        <v>0.4180750023579261</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.695485484973378</v>
+        <v>2.779454987606565</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.718279619557683</v>
+        <v>-3.57833044850237</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.037670742900291</v>
+        <v>1.093650411322417</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.2781258313026129</v>
+        <v>0.4180750023579261</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.69221451381868</v>
+        <v>2.776184016451868</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.763371864391228</v>
+        <v>-3.623422693335915</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.020317236728786</v>
+        <v>1.076296905150911</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.2162297881332231</v>
+        <v>0.3561789591885363</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.655760279678959</v>
+        <v>2.739729782312147</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.58399644315246</v>
+        <v>-3.444047272097148</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.085854380530708</v>
+        <v>1.141834048952833</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.3730065463039418</v>
+        <v>0.5129557173592549</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.743613309887805</v>
+        <v>2.827582812520992</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.629010656673067</v>
+        <v>-3.489061485617754</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.048656150454055</v>
+        <v>1.10463581887618</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.3426576509893372</v>
+        <v>0.4826068220446503</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.706211428030632</v>
+        <v>2.790180930663819</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.896015166945502</v>
+        <v>-3.756065995890189</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9475459086840265</v>
+        <v>1.003525577106152</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.1482946129463886</v>
+        <v>0.2882437840017018</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.595285167543808</v>
+        <v>2.679254670176996</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.997212948382675</v>
+        <v>-3.857263777327362</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9062707180056591</v>
+        <v>0.962250386427784</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.07988579940106943</v>
+        <v>0.2198349704563826</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.553443801313118</v>
+        <v>2.637413303946306</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.990701981768362</v>
+        <v>-3.85075281071305</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9064750662057008</v>
+        <v>0.9624547346278258</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.07988579940106943</v>
+        <v>0.2198349704563826</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.551043762867435</v>
+        <v>2.635013265500623</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.971663854061065</v>
+        <v>-3.831714683005752</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9106150364968646</v>
+        <v>0.9665947049189896</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.02170218806987489</v>
+        <v>0.161651359125188</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.512658315276963</v>
+        <v>2.596627817910151</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.002790485211683</v>
+        <v>-3.86284131415637</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.075746252975298</v>
+        <v>1.131725921397423</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.02170218806987489</v>
+        <v>0.161651359125188</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.690240184215644</v>
+        <v>2.774209686848832</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.0166572465456</v>
+        <v>-3.876708075490288</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.071032877427865</v>
+        <v>1.12701254584999</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.01615572866394804</v>
+        <v>0.1237934423913651</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.668358763161483</v>
+        <v>2.752328265794671</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.97185307500567</v>
+        <v>-3.831903903950358</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.094963076440763</v>
+        <v>1.150942744862888</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.01615572866394804</v>
+        <v>0.1237934423913651</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.674367293558409</v>
+        <v>2.758336796191597</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.582010952033977</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.824110104770668</v>
+        <v>-3.68244677140158</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.052010485811963</v>
+        <v>1.108675819159598</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.1516516285709351</v>
+        <v>0.1912257316469613</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.673001929176539</v>
+        <v>2.696746391022154</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.584804573565458</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.926124787301889</v>
+        <v>-3.784461453932801</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.013998234330955</v>
+        <v>1.070663567678591</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.1516516285709351</v>
+        <v>0.1912257316469613</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.67579555070802</v>
+        <v>2.699540012553635</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.585466921957117</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.919972081249105</v>
+        <v>-3.778308747880016</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.017121665143728</v>
+        <v>1.073786998491363</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.1578043346237194</v>
+        <v>0.1973784376997456</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.680149522731349</v>
+        <v>2.703893984576964</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.584547398697227</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.936781379399606</v>
+        <v>-3.795118046030518</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.009478422623637</v>
+        <v>1.066143755971273</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.1409950364732178</v>
+        <v>0.1805691395492439</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.669144420581158</v>
+        <v>2.692888882426773</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.650882952494048</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.874483380623484</v>
+        <v>-3.732820047254396</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.100733175930907</v>
+        <v>1.157398509278542</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.1409950364732178</v>
+        <v>0.1805691395492439</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.735479974377979</v>
+        <v>2.759224436223594</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.453174954208175</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.672693182958326</v>
+        <v>-3.531029849589238</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.983741256711097</v>
+        <v>1.040406590058732</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.3390132286423722</v>
+        <v>0.3785873317183983</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.656582891393598</v>
+        <v>2.680327353239214</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.52346518653035</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.59931508586959</v>
+        <v>-3.457651752500501</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.083382727868767</v>
+        <v>1.140048061216402</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4123913257311087</v>
+        <v>0.4519654288071349</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.770899981969015</v>
+        <v>2.794644443814631</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.538092922646394</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.697055630494564</v>
+        <v>-3.555392297125476</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.058914246134821</v>
+        <v>1.115579579482456</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.3965020475981285</v>
+        <v>0.4360761506741547</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.775994151205271</v>
+        <v>2.799738613050887</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.536628903471065</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.873393390617494</v>
+        <v>-3.731730057248405</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9869151229103208</v>
+        <v>1.043580456257956</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.2201642874751991</v>
+        <v>0.2597383905512253</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.668727475956185</v>
+        <v>2.692471937801801</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.535120521510994</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.796971344185567</v>
+        <v>-3.655308010816478</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.01597555952302</v>
+        <v>1.072640892870655</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.2201642874751991</v>
+        <v>0.2597383905512253</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.667219093996114</v>
+        <v>2.69096355584173</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.53498338894643</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.752598212546998</v>
+        <v>-3.610934879177909</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.033587679613884</v>
+        <v>1.090253012961519</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.2645374191137677</v>
+        <v>0.3041115221897939</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.693705840414691</v>
+        <v>2.717450302260307</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.529377183085021</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.629763991659831</v>
+        <v>-3.488100658290742</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.077115162107341</v>
+        <v>1.133780495454977</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.2645374191137677</v>
+        <v>0.3041115221897939</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.688099634553282</v>
+        <v>2.711844096398897</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.535758940112825</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.582108261098775</v>
+        <v>-3.440444927729686</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.102559211359568</v>
+        <v>1.159224544707204</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.3121931496748234</v>
+        <v>0.3517672527508495</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.723074829917719</v>
+        <v>2.746819291763335</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.54065131348755</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.481590102600021</v>
+        <v>-3.339926769230932</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.147658848133795</v>
+        <v>1.20432418148143</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.4127113081735779</v>
+        <v>0.4522854112496041</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.788278098391697</v>
+        <v>2.812022560237313</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.527405985963422</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.54225669300241</v>
+        <v>-3.400593359633321</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.110146884448711</v>
+        <v>1.166812217796347</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.3310129914550443</v>
+        <v>0.3705870945310704</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.726013780836449</v>
+        <v>2.749758242682065</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.531503688574051</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.497418291394012</v>
+        <v>-3.355754958024923</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.132179947702699</v>
+        <v>1.188845281050335</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.3355564243999137</v>
+        <v>0.3751305274759399</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.732837543214</v>
+        <v>2.756582005059615</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.535664628205129</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.59817692715101</v>
+        <v>-3.456513593781921</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.096037433030978</v>
+        <v>1.152702766378613</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.2467308556729083</v>
+        <v>0.2863049587489345</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.683703141608874</v>
+        <v>2.70744760345449</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.541544230732966</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.55397409006511</v>
+        <v>-3.412310756696021</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.119598170393175</v>
+        <v>1.17626350374081</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.2909336927588088</v>
+        <v>0.3305077958348349</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.716104446388252</v>
+        <v>2.739848908233868</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.539954231202214</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.590953117728553</v>
+        <v>-3.449289784359464</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.103216559797045</v>
+        <v>1.159881893144681</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.3279075945501393</v>
+        <v>0.3674816976261654</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.736698787932298</v>
+        <v>2.760443249777913</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.591201996385253</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.432661700189281</v>
+        <v>-3.290998366820192</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.217780891995794</v>
+        <v>1.274446225343429</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.3279075945501393</v>
+        <v>0.3674816976261654</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.787946553115337</v>
+        <v>2.811691014960953</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.589642700979506</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.225019696554805</v>
+        <v>-3.083356363185715</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.299278398043837</v>
+        <v>1.355943731391473</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.5355495981846154</v>
+        <v>0.5751237012606416</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.910972459890276</v>
+        <v>2.934716921735891</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.584590929217776</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.173987603832277</v>
+        <v>-3.032324270463187</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.314639463371118</v>
+        <v>1.371304796718754</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.5865816909071434</v>
+        <v>0.6261557939831696</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.936539943762063</v>
+        <v>2.960284405607678</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.601778333310481</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.108763422705071</v>
+        <v>-2.967100089335982</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.357916539914706</v>
+        <v>1.414581873262341</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.651805872034349</v>
+        <v>0.6913799751103752</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.992861856531091</v>
+        <v>3.016606318376707</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.597739305609762</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.071336402633937</v>
+        <v>-2.929673069264848</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.36884832024244</v>
+        <v>1.425513653590075</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.6570574100635307</v>
+        <v>0.6966315131395568</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.991973751647881</v>
+        <v>3.015718213493496</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.598996097941002</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.091448058668645</v>
+        <v>-2.949784725299556</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.362060450159797</v>
+        <v>1.418725783507432</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.6680847550609499</v>
+        <v>0.707658858136976</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.999846950977572</v>
+        <v>3.023591412823188</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.759553868962213</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.03770324424144</v>
+        <v>-2.896039910872351</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.544116146951889</v>
+        <v>1.600781480299525</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.6781480645014119</v>
+        <v>0.717722167577438</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.16644270766306</v>
+        <v>3.190187169508676</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.87966677818003</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.013911675635298</v>
+        <v>-2.872248342266209</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.673745683612164</v>
+        <v>1.730411016959799</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.7019396331075541</v>
+        <v>0.7415137361835803</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.300830558044563</v>
+        <v>3.324575019890179</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.871374754193889</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.98782759137149</v>
+        <v>-2.846164258002401</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.675887293331546</v>
+        <v>1.732552626679181</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.7019396331075541</v>
+        <v>0.7415137361835803</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.292538534058422</v>
+        <v>3.316282995904038</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.869567949777668</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.909696410522543</v>
+        <v>-2.768033077153454</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.705332961254904</v>
+        <v>1.76199829460254</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.7761164439912387</v>
+        <v>0.8156905470672648</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.335237816172412</v>
+        <v>3.358982278018027</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.88712235550446</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.90080394912926</v>
+        <v>-2.759140615760171</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.726444351539008</v>
+        <v>1.783109684886644</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.7761164439912387</v>
+        <v>0.8156905470672648</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.352792221899203</v>
+        <v>3.376536683744819</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.878977402909044</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.069280066099138</v>
+        <v>-2.927616732730049</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.650908952155641</v>
+        <v>1.707574285503277</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.7481686082746579</v>
+        <v>0.7877427113506841</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.327878567873839</v>
+        <v>3.351623029719454</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.860247100096906</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.371480537237555</v>
+        <v>-2.229817203868466</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.911298460888136</v>
+        <v>1.967963794235772</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.6778205489042473</v>
+        <v>0.7173946519802734</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.266939429439454</v>
+        <v>3.29068389128507</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.85091112259381</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.348759433554402</v>
+        <v>-2.207096100185313</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.911050924858302</v>
+        <v>1.967716258205938</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.6778205489042473</v>
+        <v>0.7173946519802734</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.257603451936359</v>
+        <v>3.281347913781974</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.009817248444979</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.347034390264358</v>
+        <v>-2.205371056895269</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.070647068025488</v>
+        <v>2.127312401373124</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.679545592194291</v>
+        <v>0.7191196952703172</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.417544603761554</v>
+        <v>3.44128906560717</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.046895070938626</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.501815397042614</v>
+        <v>-2.360152063673524</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.045812487807833</v>
+        <v>2.102477821155469</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.6461779181398148</v>
+        <v>0.685752021215841</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.434601821822515</v>
+        <v>3.45834628366813</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.043570426928171</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.450380063657954</v>
+        <v>-2.308716730288865</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.063061977151242</v>
+        <v>2.119727310498878</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.6976132515244745</v>
+        <v>0.7371873546005007</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.462138377842856</v>
+        <v>3.485882839688472</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.053576580572912</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.423428839331466</v>
+        <v>-2.281765505962377</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.083848620526579</v>
+        <v>2.140513953874215</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.7124935975521937</v>
+        <v>0.7520677006282198</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.481072739104229</v>
+        <v>3.504817200949844</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.237679712717872</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.559381847387782</v>
+        <v>-2.417718514018693</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.213570549449012</v>
+        <v>2.270235882796648</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.7124935975521937</v>
+        <v>0.7520677006282198</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.665175871249189</v>
+        <v>3.688920333094805</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.229796407620865</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.581789965192654</v>
+        <v>-2.440126631823565</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.196723997230056</v>
+        <v>2.253389330577692</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.7124935975521937</v>
+        <v>0.7520677006282198</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.657292566152182</v>
+        <v>3.681037027997798</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.231850407170503</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.729795732672054</v>
+        <v>-2.588132399302965</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.139575689787934</v>
+        <v>2.19624102313557</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.6257665886886522</v>
+        <v>0.6653406917646784</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.607310360383694</v>
+        <v>3.63105482222931</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.28810412489235</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.739236658560584</v>
+        <v>-2.597573325191495</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.192053037154369</v>
+        <v>2.248718370502005</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.7481937062320436</v>
+        <v>0.7877678093080698</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.737020348631576</v>
+        <v>3.760764810477192</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.290995219437651</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.737949895021027</v>
+        <v>-2.596286561651938</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.195458837115493</v>
+        <v>2.252124170463128</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7494804697716002</v>
+        <v>0.7890545728476264</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.740683501300611</v>
+        <v>3.764427963146227</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.289107032331426</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.739506949010319</v>
+        <v>-2.59784361564123</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.192947828413551</v>
+        <v>2.249613161761187</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7494804697716002</v>
+        <v>0.7890545728476264</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.738795314194387</v>
+        <v>3.762539776040002</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.283927261934288</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.746778834533783</v>
+        <v>-2.605115501164694</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.184859303807028</v>
+        <v>2.241524637154663</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7422085842481354</v>
+        <v>0.7817826873241616</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.72925241248317</v>
+        <v>3.752996874328785</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.282361272144441</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.744937815475532</v>
+        <v>-2.603274482106443</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.18402972164048</v>
+        <v>2.240695054988116</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7434768109196038</v>
+        <v>0.78305091399563</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.728447358696203</v>
+        <v>3.752191820541819</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.295434679010359</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.751846520975213</v>
+        <v>-2.610183187606124</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.194339646306527</v>
+        <v>2.251004979654162</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7434768109196038</v>
+        <v>0.78305091399563</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.741520765562122</v>
+        <v>3.765265227407737</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.295434679010359</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.753408163790072</v>
+        <v>-2.611744830420983</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.193714989180583</v>
+        <v>2.250380322528219</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7434768109196038</v>
+        <v>0.78305091399563</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.741520765562122</v>
+        <v>3.765265227407737</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.293958720137361</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.781308950899545</v>
+        <v>-2.639645617530456</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.181078715463796</v>
+        <v>2.237744048811432</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.708879886776669</v>
+        <v>0.7484539898526952</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.719286652203363</v>
+        <v>3.743031114048978</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.29072316411456</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.784341948412219</v>
+        <v>-2.64267861504313</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.176629960435925</v>
+        <v>2.233295293783561</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7058468892639951</v>
+        <v>0.7454209923400212</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.714231297672957</v>
+        <v>3.737975759518573</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.357429123705064</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.804403269688726</v>
+        <v>-2.662739936319637</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.235311391515826</v>
+        <v>2.291976724863462</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.685785567987488</v>
+        <v>0.7253596710635142</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.768900464497557</v>
+        <v>3.792644926343173</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.497740842706911</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.06112408768355</v>
+        <v>-2.919460754314461</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.272934783319744</v>
+        <v>2.329600116667379</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5773709938436732</v>
+        <v>0.6169450969196993</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.844163439013115</v>
+        <v>3.86790790085873</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.566721111852551</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.215110505459691</v>
+        <v>-3.073447172090602</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.280320485354927</v>
+        <v>2.336985818702563</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5773709938436732</v>
+        <v>0.6169450969196993</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.913143708158755</v>
+        <v>3.93688817000437</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.552772313972671</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.164588601632025</v>
+        <v>-3.022925268262936</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.286580449006114</v>
+        <v>2.34324578235375</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5773709938436732</v>
+        <v>0.6169450969196993</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.899194910278875</v>
+        <v>3.922939372124492</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.806739025974591</v>
+        <v>3.404975429165309</v>
       </c>
       <c r="C2019" t="n">
         <v>3.564642803028085</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.420719234322513</v>
+        <v>-3.38561183777219</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.195998684985333</v>
+        <v>2.210041643605462</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.5773709938436732</v>
+        <v>0.6169450969196993</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.91106539933429</v>
+        <v>3.934809861179906</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240709.xlsx
+++ b/tame_output/ON/bt/strategyON_20240709.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>57.6%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.6%</t>
+          <t>-70.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.8%</t>
+          <t>108.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.0%</t>
+          <t>121.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>95.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-644.5%</t>
+          <t>-609.8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.4%</t>
+          <t>-48.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.2%</t>
+          <t>-64.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.3%</t>
+          <t>457.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-500.1%</t>
+          <t>-468.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,62 +1135,62 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-258.2%</t>
+          <t>-244.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.0%</t>
+          <t>-37.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>-257.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-155.2%</t>
+          <t>-142.6%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-263.7%</t>
+          <t>-242.5%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.8%</t>
+          <t>-28.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>81.4%</t>
+          <t>478.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-119.0%</t>
+          <t>-127.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-162.3%</t>
+          <t>-145.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>79.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-158.6%</t>
+          <t>-145.9%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.1%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-52.5%</t>
+          <t>-42.2%</t>
         </is>
       </c>
     </row>
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.594926232146691</v>
+        <v>-4.24806595500523</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.28574461685836</v>
+        <v>1.424488727714945</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.4034927703575531</v>
+        <v>-0.1910094890569949</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.881975871816252</v>
+        <v>3.009465840596587</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.829620226279244</v>
+        <v>-4.482759949137782</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.18015179420743</v>
+        <v>1.318895905064014</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.3971565031282979</v>
+        <v>-0.1846732218277398</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.874062407155896</v>
+        <v>3.001552375936231</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.165282873509696</v>
+        <v>-4.818422596368235</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.044467326971214</v>
+        <v>1.183211437827798</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.4650874886172027</v>
+        <v>-0.2526042073166446</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.831884407518518</v>
+        <v>2.959374376298853</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.528909118410009</v>
+        <v>-5.182048841268548</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.9055043892453303</v>
+        <v>1.044248500101915</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.5633091254843285</v>
+        <v>-0.3508258441837704</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.779438985632484</v>
+        <v>2.906928954412819</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.894036501048756</v>
+        <v>-5.547176223907295</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7587079511956629</v>
+        <v>0.8974520620522473</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.859619909783341</v>
+        <v>-0.6471366284827829</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.600907030058909</v>
+        <v>2.728396998839243</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.302625278229435</v>
+        <v>-5.955765001087974</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5940339843381501</v>
+        <v>0.7327780951947349</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.268208686964019</v>
+        <v>-1.055725405663461</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.354515307765261</v>
+        <v>2.482005276545595</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.579201378545267</v>
+        <v>-6.232341101403806</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.478588976683278</v>
+        <v>0.6173330875398624</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.268208686964019</v>
+        <v>-1.055725405663461</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.349700740236721</v>
+        <v>2.477190709017056</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.995593252832265</v>
+        <v>-6.648732975690804</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.3100262775773563</v>
+        <v>0.4487703884339407</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.268208686964019</v>
+        <v>-1.055725405663461</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.347694790845599</v>
+        <v>2.475184759625933</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.239864653559335</v>
+        <v>-6.893004376417873</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.2225764079552075</v>
+        <v>0.3613205188117918</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.268208686964019</v>
+        <v>-1.055725405663461</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.357953481514278</v>
+        <v>2.485443450294612</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.445115672796095</v>
+        <v>-7.098255395654633</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.1365755654061984</v>
+        <v>0.2753196762627832</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.268208686964019</v>
+        <v>-1.055725405663461</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.354053046659972</v>
+        <v>2.481543015440308</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.608695550980478</v>
+        <v>-7.261835273839017</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.069548534187446</v>
+        <v>0.2082926450440308</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.268208686964019</v>
+        <v>-1.055725405663461</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.352457966714973</v>
+        <v>2.479947935495308</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.905356892790675</v>
+        <v>-7.558496615649214</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.04533702660742467</v>
+        <v>0.09340708424916011</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.336951822697898</v>
+        <v>-1.12446854139734</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.314991061203854</v>
+        <v>2.442481029984189</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.092076601099977</v>
+        <v>-7.745216323958517</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.1240512144655486</v>
+        <v>0.01469289639103577</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.336951822697898</v>
+        <v>-1.12446854139734</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.310964756669451</v>
+        <v>2.438454725449786</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.475077989842609</v>
+        <v>-8.128217712701147</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.277353871284185</v>
+        <v>-0.1386097604276006</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.336951822697898</v>
+        <v>-1.12446854139734</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.310862655347867</v>
+        <v>2.438352624128202</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.656947780827643</v>
+        <v>-8.310087503686182</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.3475302717067685</v>
+        <v>-0.2087861608501842</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.518821613682933</v>
+        <v>-1.306338332382375</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.204312296728276</v>
+        <v>2.331802265508611</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.016478103331645</v>
+        <v>-8.669617826190184</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.4859920974103193</v>
+        <v>-0.3472479865537346</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.518821613682933</v>
+        <v>-1.306338332382375</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.209662600026327</v>
+        <v>2.337152568806661</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.066827166785867</v>
+        <v>-8.719966889644406</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.4982157028348304</v>
+        <v>-0.3594715919782461</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.569170677137155</v>
+        <v>-1.356687395836597</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.187369181910971</v>
+        <v>2.314859150691306</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.164446444207263</v>
+        <v>-8.817586167065802</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.5342216631816199</v>
+        <v>-0.3954775523250356</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.666789954558552</v>
+        <v>-1.454306673257994</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.131839366079902</v>
+        <v>2.259329334860237</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.311972532212906</v>
+        <v>-8.965112255071444</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.5903385420623048</v>
+        <v>-0.4515944312057205</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.814316042564195</v>
+        <v>-1.601832761263637</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.046217269598088</v>
+        <v>2.173707238378423</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.516230707542769</v>
+        <v>-9.169370430401308</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.6665286150756082</v>
+        <v>-0.5277845042190235</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.941954987178184</v>
+        <v>-1.729471705877626</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.975147099948336</v>
+        <v>2.102637068728672</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.549883546051243</v>
+        <v>-9.203023268909782</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.6755071959945615</v>
+        <v>-0.5367630851379768</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.042368355095221</v>
+        <v>-1.829885073794663</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.91938163368255</v>
+        <v>2.046871602462885</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.476413714383794</v>
+        <v>-9.129553437242333</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.6307475618341609</v>
+        <v>-0.4920034509775761</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.968898523427773</v>
+        <v>-1.756415242127215</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.978835234176441</v>
+        <v>2.106325202956776</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.651538131770337</v>
+        <v>-9.304677854628876</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.6862421080412613</v>
+        <v>-0.547497997184677</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.144022940814317</v>
+        <v>-1.931539659513759</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.888315804492031</v>
+        <v>2.015805773272366</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.885990225784827</v>
+        <v>-9.539129948643366</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.7872421105486533</v>
+        <v>-0.6484979996920686</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.144022940814317</v>
+        <v>-1.931539659513759</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.881096639590435</v>
+        <v>2.00858660837077</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.990364956811273</v>
+        <v>-9.643504679669812</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.8356641937332081</v>
+        <v>-0.6969200828766233</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.248397671840763</v>
+        <v>-2.035914390540204</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.811799610200591</v>
+        <v>1.939289578980927</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.0431511124116</v>
+        <v>-9.696290835270139</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.8556628661347823</v>
+        <v>-0.7169187552781979</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.34407315842316</v>
+        <v>-2.131589877122601</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.75551010808971</v>
+        <v>1.883000076870045</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.16918790577989</v>
+        <v>-9.822327628638428</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.9033838548529833</v>
+        <v>-0.764639743996399</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.318821535613417</v>
+        <v>-2.106338254312859</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.77335481040467</v>
+        <v>1.900844779185005</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.11211613388396</v>
+        <v>-9.765255856742497</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.87656481040821</v>
+        <v>-0.7378206995516257</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.318821535613417</v>
+        <v>-2.106338254312859</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.777345146091071</v>
+        <v>1.904835114871406</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.25378797560808</v>
+        <v>-9.906927698466617</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.9347087739965998</v>
+        <v>-0.7959646631400155</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.318821535613417</v>
+        <v>-2.106338254312859</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.775869919192329</v>
+        <v>1.903359887972664</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.20419713118324</v>
+        <v>-9.857336854041783</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.899819026061794</v>
+        <v>-0.7610749152052096</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.269230691188584</v>
+        <v>-2.056747409888025</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.820677836012101</v>
+        <v>1.948167804792436</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.05527879671139</v>
+        <v>-9.708418519569927</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.8533028259197342</v>
+        <v>-0.7145587150631498</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.23798110045341</v>
+        <v>-2.025497819152852</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.826376456806522</v>
+        <v>1.953866425586857</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.829433643991976</v>
+        <v>-9.482573366850517</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.7533856917957609</v>
+        <v>-0.614641580939177</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.196054424866247</v>
+        <v>-1.983571143565688</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.861111535195029</v>
+        <v>1.988601503975364</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.704854987654384</v>
+        <v>-9.357994710512925</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.7024150847046653</v>
+        <v>-0.5636709738480814</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.196054424866247</v>
+        <v>-1.983571143565688</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.862250679751088</v>
+        <v>1.989740648531423</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.757750275698671</v>
+        <v>-9.410889998557211</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.7209394257602724</v>
+        <v>-0.5821953149036885</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.191099078777801</v>
+        <v>-1.978615797477242</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.867857661566263</v>
+        <v>1.995347630346599</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.68561710041079</v>
+        <v>-9.33875682326933</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.6863524514064832</v>
+        <v>-0.5476083405498997</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.191099078777801</v>
+        <v>-1.978615797477242</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.8735913658049</v>
+        <v>2.001081334585235</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.614250707801142</v>
+        <v>-9.267390430659683</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.6675431567564898</v>
+        <v>-0.5287990458999059</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.119732686168153</v>
+        <v>-1.907249404867594</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.906673938976823</v>
+        <v>2.034163907757159</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.520791673815918</v>
+        <v>-9.173931396674458</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.6400430244753075</v>
+        <v>-0.5012989136187236</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.119732686168153</v>
+        <v>-1.907249404867594</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.896790457663916</v>
+        <v>2.024280426444251</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.25354987294752</v>
+        <v>-8.906689595806061</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.5349808646273222</v>
+        <v>-0.3962367537707383</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.119732686168153</v>
+        <v>-1.907249404867594</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.894955897164542</v>
+        <v>2.022445865944877</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.155642834271029</v>
+        <v>-8.80878255712957</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.4961183641301865</v>
+        <v>-0.3573742532736026</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.051746936307596</v>
+        <v>-1.839263655007038</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.935447032107415</v>
+        <v>2.06293700088775</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.131689293295072</v>
+        <v>-8.784829016153612</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.48586844159431</v>
+        <v>-0.3471243307377261</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.027793395331639</v>
+        <v>-1.81531011403108</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.950487662838483</v>
+        <v>2.077977631618818</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.867629354972275</v>
+        <v>-8.520769077830815</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.3935047824269433</v>
+        <v>-0.2547606715703594</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.763733457008843</v>
+        <v>-1.551250175708284</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.095663309670408</v>
+        <v>2.223153278450744</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.160549731467437</v>
+        <v>-7.813689454325977</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.1134599666853093</v>
+        <v>0.025284144171275</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.763733457008843</v>
+        <v>-1.551250175708284</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.092876276010108</v>
+        <v>2.220366244790443</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.120365433101247</v>
+        <v>-7.773505155959787</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.09704262345099179</v>
+        <v>0.04170148740559254</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.723549158642652</v>
+        <v>-1.511065877342093</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.117330478917664</v>
+        <v>2.244820447697999</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.956965562161884</v>
+        <v>-7.610105285020424</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.03231585385448987</v>
+        <v>0.1064282570020945</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.56014928770329</v>
+        <v>-1.347666006402731</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.214737222702038</v>
+        <v>2.342227191482373</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.723484339932286</v>
+        <v>-7.376624062790825</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.06900106387520211</v>
+        <v>0.2077451747317864</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.326668065473691</v>
+        <v>-1.114184784173132</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.362750384877649</v>
+        <v>2.490240353657985</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.573817948924771</v>
+        <v>-7.22695767178331</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.1259754099652488</v>
+        <v>0.2647195208218331</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.233764574231155</v>
+        <v>-1.021281292930596</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.415600269310212</v>
+        <v>2.543090238090547</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.441542475293884</v>
+        <v>-7.094682198152424</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.1742530861646308</v>
+        <v>0.3129971970212146</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.101489100600269</v>
+        <v>-0.8890058192997095</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.490333040235771</v>
+        <v>2.617823009016107</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.285804142734142</v>
+        <v>-6.938943865592682</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.2393634798761641</v>
+        <v>0.378107590732748</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.9457507680405269</v>
+        <v>-0.7332674867399679</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.586591100459253</v>
+        <v>2.714081069239588</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.036804344050561</v>
+        <v>-6.689944066909101</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3518697405732554</v>
+        <v>0.4906138514298393</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.9457507680405269</v>
+        <v>-0.7332674867399679</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.599497441682911</v>
+        <v>2.726987410463247</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.142394333823666</v>
+        <v>-6.795534056682206</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.1816578150647947</v>
+        <v>0.3204019259213791</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.051340757813631</v>
+        <v>-0.8388574765130723</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.40816751821983</v>
+        <v>2.535657487000165</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.161129235942263</v>
+        <v>-6.814268958800803</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2227081960944424</v>
+        <v>0.3614523069510263</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.056936767473763</v>
+        <v>-0.8444534861732036</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.453354254300837</v>
+        <v>2.580844223081173</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.013189194534664</v>
+        <v>-6.666328917393203</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.1620052899693145</v>
+        <v>0.3007494008258984</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.036615851565205</v>
+        <v>-0.824132570264646</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.345667881157804</v>
+        <v>2.47315784993814</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.960219672280675</v>
+        <v>-6.613359395139215</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.1744791126174317</v>
+        <v>0.313223223474016</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.9836463293112162</v>
+        <v>-0.7711630480106572</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.36873560825672</v>
+        <v>2.496225577037055</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.916671265509985</v>
+        <v>-6.569810988368524</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.1849378632306147</v>
+        <v>0.323681974087199</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.9836463293112162</v>
+        <v>-0.7711630480106572</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.361774996161627</v>
+        <v>2.489264964941962</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.674522872056126</v>
+        <v>-6.327662594914666</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.296259574993301</v>
+        <v>0.4350036858498854</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.9836463293112162</v>
+        <v>-0.7711630480106572</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.37623735054277</v>
+        <v>2.503727319323105</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.566263734933605</v>
+        <v>-6.219403457792144</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3340953503015047</v>
+        <v>0.4728394611580891</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.9836463293112162</v>
+        <v>-0.7711630480106572</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.370769471001965</v>
+        <v>2.4982594397823</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.442972600116474</v>
+        <v>-6.096112322975014</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.3809098982389338</v>
+        <v>0.5196540090955182</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.8603551944940857</v>
+        <v>-0.6478719131935267</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.44224224590282</v>
+        <v>2.569732214683155</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.421823401213031</v>
+        <v>-6.07496312407157</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.3970705560376366</v>
+        <v>0.5358146668942205</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.8392059955906424</v>
+        <v>-0.6267227142900833</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.462632743482211</v>
+        <v>2.590122712262546</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.178057959229586</v>
+        <v>-5.831197682088126</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.4903574411780647</v>
+        <v>0.629101552034649</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.8392059955906424</v>
+        <v>-0.6267227142900833</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.458413451829262</v>
+        <v>2.585903420609597</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.076295138952291</v>
+        <v>-5.729434861810831</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.533186883208999</v>
+        <v>0.6719309940655829</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.8259869271982136</v>
+        <v>-0.6135036458976546</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.468469206784735</v>
+        <v>2.59595917556507</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.826444745003217</v>
+        <v>-5.479584467861756</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6258691157723311</v>
+        <v>0.764613226628915</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.8259869271982136</v>
+        <v>-0.6135036458976546</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.461211281768437</v>
+        <v>2.588701250548772</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.650552652535785</v>
+        <v>-5.303692375394323</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6998250762799523</v>
+        <v>0.8385691871365371</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.8259869271982136</v>
+        <v>-0.6135036458976546</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.464810405289086</v>
+        <v>2.592300374069421</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.479106189513321</v>
+        <v>-5.13224591237186</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7817311675434917</v>
+        <v>0.920475278400076</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.6545404641757505</v>
+        <v>-0.4420571828751915</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.581005789157117</v>
+        <v>2.708495757937453</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.404816623774982</v>
+        <v>-5.057956346633521</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8104674714551243</v>
+        <v>0.9492115823117087</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.5802508984374113</v>
+        <v>-0.3677676171368522</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.624600006216418</v>
+        <v>2.752089974996753</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.201231710485734</v>
+        <v>-4.994320604399586</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8965962378251406</v>
+        <v>0.9793606802595998</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.3766659851481636</v>
+        <v>-0.3041318749029177</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.751445755244283</v>
+        <v>2.794966221391431</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.089804951159814</v>
+        <v>-4.882893845073666</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9223612003393042</v>
+        <v>1.005125642773763</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.3766659851481636</v>
+        <v>-0.3041318749029177</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.732640014028079</v>
+        <v>2.776160480175227</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.849374454354954</v>
+        <v>-4.642463348268806</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.020276475686126</v>
+        <v>1.103040918120585</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.1362354883433033</v>
+        <v>-0.06370137809805737</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.878641388735873</v>
+        <v>2.92216185488302</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.777131886183759</v>
+        <v>-4.570220780097611</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.053102816789424</v>
+        <v>1.135867259223883</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.1362354883433033</v>
+        <v>-0.06370137809805737</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.882570702570693</v>
+        <v>2.926091168717841</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.724133563902371</v>
+        <v>-4.517222457816223</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.074980729619319</v>
+        <v>1.157745172053778</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.08089922934136451</v>
+        <v>-0.008365119096118534</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.916451041889196</v>
+        <v>2.959971508036344</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.615328678422644</v>
+        <v>-4.408417572336496</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.115500755031203</v>
+        <v>1.198265197465662</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.08089922934136451</v>
+        <v>-0.008365119096118534</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.91344911310919</v>
+        <v>2.956969579256338</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.395307880385634</v>
+        <v>-4.188396774299486</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.205088111256622</v>
+        <v>1.287852553691081</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.06032061572661573</v>
+        <v>0.1328547259718617</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.999760057160592</v>
+        <v>3.04328052330774</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.262440191322356</v>
+        <v>-4.055529085236208</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.274129369683756</v>
+        <v>1.356893812118215</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.06032061572661573</v>
+        <v>0.1328547259718617</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.015654239962415</v>
+        <v>3.059174706109563</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.142267107957857</v>
+        <v>-3.93535600187171</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.323344447469857</v>
+        <v>1.406108889904317</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.1804936990911147</v>
+        <v>0.2530278093363607</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.088903934421417</v>
+        <v>3.132424400568564</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.99759496285812</v>
+        <v>-3.790683856771972</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.391301408071192</v>
+        <v>1.474065850505651</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.3251658441908521</v>
+        <v>0.3976999544360981</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.185795324042699</v>
+        <v>3.229315790189847</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.057469790215812</v>
+        <v>-3.850558684129664</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.353388968529541</v>
+        <v>1.436153410964</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.26529101683316</v>
+        <v>0.337825127078406</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.135907919029509</v>
+        <v>3.179428385176657</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.937649559304975</v>
+        <v>-3.730738453218827</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.416606230128085</v>
+        <v>1.499370672562544</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.26529101683316</v>
+        <v>0.337825127078406</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.151197088263718</v>
+        <v>3.194717554410865</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.940119265766781</v>
+        <v>-3.733208159680633</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.323262546865804</v>
+        <v>1.406026989300263</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.2628213103713538</v>
+        <v>0.3353554206165998</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.057359463709076</v>
+        <v>3.100879929856224</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.008489452090791</v>
+        <v>-3.801578346004643</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.215176333821501</v>
+        <v>1.29794077625596</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.2720970094075688</v>
+        <v>0.3446311196528147</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.982186744616106</v>
+        <v>3.025707210763254</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.022277504937837</v>
+        <v>-3.815366398851689</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.200097821314574</v>
+        <v>1.282862263749033</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.2720970094075688</v>
+        <v>0.3446311196528147</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.972623453247998</v>
+        <v>3.016143919395145</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.053270664266543</v>
+        <v>-3.846359558180395</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.012410122623479</v>
+        <v>1.095174565057938</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.2720970094075688</v>
+        <v>0.3446311196528147</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.797333018288384</v>
+        <v>2.840853484435532</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.877796404474073</v>
+        <v>-3.670885298387926</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.087167058532254</v>
+        <v>1.169931500966713</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.2720970094075688</v>
+        <v>0.3446311196528147</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.801900250280172</v>
+        <v>2.84542071642732</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.988732657115322</v>
+        <v>-3.781821551029174</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.018534586236962</v>
+        <v>1.101299028671421</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.2720970094075688</v>
+        <v>0.3446311196528147</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.77764227904138</v>
+        <v>2.821162745188527</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.95506911164304</v>
+        <v>-3.748158005556892</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.03513138964578</v>
+        <v>1.117895832080239</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.3057605548798506</v>
+        <v>0.3782946651250966</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.800971791544654</v>
+        <v>2.844492257691801</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.895216492439317</v>
+        <v>-3.688305386353169</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.069244823759402</v>
+        <v>1.152009266193861</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.3057605548798506</v>
+        <v>0.3782946651250966</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.811144177976786</v>
+        <v>2.854664644123934</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.80897302941294</v>
+        <v>-3.602061923326792</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.098688479543813</v>
+        <v>1.181452921978272</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.3057605548798506</v>
+        <v>0.3782946651250966</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.806090448550647</v>
+        <v>2.849610914697794</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.854279848811919</v>
+        <v>-3.647368742725772</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.072341527228746</v>
+        <v>1.155105969663206</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.2649503918706198</v>
+        <v>0.3374845021158658</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.773380126189634</v>
+        <v>2.816900592336781</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.883312953514221</v>
+        <v>-3.676401847428073</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.061280158380927</v>
+        <v>1.144044600815386</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.2649503918706198</v>
+        <v>0.3374845021158658</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.773931999222735</v>
+        <v>2.817452465369883</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.790502472063362</v>
+        <v>-3.583591365977214</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.027677042852637</v>
+        <v>1.110441485287096</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.3577608733214792</v>
+        <v>0.4302949835667251</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.758890979984617</v>
+        <v>2.802411446131764</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.834891941392789</v>
+        <v>-3.627980835306642</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.011794731045466</v>
+        <v>1.094559173479926</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.3133714039920515</v>
+        <v>0.3859055142372975</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.734130774311561</v>
+        <v>2.777651240458708</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.722220723156539</v>
+        <v>-3.515309617070391</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.05193892685169</v>
+        <v>1.134703369286149</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4260426222283017</v>
+        <v>0.4985767324735477</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.796809213765034</v>
+        <v>2.840329679912181</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.609843721973867</v>
+        <v>-3.402932615887719</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.102381023155426</v>
+        <v>1.185145465589885</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4260426222283017</v>
+        <v>0.4985767324735477</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.802300509595701</v>
+        <v>2.845820975742849</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.63762411987522</v>
+        <v>-3.430713013789072</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.102766065763424</v>
+        <v>1.185530508197883</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.3982622243269486</v>
+        <v>0.4707963345721947</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.797129472623428</v>
+        <v>2.840649938770576</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.720625400900499</v>
+        <v>-3.513714294814351</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9079212733539654</v>
+        <v>0.9906857157884246</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3796913397997749</v>
+        <v>0.4522254500450209</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.624342661907777</v>
+        <v>2.667863128054925</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.82923947934383</v>
+        <v>-3.622328373257682</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9846253026958385</v>
+        <v>1.067389745130298</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3796913397997749</v>
+        <v>0.4522254500450209</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.744492322626983</v>
+        <v>2.788012788774131</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.793830441095687</v>
+        <v>-3.586919335009539</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.013301944097419</v>
+        <v>1.096066386531878</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3796913397997749</v>
+        <v>0.4522254500450209</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.759005348729306</v>
+        <v>2.802525814876454</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.755446778537536</v>
+        <v>-3.548535672451388</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.026074850463048</v>
+        <v>1.108839292897507</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4180750023579261</v>
+        <v>0.4906091126031721</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.779454987606565</v>
+        <v>2.822975453753713</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.57833044850237</v>
+        <v>-3.371419342416222</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.093650411322417</v>
+        <v>1.176414853756876</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4180750023579261</v>
+        <v>0.4906091126031721</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.776184016451868</v>
+        <v>2.819704482599015</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.623422693335915</v>
+        <v>-3.416511587249768</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.076296905150911</v>
+        <v>1.159061347585371</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3561789591885363</v>
+        <v>0.4287130694337823</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.739729782312147</v>
+        <v>2.783250248459295</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.444047272097148</v>
+        <v>-3.237136166011</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.141834048952833</v>
+        <v>1.224598491387292</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5129557173592549</v>
+        <v>0.585489827604501</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.827582812520992</v>
+        <v>2.87110327866814</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.489061485617754</v>
+        <v>-3.282150379531606</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.10463581887618</v>
+        <v>1.187400261310639</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4826068220446503</v>
+        <v>0.5551409322898964</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.790180930663819</v>
+        <v>2.833701396810967</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.756065995890189</v>
+        <v>-3.549154889804042</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.003525577106152</v>
+        <v>1.086290019540611</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2882437840017018</v>
+        <v>0.3607778942469478</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.679254670176996</v>
+        <v>2.722775136324143</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.857263777327362</v>
+        <v>-3.650352671241214</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.962250386427784</v>
+        <v>1.045014828862243</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2198349704563826</v>
+        <v>0.2923690807016286</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.637413303946306</v>
+        <v>2.680933770093453</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.85075281071305</v>
+        <v>-3.643841704626902</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9624547346278258</v>
+        <v>1.045219177062285</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2198349704563826</v>
+        <v>0.2923690807016286</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.635013265500623</v>
+        <v>2.67853373164777</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.831714683005752</v>
+        <v>-3.624803576919605</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9665947049189896</v>
+        <v>1.049359147353449</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.161651359125188</v>
+        <v>0.2341854693704341</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.596627817910151</v>
+        <v>2.640148284057299</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.86284131415637</v>
+        <v>-3.655930208070223</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.131725921397423</v>
+        <v>1.214490363831882</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.161651359125188</v>
+        <v>0.2341854693704341</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.774209686848832</v>
+        <v>2.817730152995979</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.876708075490288</v>
+        <v>-3.66979696940414</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.12701254584999</v>
+        <v>1.209776988284449</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1237934423913651</v>
+        <v>0.1963275526366111</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.752328265794671</v>
+        <v>2.795848731941819</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.831903903950358</v>
+        <v>-3.62499279786421</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.150942744862888</v>
+        <v>1.233707187297347</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1237934423913651</v>
+        <v>0.1963275526366111</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.758336796191597</v>
+        <v>2.801857262338745</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.582010952033977</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.68244677140158</v>
+        <v>-3.477249827629208</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.108675819159598</v>
+        <v>1.190754596668547</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.1912257316469613</v>
+        <v>0.3641349098714943</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.696746391022154</v>
+        <v>2.800491897956874</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.584804573565458</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.784461453932801</v>
+        <v>-3.579264510160429</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.070663567678591</v>
+        <v>1.15274234518754</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.1912257316469613</v>
+        <v>0.3641349098714943</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.699540012553635</v>
+        <v>2.803285519488355</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.585466921957117</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.778308747880016</v>
+        <v>-3.573111804107644</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.073786998491363</v>
+        <v>1.155865776000312</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.1973784376997456</v>
+        <v>0.3702876159242786</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.703893984576964</v>
+        <v>2.807639491511684</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.584547398697227</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.795118046030518</v>
+        <v>-3.589921102258146</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.066143755971273</v>
+        <v>1.148222533480221</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.1805691395492439</v>
+        <v>0.3534783177737769</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.692888882426773</v>
+        <v>2.796634389361493</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.650882952494048</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.732820047254396</v>
+        <v>-3.527623103482024</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.157398509278542</v>
+        <v>1.239477286787491</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.1805691395492439</v>
+        <v>0.3534783177737769</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.759224436223594</v>
+        <v>2.862969943158314</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.453174954208175</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.531029849589238</v>
+        <v>-3.325832905816866</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.040406590058732</v>
+        <v>1.122485367567681</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.3785873317183983</v>
+        <v>0.5514965099429313</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.680327353239214</v>
+        <v>2.784072860173934</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.52346518653035</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.457651752500501</v>
+        <v>-3.25245480872813</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.140048061216402</v>
+        <v>1.222126838725351</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4519654288071349</v>
+        <v>0.6248746070316679</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.794644443814631</v>
+        <v>2.898389950749351</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.538092922646394</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.555392297125476</v>
+        <v>-3.350195353353104</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.115579579482456</v>
+        <v>1.197658356991405</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.4360761506741547</v>
+        <v>0.6089853288986877</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.799738613050887</v>
+        <v>2.903484119985607</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.536628903471065</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.731730057248405</v>
+        <v>-3.526533113476033</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.043580456257956</v>
+        <v>1.125659233766905</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.2597383905512253</v>
+        <v>0.4326475687757583</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.692471937801801</v>
+        <v>2.796217444736521</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.535120521510994</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.655308010816478</v>
+        <v>-3.450111067044106</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.072640892870655</v>
+        <v>1.154719670379604</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.2597383905512253</v>
+        <v>0.4326475687757583</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.69096355584173</v>
+        <v>2.794709062776449</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.53498338894643</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.610934879177909</v>
+        <v>-3.405737935405538</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.090253012961519</v>
+        <v>1.172331790470468</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.3041115221897939</v>
+        <v>0.4770207004143269</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.717450302260307</v>
+        <v>2.821195809195026</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.529377183085021</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.488100658290742</v>
+        <v>-3.28290371451837</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.133780495454977</v>
+        <v>1.215859272963925</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.3041115221897939</v>
+        <v>0.4770207004143269</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.711844096398897</v>
+        <v>2.815589603333617</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.535758940112825</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.440444927729686</v>
+        <v>-3.235247983957315</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.159224544707204</v>
+        <v>1.241303322216152</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.3517672527508495</v>
+        <v>0.5246764309753826</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.746819291763335</v>
+        <v>2.850564798698055</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.54065131348755</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.339926769230932</v>
+        <v>-3.13472982545856</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.20432418148143</v>
+        <v>1.286402958990379</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.4522854112496041</v>
+        <v>0.6251945894741372</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.812022560237313</v>
+        <v>2.915768067172033</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.527405985963422</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.400593359633321</v>
+        <v>-3.195396415860949</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.166812217796347</v>
+        <v>1.248890995305295</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.3705870945310704</v>
+        <v>0.5434962727556035</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.749758242682065</v>
+        <v>2.853503749616785</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.531503688574051</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.355754958024923</v>
+        <v>-3.150558014252551</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.188845281050335</v>
+        <v>1.270924058559283</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.3751305274759399</v>
+        <v>0.548039705700473</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.756582005059615</v>
+        <v>2.860327511994335</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.535664628205129</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.456513593781921</v>
+        <v>-3.25131665000955</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.152702766378613</v>
+        <v>1.234781543887562</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.2863049587489345</v>
+        <v>0.4592141369734676</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.70744760345449</v>
+        <v>2.81119311038921</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.541544230732966</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.412310756696021</v>
+        <v>-3.207113812923649</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.17626350374081</v>
+        <v>1.258342281249759</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.3305077958348349</v>
+        <v>0.503416974059368</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.739848908233868</v>
+        <v>2.843594415168587</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.539954231202214</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.449289784359464</v>
+        <v>-3.244092840587093</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.159881893144681</v>
+        <v>1.241960670653629</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.3674816976261654</v>
+        <v>0.5403908758506986</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.760443249777913</v>
+        <v>2.864188756712633</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.591201996385253</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.290998366820192</v>
+        <v>-3.08580142304782</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.274446225343429</v>
+        <v>1.356525002852378</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.3674816976261654</v>
+        <v>0.5403908758506986</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.811691014960953</v>
+        <v>2.915436521895673</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.589642700979506</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.083356363185715</v>
+        <v>-2.878159419413344</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.355943731391473</v>
+        <v>1.438022508900421</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.5751237012606416</v>
+        <v>0.7480328794851747</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.934716921735891</v>
+        <v>3.038462428670611</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.584590929217776</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.032324270463187</v>
+        <v>-2.827127326690816</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.371304796718754</v>
+        <v>1.453383574227703</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.6261557939831696</v>
+        <v>0.7990649722077027</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.960284405607678</v>
+        <v>3.064029912542398</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.601778333310481</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.967100089335982</v>
+        <v>-2.76190314556361</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.414581873262341</v>
+        <v>1.49666065077129</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.6913799751103752</v>
+        <v>0.8642891533349083</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.016606318376707</v>
+        <v>3.120351825311427</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.597739305609762</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.929673069264848</v>
+        <v>-2.724476125492477</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.425513653590075</v>
+        <v>1.507592431099024</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.6966315131395568</v>
+        <v>0.86954069136409</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.015718213493496</v>
+        <v>3.119463720428216</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.598996097941002</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.949784725299556</v>
+        <v>-2.744587781527185</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.418725783507432</v>
+        <v>1.500804561016381</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.707658858136976</v>
+        <v>0.8805680363615092</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.023591412823188</v>
+        <v>3.127336919757908</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.759553868962213</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.896039910872351</v>
+        <v>-2.69084296709998</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.600781480299525</v>
+        <v>1.682860257808473</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.717722167577438</v>
+        <v>0.8906313458019711</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.190187169508676</v>
+        <v>3.293932676443396</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.87966677818003</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.872248342266209</v>
+        <v>-2.667051398493838</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.730411016959799</v>
+        <v>1.812489794468748</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.7415137361835803</v>
+        <v>0.9144229144081134</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.324575019890179</v>
+        <v>3.428320526824898</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.871374754193889</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.846164258002401</v>
+        <v>-2.64096731423003</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.732552626679181</v>
+        <v>1.81463140418813</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.7415137361835803</v>
+        <v>0.9144229144081134</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.316282995904038</v>
+        <v>3.420028502838757</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.869567949777668</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.768033077153454</v>
+        <v>-2.562836133381083</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.76199829460254</v>
+        <v>1.844077072111488</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.8156905470672648</v>
+        <v>0.988599725291798</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.358982278018027</v>
+        <v>3.462727784952747</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.88712235550446</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.759140615760171</v>
+        <v>-2.5539436719878</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.783109684886644</v>
+        <v>1.865188462395593</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.8156905470672648</v>
+        <v>0.988599725291798</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.376536683744819</v>
+        <v>3.480282190679539</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.878977402909044</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.927616732730049</v>
+        <v>-2.722419788957678</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.707574285503277</v>
+        <v>1.789653063012225</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.7877427113506841</v>
+        <v>0.9606518895752172</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.351623029719454</v>
+        <v>3.455368536654174</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.860247100096906</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.229817203868466</v>
+        <v>-2.024620260096095</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.967963794235772</v>
+        <v>2.05004257174472</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.7173946519802734</v>
+        <v>0.8903038302048065</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.29068389128507</v>
+        <v>3.39442939821979</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.85091112259381</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.207096100185313</v>
+        <v>-2.001899156412942</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.967716258205938</v>
+        <v>2.049795035714886</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.7173946519802734</v>
+        <v>0.8903038302048065</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.281347913781974</v>
+        <v>3.385093420716694</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.009817248444979</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.205371056895269</v>
+        <v>-2.000174113122898</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.127312401373124</v>
+        <v>2.209391178882073</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.7191196952703172</v>
+        <v>0.8920288734948503</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.44128906560717</v>
+        <v>3.54503457254189</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.046895070938626</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.360152063673524</v>
+        <v>-2.154955119901153</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.102477821155469</v>
+        <v>2.184556598664417</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.685752021215841</v>
+        <v>0.8586611994403741</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.45834628366813</v>
+        <v>3.56209179060285</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.043570426928171</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.308716730288865</v>
+        <v>-2.103519786516494</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.119727310498878</v>
+        <v>2.201806088007826</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7371873546005007</v>
+        <v>0.9100965328250338</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.485882839688472</v>
+        <v>3.589628346623191</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.053576580572912</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.281765505962377</v>
+        <v>-2.076568562190006</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.140513953874215</v>
+        <v>2.222592731383163</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.7520677006282198</v>
+        <v>0.9249768788527529</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.504817200949844</v>
+        <v>3.608562707884564</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.237679712717872</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.417718514018693</v>
+        <v>-2.212521570246321</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.270235882796648</v>
+        <v>2.352314660305596</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.7520677006282198</v>
+        <v>0.9249768788527529</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.688920333094805</v>
+        <v>3.792665840029524</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.229796407620865</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.440126631823565</v>
+        <v>-2.234929688051194</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.253389330577692</v>
+        <v>2.335468108086641</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.7520677006282198</v>
+        <v>0.9249768788527529</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.681037027997798</v>
+        <v>3.784782534932517</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.231850407170503</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.588132399302965</v>
+        <v>-2.382935455530593</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.19624102313557</v>
+        <v>2.278319800644518</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.6653406917646784</v>
+        <v>0.8382498699892115</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.63105482222931</v>
+        <v>3.73480032916403</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.28810412489235</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.597573325191495</v>
+        <v>-2.392376381419123</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.248718370502005</v>
+        <v>2.330797148010953</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.7877678093080698</v>
+        <v>0.9606769875326029</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.760764810477192</v>
+        <v>3.864510317411912</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.290995219437651</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.596286561651938</v>
+        <v>-2.391089617879567</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.252124170463128</v>
+        <v>2.334202947972077</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7890545728476264</v>
+        <v>0.9619637510721595</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.764427963146227</v>
+        <v>3.868173470080947</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.289107032331426</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.59784361564123</v>
+        <v>-2.392646671868858</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.249613161761187</v>
+        <v>2.331691939270136</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7890545728476264</v>
+        <v>0.9619637510721595</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.762539776040002</v>
+        <v>3.866285282974722</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.283927261934288</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.605115501164694</v>
+        <v>-2.399918557392323</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.241524637154663</v>
+        <v>2.323603414663612</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7817826873241616</v>
+        <v>0.9546918655486947</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.752996874328785</v>
+        <v>3.856742381263505</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.282361272144441</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.603274482106443</v>
+        <v>-2.398077538334071</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.240695054988116</v>
+        <v>2.322773832497065</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.78305091399563</v>
+        <v>0.9559600922201631</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.752191820541819</v>
+        <v>3.855937327476539</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.295434679010359</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.610183187606124</v>
+        <v>-2.404986243833752</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.251004979654162</v>
+        <v>2.333083757163111</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.78305091399563</v>
+        <v>0.9559600922201631</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.765265227407737</v>
+        <v>3.869010734342457</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.295434679010359</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.611744830420983</v>
+        <v>-2.406547886648612</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.250380322528219</v>
+        <v>2.332459100037167</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.78305091399563</v>
+        <v>0.9559600922201631</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.765265227407737</v>
+        <v>3.869010734342457</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.293958720137361</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.639645617530456</v>
+        <v>-2.434448673758085</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.237744048811432</v>
+        <v>2.31982282632038</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7484539898526952</v>
+        <v>0.9213631680772283</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.743031114048978</v>
+        <v>3.846776620983698</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.29072316411456</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.64267861504313</v>
+        <v>-2.437481671270759</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.233295293783561</v>
+        <v>2.315374071292509</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7454209923400212</v>
+        <v>0.9183301705645543</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.737975759518573</v>
+        <v>3.841721266453293</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.357429123705064</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.662739936319637</v>
+        <v>-2.457542992547265</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.291976724863462</v>
+        <v>2.37405550237241</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.7253596710635142</v>
+        <v>0.8982688492880473</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.792644926343173</v>
+        <v>3.896390433277892</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.497740842706911</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.919460754314461</v>
+        <v>-2.714263810542089</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.329600116667379</v>
+        <v>2.411678894176328</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.6169450969196993</v>
+        <v>0.7898542751442325</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.86790790085873</v>
+        <v>3.97165340779345</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.566721111852551</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.073447172090602</v>
+        <v>-2.86825022831823</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.336985818702563</v>
+        <v>2.419064596211511</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.6169450969196993</v>
+        <v>0.7898542751442325</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.93688817000437</v>
+        <v>4.04063367693909</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.552772313972671</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.022925268262936</v>
+        <v>-2.817728324490564</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.34324578235375</v>
+        <v>2.425324559862698</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.6169450969196993</v>
+        <v>0.7898542751442325</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.922939372124492</v>
+        <v>4.026684879059212</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.404975429165309</v>
+        <v>3.857169047729485</v>
       </c>
       <c r="C2019" t="n">
         <v>3.564642803028085</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.38561183777219</v>
+        <v>-3.070203478498289</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.210041643605462</v>
+        <v>2.336204987315023</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.6169450969196993</v>
+        <v>0.7898542751442325</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.934809861179906</v>
+        <v>4.038555368114626</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240709.xlsx
+++ b/tame_output/ON/bt/strategyON_20240709.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>47.9%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.0%</t>
+          <t>-71.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.5%</t>
+          <t>110.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.2%</t>
+          <t>124.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-609.8%</t>
+          <t>-644.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.7%</t>
+          <t>-50.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-64.1%</t>
+          <t>-66.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.4%</t>
+          <t>457.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-468.6%</t>
+          <t>-489.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-244.3%</t>
+          <t>-258.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.4%</t>
+          <t>-38.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-257.1%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-142.6%</t>
+          <t>-151.1%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-242.5%</t>
+          <t>-263.7%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-29.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>478.3%</t>
+          <t>79.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-127.1%</t>
+          <t>-118.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-145.0%</t>
+          <t>-152.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>77.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-145.9%</t>
+          <t>-158.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-42.2%</t>
+          <t>-46.8%</t>
         </is>
       </c>
     </row>
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.24806595500523</v>
+        <v>-4.594926232146691</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.424488727714945</v>
+        <v>1.28574461685836</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.1910094890569949</v>
+        <v>-0.4034927703575531</v>
       </c>
       <c r="G1859" t="n">
-        <v>3.009465840596587</v>
+        <v>2.881975871816252</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.482759949137782</v>
+        <v>-4.829620226279244</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.318895905064014</v>
+        <v>1.18015179420743</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.1846732218277398</v>
+        <v>-0.3971565031282979</v>
       </c>
       <c r="G1860" t="n">
-        <v>3.001552375936231</v>
+        <v>2.874062407155896</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.818422596368235</v>
+        <v>-5.165282873509696</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.183211437827798</v>
+        <v>1.044467326971214</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.2526042073166446</v>
+        <v>-0.4650874886172027</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.959374376298853</v>
+        <v>2.831884407518518</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.182048841268548</v>
+        <v>-5.528909118410009</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.044248500101915</v>
+        <v>0.9055043892453303</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.3508258441837704</v>
+        <v>-0.5633091254843285</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.906928954412819</v>
+        <v>2.779438985632484</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.547176223907295</v>
+        <v>-5.894036501048756</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8974520620522473</v>
+        <v>0.7587079511956629</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6471366284827829</v>
+        <v>-0.859619909783341</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.728396998839243</v>
+        <v>2.600907030058909</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.955765001087974</v>
+        <v>-6.302625278229435</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7327780951947349</v>
+        <v>0.5940339843381501</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.055725405663461</v>
+        <v>-1.268208686964019</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.482005276545595</v>
+        <v>2.354515307765261</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.232341101403806</v>
+        <v>-6.579201378545267</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6173330875398624</v>
+        <v>0.478588976683278</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.055725405663461</v>
+        <v>-1.268208686964019</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.477190709017056</v>
+        <v>2.349700740236721</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.648732975690804</v>
+        <v>-6.995593252832265</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.4487703884339407</v>
+        <v>0.3100262775773563</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.055725405663461</v>
+        <v>-1.268208686964019</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.475184759625933</v>
+        <v>2.347694790845599</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.893004376417873</v>
+        <v>-7.239864653559335</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.3613205188117918</v>
+        <v>0.2225764079552075</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.055725405663461</v>
+        <v>-1.268208686964019</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.485443450294612</v>
+        <v>2.357953481514278</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.098255395654633</v>
+        <v>-7.445115672796095</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.2753196762627832</v>
+        <v>0.1365755654061984</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.055725405663461</v>
+        <v>-1.268208686964019</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.481543015440308</v>
+        <v>2.354053046659972</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.261835273839017</v>
+        <v>-7.608695550980478</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2082926450440308</v>
+        <v>0.069548534187446</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.055725405663461</v>
+        <v>-1.268208686964019</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.479947935495308</v>
+        <v>2.352457966714973</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.558496615649214</v>
+        <v>-7.905356892790675</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.09340708424916011</v>
+        <v>-0.04533702660742467</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.12446854139734</v>
+        <v>-1.336951822697898</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.442481029984189</v>
+        <v>2.314991061203854</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.745216323958517</v>
+        <v>-8.092076601099977</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.01469289639103577</v>
+        <v>-0.1240512144655486</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.12446854139734</v>
+        <v>-1.336951822697898</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.438454725449786</v>
+        <v>2.310964756669451</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.128217712701147</v>
+        <v>-8.475077989842609</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.1386097604276006</v>
+        <v>-0.277353871284185</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.12446854139734</v>
+        <v>-1.336951822697898</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.438352624128202</v>
+        <v>2.310862655347867</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.310087503686182</v>
+        <v>-8.656947780827643</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.2087861608501842</v>
+        <v>-0.3475302717067685</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.306338332382375</v>
+        <v>-1.518821613682933</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.331802265508611</v>
+        <v>2.204312296728276</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.669617826190184</v>
+        <v>-9.016478103331645</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.3472479865537346</v>
+        <v>-0.4859920974103193</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.306338332382375</v>
+        <v>-1.518821613682933</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.337152568806661</v>
+        <v>2.209662600026327</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.719966889644406</v>
+        <v>-9.066827166785867</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.3594715919782461</v>
+        <v>-0.4982157028348304</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.356687395836597</v>
+        <v>-1.569170677137155</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.314859150691306</v>
+        <v>2.187369181910971</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.817586167065802</v>
+        <v>-9.164446444207263</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.3954775523250356</v>
+        <v>-0.5342216631816199</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.454306673257994</v>
+        <v>-1.666789954558552</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.259329334860237</v>
+        <v>2.131839366079902</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.965112255071444</v>
+        <v>-9.311972532212906</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.4515944312057205</v>
+        <v>-0.5903385420623048</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.601832761263637</v>
+        <v>-1.814316042564195</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.173707238378423</v>
+        <v>2.046217269598088</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.169370430401308</v>
+        <v>-9.516230707542769</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.5277845042190235</v>
+        <v>-0.6665286150756082</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.729471705877626</v>
+        <v>-1.941954987178184</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.102637068728672</v>
+        <v>1.975147099948336</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.203023268909782</v>
+        <v>-9.549883546051243</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.5367630851379768</v>
+        <v>-0.6755071959945615</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.829885073794663</v>
+        <v>-2.042368355095221</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.046871602462885</v>
+        <v>1.91938163368255</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.129553437242333</v>
+        <v>-9.476413714383794</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.4920034509775761</v>
+        <v>-0.6307475618341609</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.756415242127215</v>
+        <v>-1.968898523427773</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.106325202956776</v>
+        <v>1.978835234176441</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.304677854628876</v>
+        <v>-9.651538131770337</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.547497997184677</v>
+        <v>-0.6862421080412613</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.931539659513759</v>
+        <v>-2.144022940814317</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.015805773272366</v>
+        <v>1.888315804492031</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.539129948643366</v>
+        <v>-9.885990225784827</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.6484979996920686</v>
+        <v>-0.7872421105486533</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.931539659513759</v>
+        <v>-2.144022940814317</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.00858660837077</v>
+        <v>1.881096639590435</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.643504679669812</v>
+        <v>-9.990364956811273</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.6969200828766233</v>
+        <v>-0.8356641937332081</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.035914390540204</v>
+        <v>-2.248397671840763</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.939289578980927</v>
+        <v>1.811799610200591</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.696290835270139</v>
+        <v>-10.0431511124116</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.7169187552781979</v>
+        <v>-0.8556628661347823</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.131589877122601</v>
+        <v>-2.34407315842316</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.883000076870045</v>
+        <v>1.75551010808971</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.822327628638428</v>
+        <v>-10.16918790577989</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.764639743996399</v>
+        <v>-0.9033838548529833</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.106338254312859</v>
+        <v>-2.318821535613417</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.900844779185005</v>
+        <v>1.77335481040467</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.765255856742497</v>
+        <v>-10.11211613388396</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.7378206995516257</v>
+        <v>-0.87656481040821</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.106338254312859</v>
+        <v>-2.318821535613417</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.904835114871406</v>
+        <v>1.777345146091071</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.906927698466617</v>
+        <v>-10.25378797560808</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.7959646631400155</v>
+        <v>-0.9347087739965998</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.106338254312859</v>
+        <v>-2.318821535613417</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.903359887972664</v>
+        <v>1.775869919192329</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.857336854041783</v>
+        <v>-10.20419713118324</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.7610749152052096</v>
+        <v>-0.899819026061794</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.056747409888025</v>
+        <v>-2.269230691188584</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.948167804792436</v>
+        <v>1.820677836012101</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.708418519569927</v>
+        <v>-10.05527879671139</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.7145587150631498</v>
+        <v>-0.8533028259197342</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.025497819152852</v>
+        <v>-2.23798110045341</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.953866425586857</v>
+        <v>1.826376456806522</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.482573366850517</v>
+        <v>-9.829433643991976</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.614641580939177</v>
+        <v>-0.7533856917957609</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.983571143565688</v>
+        <v>-2.196054424866247</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.988601503975364</v>
+        <v>1.861111535195029</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.357994710512925</v>
+        <v>-9.704854987654384</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.5636709738480814</v>
+        <v>-0.7024150847046653</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.983571143565688</v>
+        <v>-2.196054424866247</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.989740648531423</v>
+        <v>1.862250679751088</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.410889998557211</v>
+        <v>-9.757750275698671</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.5821953149036885</v>
+        <v>-0.7209394257602724</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.978615797477242</v>
+        <v>-2.191099078777801</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.995347630346599</v>
+        <v>1.867857661566263</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.33875682326933</v>
+        <v>-9.68561710041079</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.5476083405498997</v>
+        <v>-0.6863524514064832</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.978615797477242</v>
+        <v>-2.191099078777801</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.001081334585235</v>
+        <v>1.8735913658049</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.267390430659683</v>
+        <v>-9.47971056860494</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.5287990458999059</v>
+        <v>-0.6137271010780085</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.907249404867594</v>
+        <v>-1.985192546971951</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.034163907757159</v>
+        <v>1.987398022494544</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.173931396674458</v>
+        <v>-9.386251534619715</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.5012989136187236</v>
+        <v>-0.5862269687968262</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.907249404867594</v>
+        <v>-1.985192546971951</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.024280426444251</v>
+        <v>1.977514541181637</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.906689595806061</v>
+        <v>-9.119009733751318</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3962367537707383</v>
+        <v>-0.4811648089488409</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.907249404867594</v>
+        <v>-1.985192546971951</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.022445865944877</v>
+        <v>1.975679980682263</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.80878255712957</v>
+        <v>-9.021102695074827</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3573742532736026</v>
+        <v>-0.4423023084517057</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.839263655007038</v>
+        <v>-1.917206797111395</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.06293700088775</v>
+        <v>2.016171115625136</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.784829016153612</v>
+        <v>-8.997149154098869</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3471243307377261</v>
+        <v>-0.4320523859158287</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.81531011403108</v>
+        <v>-1.893253256135437</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.077977631618818</v>
+        <v>2.031211746356204</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.520769077830815</v>
+        <v>-8.733089215776072</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2547606715703594</v>
+        <v>-0.3396887267484621</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.551250175708284</v>
+        <v>-1.629193317812641</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.223153278450744</v>
+        <v>2.17638739318813</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.813689454325977</v>
+        <v>-8.026009592271235</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.025284144171275</v>
+        <v>-0.05964391100682809</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.551250175708284</v>
+        <v>-1.629193317812641</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.220366244790443</v>
+        <v>2.173600359527829</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.773505155959787</v>
+        <v>-7.985825293905044</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.04170148740559254</v>
+        <v>-0.04322656777251055</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.511065877342093</v>
+        <v>-1.58900901944645</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.244820447697999</v>
+        <v>2.198054562435385</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.610105285020424</v>
+        <v>-7.822425422965682</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1064282570020945</v>
+        <v>0.02150020182399137</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.347666006402731</v>
+        <v>-1.425609148507088</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.342227191482373</v>
+        <v>2.295461306219759</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.376624062790825</v>
+        <v>-7.588944200736083</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2077451747317864</v>
+        <v>0.1228171195536829</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.114184784173132</v>
+        <v>-1.192127926277489</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.490240353657985</v>
+        <v>2.443474468395371</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.22695767178331</v>
+        <v>-7.439277809728568</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.2647195208218331</v>
+        <v>0.1797914656437301</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.021281292930596</v>
+        <v>-1.099224435034953</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.543090238090547</v>
+        <v>2.496324352827933</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.094682198152424</v>
+        <v>-7.307002336097682</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3129971970212146</v>
+        <v>0.2280691418431116</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.8890058192997095</v>
+        <v>-0.9669489614040665</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.617823009016107</v>
+        <v>2.571057123753492</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.938943865592682</v>
+        <v>-7.15126400353794</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.378107590732748</v>
+        <v>0.2931795355546449</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.7332674867399679</v>
+        <v>-0.8112106288443249</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.714081069239588</v>
+        <v>2.667315183976974</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.689944066909101</v>
+        <v>-6.902264204854359</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4906138514298393</v>
+        <v>0.4056857962517362</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.7332674867399679</v>
+        <v>-0.8112106288443249</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.726987410463247</v>
+        <v>2.680221525200632</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.795534056682206</v>
+        <v>-7.007854194627464</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3204019259213791</v>
+        <v>0.2354738707432755</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.8388574765130723</v>
+        <v>-0.9168006186174293</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.535657487000165</v>
+        <v>2.488891601737551</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.814268958800803</v>
+        <v>-7.02658909674606</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3614523069510263</v>
+        <v>0.2765242517729232</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.8444534861732036</v>
+        <v>-0.9223966282775606</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.580844223081173</v>
+        <v>2.534078337818559</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.666328917393203</v>
+        <v>-6.878649055338461</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3007494008258984</v>
+        <v>0.2158213456477953</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.824132570264646</v>
+        <v>-0.9020757123690031</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.47315784993814</v>
+        <v>2.426391964675526</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.613359395139215</v>
+        <v>-6.825679533084473</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.313223223474016</v>
+        <v>0.2282951682959125</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.7711630480106572</v>
+        <v>-0.8491061901150142</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.496225577037055</v>
+        <v>2.449459691774441</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.569810988368524</v>
+        <v>-6.782131126313782</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.323681974087199</v>
+        <v>0.2387539189090955</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.7711630480106572</v>
+        <v>-0.8491061901150142</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.489264964941962</v>
+        <v>2.442499079679348</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.327662594914666</v>
+        <v>-6.539982732859924</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4350036858498854</v>
+        <v>0.3500756306717818</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.7711630480106572</v>
+        <v>-0.8491061901150142</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.503727319323105</v>
+        <v>2.456961434060491</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.219403457792144</v>
+        <v>-6.431723595737402</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4728394611580891</v>
+        <v>0.3879114059799855</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.7711630480106572</v>
+        <v>-0.8491061901150142</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.4982594397823</v>
+        <v>2.451493554519686</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.096112322975014</v>
+        <v>-6.308432460920272</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5196540090955182</v>
+        <v>0.4347259539174151</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.6478719131935267</v>
+        <v>-0.7258150552978837</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.569732214683155</v>
+        <v>2.522966329420541</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.07496312407157</v>
+        <v>-6.287283262016828</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5358146668942205</v>
+        <v>0.4508866117161174</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.6267227142900833</v>
+        <v>-0.7046658563944403</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.590122712262546</v>
+        <v>2.543356826999932</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.831197682088126</v>
+        <v>-6.043517820033384</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.629101552034649</v>
+        <v>0.5441734968565459</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.6267227142900833</v>
+        <v>-0.7046658563944403</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.585903420609597</v>
+        <v>2.539137535346983</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.729434861810831</v>
+        <v>-5.941754999756089</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6719309940655829</v>
+        <v>0.5870029388874798</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.6135036458976546</v>
+        <v>-0.6914467880020116</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.59595917556507</v>
+        <v>2.549193290302456</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.479584467861756</v>
+        <v>-5.691904605807014</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.764613226628915</v>
+        <v>0.6796851714508119</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.6135036458976546</v>
+        <v>-0.6914467880020116</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.588701250548772</v>
+        <v>2.541935365286158</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.303692375394323</v>
+        <v>-5.516012513339582</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8385691871365371</v>
+        <v>0.7536411319584335</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.6135036458976546</v>
+        <v>-0.6914467880020116</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.592300374069421</v>
+        <v>2.545534488806807</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.13224591237186</v>
+        <v>-5.344566050317119</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.920475278400076</v>
+        <v>0.8355472232219725</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.4420571828751915</v>
+        <v>-0.5200003249795485</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.708495757937453</v>
+        <v>2.661729872674838</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.057956346633521</v>
+        <v>-5.27027648457878</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9492115823117087</v>
+        <v>0.8642835271336051</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.3677676171368522</v>
+        <v>-0.4457107592412092</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.752089974996753</v>
+        <v>2.705324089734139</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.994320604399586</v>
+        <v>-5.206640742344845</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9793606802595998</v>
+        <v>0.894432625081496</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.3041318749029177</v>
+        <v>-0.3820750170072747</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.794966221391431</v>
+        <v>2.748200336128817</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.882893845073666</v>
+        <v>-5.095213983018925</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.005125642773763</v>
+        <v>0.9201975875956601</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.3041318749029177</v>
+        <v>-0.3820750170072747</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.776160480175227</v>
+        <v>2.729394594912613</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.642463348268806</v>
+        <v>-4.854783486214065</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.103040918120585</v>
+        <v>1.018112862942481</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.06370137809805737</v>
+        <v>-0.1416445202024144</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.92216185488302</v>
+        <v>2.875395969620406</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.570220780097611</v>
+        <v>-4.78254091804287</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.135867259223883</v>
+        <v>1.050939204045779</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.06370137809805737</v>
+        <v>-0.1416445202024144</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.926091168717841</v>
+        <v>2.879325283455227</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.517222457816223</v>
+        <v>-4.729542595761482</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.157745172053778</v>
+        <v>1.072817116875675</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.008365119096118534</v>
+        <v>-0.08630826120047558</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.959971508036344</v>
+        <v>2.91320562277373</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.408417572336496</v>
+        <v>-4.620737710281755</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.198265197465662</v>
+        <v>1.113337142287559</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.008365119096118534</v>
+        <v>-0.08630826120047558</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.956969579256338</v>
+        <v>2.910203693993723</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.188396774299486</v>
+        <v>-4.400716912244745</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.287852553691081</v>
+        <v>1.202924498512977</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.1328547259718617</v>
+        <v>0.05491158386750467</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.04328052330774</v>
+        <v>2.996514638045126</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.055529085236208</v>
+        <v>-4.267849223181467</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.356893812118215</v>
+        <v>1.271965756940112</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.1328547259718617</v>
+        <v>0.05491158386750467</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.059174706109563</v>
+        <v>3.012408820846949</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.93535600187171</v>
+        <v>-4.147676139816968</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.406108889904317</v>
+        <v>1.321180834726213</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.2530278093363607</v>
+        <v>0.1750846672320036</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.132424400568564</v>
+        <v>3.08565851530595</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.790683856771972</v>
+        <v>-4.003003994717231</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.474065850505651</v>
+        <v>1.389137795327548</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.3976999544360981</v>
+        <v>0.319756812331741</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.229315790189847</v>
+        <v>3.182549904927233</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.850558684129664</v>
+        <v>-4.062878822074923</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.436153410964</v>
+        <v>1.351225355785897</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.337825127078406</v>
+        <v>0.2598819849740489</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.179428385176657</v>
+        <v>3.132662499914043</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.730738453218827</v>
+        <v>-3.943058591164086</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.499370672562544</v>
+        <v>1.41444261738444</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.337825127078406</v>
+        <v>0.2598819849740489</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.194717554410865</v>
+        <v>3.147951669148251</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.733208159680633</v>
+        <v>-3.945528297625892</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.406026989300263</v>
+        <v>1.321098934122159</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.3353554206165998</v>
+        <v>0.2574122785122427</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.100879929856224</v>
+        <v>3.054114044593609</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.801578346004643</v>
+        <v>-4.013898483949902</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.29794077625596</v>
+        <v>1.213012721077857</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.3446311196528147</v>
+        <v>0.2666879775484577</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.025707210763254</v>
+        <v>2.97894132550064</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.815366398851689</v>
+        <v>-4.027686536796948</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.282862263749033</v>
+        <v>1.197934208570929</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.3446311196528147</v>
+        <v>0.2666879775484577</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.016143919395145</v>
+        <v>2.969378034132531</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.846359558180395</v>
+        <v>-4.058679696125654</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.095174565057938</v>
+        <v>1.010246509879834</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.3446311196528147</v>
+        <v>0.2666879775484577</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.840853484435532</v>
+        <v>2.794087599172918</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.670885298387926</v>
+        <v>-3.883205436333184</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.169931500966713</v>
+        <v>1.08500344578861</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.3446311196528147</v>
+        <v>0.2666879775484577</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.84542071642732</v>
+        <v>2.798654831164705</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.781821551029174</v>
+        <v>-3.994141688974433</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.101299028671421</v>
+        <v>1.016370973493317</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.3446311196528147</v>
+        <v>0.2666879775484577</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.821162745188527</v>
+        <v>2.774396859925913</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.748158005556892</v>
+        <v>-3.960478143502151</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.117895832080239</v>
+        <v>1.032967776902135</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.3782946651250966</v>
+        <v>0.3003515230207395</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.844492257691801</v>
+        <v>2.797726372429187</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.688305386353169</v>
+        <v>-3.900625524298428</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.152009266193861</v>
+        <v>1.067081211015757</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.3782946651250966</v>
+        <v>0.3003515230207395</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.854664644123934</v>
+        <v>2.80789875886132</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.602061923326792</v>
+        <v>-3.814382061272051</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.181452921978272</v>
+        <v>1.096524866800168</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.3782946651250966</v>
+        <v>0.3003515230207395</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.849610914697794</v>
+        <v>2.80284502943518</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.647368742725772</v>
+        <v>-3.859688880671031</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.155105969663206</v>
+        <v>1.070177914485102</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.3374845021158658</v>
+        <v>0.2595413600115087</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.816900592336781</v>
+        <v>2.770134707074167</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.676401847428073</v>
+        <v>-3.888721985373332</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.144044600815386</v>
+        <v>1.059116545637283</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.3374845021158658</v>
+        <v>0.2595413600115087</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.817452465369883</v>
+        <v>2.770686580107268</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.583591365977214</v>
+        <v>-3.795911503922473</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.110441485287096</v>
+        <v>1.025513430108992</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.4302949835667251</v>
+        <v>0.3523518414623681</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.802411446131764</v>
+        <v>2.75564556086915</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.627980835306642</v>
+        <v>-3.8403009732519</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.094559173479926</v>
+        <v>1.009631118301822</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.3859055142372975</v>
+        <v>0.3079623721329404</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.777651240458708</v>
+        <v>2.730885355196094</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.515309617070391</v>
+        <v>-3.72762975501565</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.134703369286149</v>
+        <v>1.049775314108045</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4985767324735477</v>
+        <v>0.4206335903691906</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.840329679912181</v>
+        <v>2.793563794649567</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.402932615887719</v>
+        <v>-3.615252753832978</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.185145465589885</v>
+        <v>1.100217410411781</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4985767324735477</v>
+        <v>0.4206335903691906</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.845820975742849</v>
+        <v>2.799055090480234</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.430713013789072</v>
+        <v>-3.643033151734331</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.185530508197883</v>
+        <v>1.100602453019779</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4707963345721947</v>
+        <v>0.3928531924678376</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.840649938770576</v>
+        <v>2.793884053507962</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.513714294814351</v>
+        <v>-3.72603443275961</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9906857157884246</v>
+        <v>0.905757660610321</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4522254500450209</v>
+        <v>0.3742823079406638</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.667863128054925</v>
+        <v>2.62109724279231</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.622328373257682</v>
+        <v>-3.834648511202941</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.067389745130298</v>
+        <v>0.9824616899521941</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4522254500450209</v>
+        <v>0.3742823079406638</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.788012788774131</v>
+        <v>2.741246903511516</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.586919335009539</v>
+        <v>-3.799239472954798</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.096066386531878</v>
+        <v>1.011138331353774</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4522254500450209</v>
+        <v>0.3742823079406638</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.802525814876454</v>
+        <v>2.755759929613839</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.548535672451388</v>
+        <v>-3.760855810396647</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.108839292897507</v>
+        <v>1.023911237719403</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4906091126031721</v>
+        <v>0.412665970498815</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.822975453753713</v>
+        <v>2.776209568491099</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.371419342416222</v>
+        <v>-3.583739480361481</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.176414853756876</v>
+        <v>1.091486798578772</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4906091126031721</v>
+        <v>0.412665970498815</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.819704482599015</v>
+        <v>2.772938597336401</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.416511587249768</v>
+        <v>-3.628831725195027</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.159061347585371</v>
+        <v>1.074133292407267</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4287130694337823</v>
+        <v>0.3507699273294252</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.783250248459295</v>
+        <v>2.73648436319668</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.237136166011</v>
+        <v>-3.449456303956259</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.224598491387292</v>
+        <v>1.139670436209189</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.585489827604501</v>
+        <v>0.5075466855001438</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.87110327866814</v>
+        <v>2.824337393405526</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.282150379531606</v>
+        <v>-3.494470517476865</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.187400261310639</v>
+        <v>1.102472206132536</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5551409322898964</v>
+        <v>0.4771977901855392</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.833701396810967</v>
+        <v>2.786935511548353</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.549154889804042</v>
+        <v>-3.761475027749301</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.086290019540611</v>
+        <v>1.001361964362507</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3607778942469478</v>
+        <v>0.2828347521425906</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.722775136324143</v>
+        <v>2.676009251061529</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.650352671241214</v>
+        <v>-3.862672809186473</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.045014828862243</v>
+        <v>0.9600867736841396</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2923690807016286</v>
+        <v>0.2144259385972714</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.680933770093453</v>
+        <v>2.634167884830839</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.643841704626902</v>
+        <v>-3.856161842572161</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.045219177062285</v>
+        <v>0.9602911218841814</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2923690807016286</v>
+        <v>0.2144259385972714</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.67853373164777</v>
+        <v>2.631767846385156</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.624803576919605</v>
+        <v>-3.837123714864863</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.049359147353449</v>
+        <v>0.9644310921753452</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2341854693704341</v>
+        <v>0.1562423272660769</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.640148284057299</v>
+        <v>2.593382398794684</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.655930208070223</v>
+        <v>-3.868250346015481</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.214490363831882</v>
+        <v>1.129562308653778</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2341854693704341</v>
+        <v>0.1562423272660769</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.817730152995979</v>
+        <v>2.770964267733365</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.66979696940414</v>
+        <v>-3.882117107349399</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.209776988284449</v>
+        <v>1.124848933106345</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1963275526366111</v>
+        <v>0.118384410532254</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.795848731941819</v>
+        <v>2.749082846679205</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.62499279786421</v>
+        <v>-3.837312935809469</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.233707187297347</v>
+        <v>1.148779132119243</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1963275526366111</v>
+        <v>0.118384410532254</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.801857262338745</v>
+        <v>2.75509137707613</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.582010952033977</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.477249827629208</v>
+        <v>-3.689569965574467</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.190754596668547</v>
+        <v>1.105826541490443</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3641349098714943</v>
+        <v>0.2861917677671371</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.800491897956874</v>
+        <v>2.75372601269426</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.584804573565458</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.579264510160429</v>
+        <v>-3.791584648105688</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.15274234518754</v>
+        <v>1.067814290009436</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3641349098714943</v>
+        <v>0.2861917677671371</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.803285519488355</v>
+        <v>2.756519634225741</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.585466921957117</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.573111804107644</v>
+        <v>-3.785431942052903</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.155865776000312</v>
+        <v>1.070937720822208</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3702876159242786</v>
+        <v>0.2923444738199214</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.807639491511684</v>
+        <v>2.76087360624907</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.584547398697227</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.589921102258146</v>
+        <v>-3.802241240203405</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.148222533480221</v>
+        <v>1.063294478302118</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3534783177737769</v>
+        <v>0.2755351756694198</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.796634389361493</v>
+        <v>2.749868504098879</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.650882952494048</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.527623103482024</v>
+        <v>-3.739943241427283</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.239477286787491</v>
+        <v>1.154549231609387</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3534783177737769</v>
+        <v>0.2755351756694198</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.862969943158314</v>
+        <v>2.8162040578957</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.453174954208175</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.325832905816866</v>
+        <v>-3.538153043762125</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.122485367567681</v>
+        <v>1.037557312389578</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5514965099429313</v>
+        <v>0.4735533678385742</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.784072860173934</v>
+        <v>2.737306974911319</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.52346518653035</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.25245480872813</v>
+        <v>-3.464774946673388</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.222126838725351</v>
+        <v>1.137198783547247</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6248746070316679</v>
+        <v>0.5469314649273107</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.898389950749351</v>
+        <v>2.851624065486737</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.538092922646394</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.350195353353104</v>
+        <v>-3.562515491298363</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.197658356991405</v>
+        <v>1.112730301813301</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6089853288986877</v>
+        <v>0.5310421867943305</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.903484119985607</v>
+        <v>2.856718234722992</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.536628903471065</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.526533113476033</v>
+        <v>-3.738853251421292</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.125659233766905</v>
+        <v>1.040731178588801</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4326475687757583</v>
+        <v>0.3547044266714011</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.796217444736521</v>
+        <v>2.749451559473906</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.535120521510994</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.450111067044106</v>
+        <v>-3.662431204989365</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.154719670379604</v>
+        <v>1.069791615201501</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4326475687757583</v>
+        <v>0.3547044266714011</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.794709062776449</v>
+        <v>2.747943177513835</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.53498338894643</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.405737935405538</v>
+        <v>-3.618058073350797</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.172331790470468</v>
+        <v>1.087403735292364</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4770207004143269</v>
+        <v>0.3990775583099697</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.821195809195026</v>
+        <v>2.774429923932412</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.529377183085021</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.28290371451837</v>
+        <v>-3.495223852463629</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.215859272963925</v>
+        <v>1.130931217785822</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4770207004143269</v>
+        <v>0.3990775583099697</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.815589603333617</v>
+        <v>2.768823718071003</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.535758940112825</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.235247983957315</v>
+        <v>-3.447568121902574</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.241303322216152</v>
+        <v>1.156375267038048</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5246764309753826</v>
+        <v>0.4467332888710253</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.850564798698055</v>
+        <v>2.803798913435441</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.54065131348755</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.13472982545856</v>
+        <v>-3.347049963403819</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.286402958990379</v>
+        <v>1.201474903812275</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6251945894741372</v>
+        <v>0.5472514473697798</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.915768067172033</v>
+        <v>2.869002181909418</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.527405985963422</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.195396415860949</v>
+        <v>-3.407716553806208</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.248890995305295</v>
+        <v>1.163962940127192</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5434962727556035</v>
+        <v>0.4655531306512461</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.853503749616785</v>
+        <v>2.80673786435417</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.531503688574051</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.150558014252551</v>
+        <v>-3.36287815219781</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.270924058559283</v>
+        <v>1.18599600338118</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.548039705700473</v>
+        <v>0.4700965635961156</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.860327511994335</v>
+        <v>2.813561626731721</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.535664628205129</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.25131665000955</v>
+        <v>-3.463636787954809</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.234781543887562</v>
+        <v>1.149853488709458</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.4592141369734676</v>
+        <v>0.3812709948691102</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.81119311038921</v>
+        <v>2.764427225126595</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.541544230732966</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.207113812923649</v>
+        <v>-3.419433950868908</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.258342281249759</v>
+        <v>1.173414226071656</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.503416974059368</v>
+        <v>0.4254738319550107</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.843594415168587</v>
+        <v>2.796828529905973</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.539954231202214</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.244092840587093</v>
+        <v>-3.456412978532351</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.241960670653629</v>
+        <v>1.157032615475526</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5403908758506986</v>
+        <v>0.4624477337463412</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.864188756712633</v>
+        <v>2.817422871450018</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.591201996385253</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.08580142304782</v>
+        <v>-3.298121560993079</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.356525002852378</v>
+        <v>1.271596947674274</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5403908758506986</v>
+        <v>0.4624477337463412</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.915436521895673</v>
+        <v>2.868670636633058</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.589642700979506</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.878159419413344</v>
+        <v>-3.090479557358603</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.438022508900421</v>
+        <v>1.353094453722318</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.7480328794851747</v>
+        <v>0.6700897373808173</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.038462428670611</v>
+        <v>2.991696543407997</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.584590929217776</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.827127326690816</v>
+        <v>-3.039447464636075</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.453383574227703</v>
+        <v>1.368455519049599</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7990649722077027</v>
+        <v>0.7211218301033453</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.064029912542398</v>
+        <v>3.017264027279784</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.601778333310481</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.76190314556361</v>
+        <v>-2.974223283508869</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.49666065077129</v>
+        <v>1.411732595593187</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.8642891533349083</v>
+        <v>0.7863460112305509</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.120351825311427</v>
+        <v>3.073585940048812</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.597739305609762</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.724476125492477</v>
+        <v>-2.936796263437735</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.507592431099024</v>
+        <v>1.42266437592092</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.86954069136409</v>
+        <v>0.7915975492597326</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.119463720428216</v>
+        <v>3.072697835165601</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.598996097941002</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.744587781527185</v>
+        <v>-2.956907919472444</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.500804561016381</v>
+        <v>1.415876505838277</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.8805680363615092</v>
+        <v>0.8026248942571518</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.127336919757908</v>
+        <v>3.080571034495293</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.759553868962213</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.69084296709998</v>
+        <v>-2.903163105045239</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.682860257808473</v>
+        <v>1.59793220263037</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8906313458019711</v>
+        <v>0.8126882036976137</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.293932676443396</v>
+        <v>3.247166791180781</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.87966677818003</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.667051398493838</v>
+        <v>-2.879371536439097</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.812489794468748</v>
+        <v>1.727561739290644</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9144229144081134</v>
+        <v>0.836479772303756</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.428320526824898</v>
+        <v>3.381554641562284</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.871374754193889</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.64096731423003</v>
+        <v>-2.853287452175289</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.81463140418813</v>
+        <v>1.729703349010026</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9144229144081134</v>
+        <v>0.836479772303756</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.420028502838757</v>
+        <v>3.373262617576143</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.869567949777668</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.562836133381083</v>
+        <v>-2.775156271326342</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.844077072111488</v>
+        <v>1.759149016933385</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.988599725291798</v>
+        <v>0.9106565831874406</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.462727784952747</v>
+        <v>3.415961899690133</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.88712235550446</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.5539436719878</v>
+        <v>-2.766263809933059</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.865188462395593</v>
+        <v>1.780260407217489</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.988599725291798</v>
+        <v>0.9106565831874406</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.480282190679539</v>
+        <v>3.433516305416925</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.878977402909044</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.722419788957678</v>
+        <v>-2.934739926902937</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.789653063012225</v>
+        <v>1.704725007834122</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.9606518895752172</v>
+        <v>0.8827087474708598</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.455368536654174</v>
+        <v>3.40860265139156</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.860247100096906</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.024620260096095</v>
+        <v>-2.236940398041353</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.05004257174472</v>
+        <v>1.965114516566617</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.8903038302048065</v>
+        <v>0.812360688100449</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.39442939821979</v>
+        <v>3.347663512957175</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.85091112259381</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.001899156412942</v>
+        <v>-2.214219294358201</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.049795035714886</v>
+        <v>1.964866980536783</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.8903038302048065</v>
+        <v>0.812360688100449</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.385093420716694</v>
+        <v>3.33832753545408</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.009817248444979</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.000174113122898</v>
+        <v>-2.212494251068157</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.209391178882073</v>
+        <v>2.124463123703969</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8920288734948503</v>
+        <v>0.8140857313904928</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.54503457254189</v>
+        <v>3.498268687279275</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.046895070938626</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.154955119901153</v>
+        <v>-2.367275257846412</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.184556598664417</v>
+        <v>2.099628543486314</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.8586611994403741</v>
+        <v>0.7807180573360166</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.56209179060285</v>
+        <v>3.515325905340236</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.043570426928171</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.103519786516494</v>
+        <v>-2.315839924461752</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.201806088007826</v>
+        <v>2.116878032829723</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9100965328250338</v>
+        <v>0.8321533907206763</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.589628346623191</v>
+        <v>3.542862461360577</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.053576580572912</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.076568562190006</v>
+        <v>-2.288888700135264</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.222592731383163</v>
+        <v>2.13766467620506</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9249768788527529</v>
+        <v>0.8470337367483954</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.608562707884564</v>
+        <v>3.56179682262195</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.237679712717872</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.212521570246321</v>
+        <v>-2.424841708191581</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.352314660305596</v>
+        <v>2.267386605127493</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9249768788527529</v>
+        <v>0.8470337367483954</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.792665840029524</v>
+        <v>3.74589995476691</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.229796407620865</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.234929688051194</v>
+        <v>-2.447249825996453</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.335468108086641</v>
+        <v>2.250540052908537</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9249768788527529</v>
+        <v>0.8470337367483954</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.784782534932517</v>
+        <v>3.738016649669903</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.231850407170503</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.382935455530593</v>
+        <v>-2.595255593475852</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.278319800644518</v>
+        <v>2.193391745466415</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.8382498699892115</v>
+        <v>0.760306727884854</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.73480032916403</v>
+        <v>3.688034443901415</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.28810412489235</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.392376381419123</v>
+        <v>-2.604696519364382</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.330797148010953</v>
+        <v>2.24586909283285</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.9606769875326029</v>
+        <v>0.8827338454282454</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.864510317411912</v>
+        <v>3.817744432149297</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.290995219437651</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.391089617879567</v>
+        <v>-2.603409755824826</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.334202947972077</v>
+        <v>2.249274892793973</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9619637510721595</v>
+        <v>0.884020608967802</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.868173470080947</v>
+        <v>3.821407584818332</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.289107032331426</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.392646671868858</v>
+        <v>-2.604966809814117</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.331691939270136</v>
+        <v>2.246763884092032</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9619637510721595</v>
+        <v>0.884020608967802</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.866285282974722</v>
+        <v>3.819519397712107</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.283927261934288</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.399918557392323</v>
+        <v>-2.612238695337582</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.323603414663612</v>
+        <v>2.238675359485509</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9546918655486947</v>
+        <v>0.8767487234443372</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.856742381263505</v>
+        <v>3.809976496000891</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.282361272144441</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.398077538334071</v>
+        <v>-2.610397676279331</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.322773832497065</v>
+        <v>2.237845777318961</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9559600922201631</v>
+        <v>0.8780169501158056</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.855937327476539</v>
+        <v>3.809171442213924</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.295434679010359</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.404986243833752</v>
+        <v>-2.617306381779011</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.333083757163111</v>
+        <v>2.248155701985008</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9559600922201631</v>
+        <v>0.8780169501158056</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.869010734342457</v>
+        <v>3.822244849079843</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.295434679010359</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.406547886648612</v>
+        <v>-2.618868024593871</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.332459100037167</v>
+        <v>2.247531044859064</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9559600922201631</v>
+        <v>0.8780169501158056</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.869010734342457</v>
+        <v>3.822244849079843</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.293958720137361</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.434448673758085</v>
+        <v>-2.646768811703344</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.31982282632038</v>
+        <v>2.234894771142276</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9213631680772283</v>
+        <v>0.8434200259728708</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.846776620983698</v>
+        <v>3.800010735721084</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.29072316411456</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.437481671270759</v>
+        <v>-2.649801809216018</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.315374071292509</v>
+        <v>2.230446016114406</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9183301705645543</v>
+        <v>0.8403870284601969</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.841721266453293</v>
+        <v>3.794955381190678</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.357429123705064</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.457542992547265</v>
+        <v>-2.669863130492525</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.37405550237241</v>
+        <v>2.289127447194307</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.8982688492880473</v>
+        <v>0.8203257071836898</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.896390433277892</v>
+        <v>3.849624548015278</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.497740842706911</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.714263810542089</v>
+        <v>-2.926583948487349</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.411678894176328</v>
+        <v>2.326750838998224</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.7898542751442325</v>
+        <v>0.711911133039875</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.97165340779345</v>
+        <v>3.924887522530836</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.566721111852551</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.86825022831823</v>
+        <v>-3.080570366263489</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.419064596211511</v>
+        <v>2.334136541033407</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.7898542751442325</v>
+        <v>0.711911133039875</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.04063367693909</v>
+        <v>3.993867791676476</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.552772313972671</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.817728324490564</v>
+        <v>-3.030048462435823</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.425324559862698</v>
+        <v>2.340396504684595</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.7898542751442325</v>
+        <v>0.711911133039875</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.026684879059212</v>
+        <v>3.979918993796597</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.857169047729485</v>
+        <v>3.7599301064677</v>
       </c>
       <c r="C2019" t="n">
         <v>3.564642803028085</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.070203478498289</v>
+        <v>-3.282523616443548</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.336204987315023</v>
+        <v>2.251276932136919</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.7898542751442325</v>
+        <v>0.711911133039875</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.038555368114626</v>
+        <v>3.991789482852011</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240709.xlsx
+++ b/tame_output/ON/bt/strategyON_20240709.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>12.7%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-40.2%</t>
+          <t>-29.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,17 +864,17 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>44.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.9%</t>
+          <t>-71.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.3%</t>
+          <t>110.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.0%</t>
+          <t>123.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.6%</t>
+          <t>-66.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.3%</t>
+          <t>453.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-489.8%</t>
+          <t>-479.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-14.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-151.1%</t>
+          <t>-136.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-118.1%</t>
+          <t>-121.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-152.8%</t>
+          <t>-142.2%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>77.2%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-46.8%</t>
+          <t>-90.4%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2019"/>
+  <dimension ref="A1:G2020"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.80082935409724</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017768</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.634074812643843</v>
+        <v>2.737275035876832</v>
       </c>
       <c r="D1938" t="n">
         <v>-4.058679696125654</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.010246509879834</v>
+        <v>1.113446733112823</v>
       </c>
       <c r="F1938" t="n">
         <v>0.2666879775484577</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.794087599172918</v>
+        <v>2.897287822405907</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.638642044635631</v>
+        <v>2.74184226786862</v>
       </c>
       <c r="D1939" t="n">
         <v>-3.883205436333184</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.08500344578861</v>
+        <v>1.188203669021599</v>
       </c>
       <c r="F1939" t="n">
         <v>0.2666879775484577</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.798654831164705</v>
+        <v>2.901855054397695</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.614384073396838</v>
+        <v>2.717584296629827</v>
       </c>
       <c r="D1940" t="n">
         <v>-3.994141688974433</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.016370973493317</v>
+        <v>1.119571196726306</v>
       </c>
       <c r="F1940" t="n">
         <v>0.2666879775484577</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.774396859925913</v>
+        <v>2.877597083158902</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.617515458616743</v>
+        <v>2.720715681849732</v>
       </c>
       <c r="D1941" t="n">
         <v>-3.960478143502151</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.032967776902135</v>
+        <v>1.136168000135125</v>
       </c>
       <c r="F1941" t="n">
         <v>0.3003515230207395</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.797726372429187</v>
+        <v>2.900926595662177</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.627687845048876</v>
+        <v>2.730888068281865</v>
       </c>
       <c r="D1942" t="n">
         <v>-3.900625524298428</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.067081211015757</v>
+        <v>1.170281434248746</v>
       </c>
       <c r="F1942" t="n">
         <v>0.3003515230207395</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.80789875886132</v>
+        <v>2.911098982094309</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.622634115622736</v>
+        <v>2.725834338855725</v>
       </c>
       <c r="D1943" t="n">
         <v>-3.814382061272051</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.096524866800168</v>
+        <v>1.199725090033158</v>
       </c>
       <c r="F1943" t="n">
         <v>0.3003515230207395</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.80284502943518</v>
+        <v>2.906045252668169</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.614409891067262</v>
+        <v>2.717610114300251</v>
       </c>
       <c r="D1944" t="n">
         <v>-3.859688880671031</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.070177914485102</v>
+        <v>1.173378137718091</v>
       </c>
       <c r="F1944" t="n">
         <v>0.2595413600115087</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.770134707074167</v>
+        <v>2.873334930307156</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.614961764100363</v>
+        <v>2.718161987333352</v>
       </c>
       <c r="D1945" t="n">
         <v>-3.888721985373332</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.059116545637283</v>
+        <v>1.162316768870272</v>
       </c>
       <c r="F1945" t="n">
         <v>0.2595413600115087</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.770686580107268</v>
+        <v>2.873886803340258</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.544234455991729</v>
+        <v>2.647434679224718</v>
       </c>
       <c r="D1946" t="n">
         <v>-3.795911503922473</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.025513430108992</v>
+        <v>1.128713653341981</v>
       </c>
       <c r="F1946" t="n">
         <v>0.3523518414623681</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.75564556086915</v>
+        <v>2.858845784102139</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.54610793191633</v>
+        <v>2.649308155149319</v>
       </c>
       <c r="D1947" t="n">
         <v>-3.8403009732519</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.009631118301822</v>
+        <v>1.112831341534811</v>
       </c>
       <c r="F1947" t="n">
         <v>0.3079623721329404</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.730885355196094</v>
+        <v>2.834085578429083</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.541183640428053</v>
+        <v>2.644383863661042</v>
       </c>
       <c r="D1948" t="n">
         <v>-3.72762975501565</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.049775314108045</v>
+        <v>1.152975537341034</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4206335903691906</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.793563794649567</v>
+        <v>2.896764017882556</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.54667493625872</v>
+        <v>2.649875159491709</v>
       </c>
       <c r="D1949" t="n">
         <v>-3.615252753832978</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.100217410411781</v>
+        <v>1.203417633644771</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4206335903691906</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.799055090480234</v>
+        <v>2.902255313713224</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.558172138027259</v>
+        <v>2.661372361260248</v>
       </c>
       <c r="D1950" t="n">
         <v>-3.643033151734331</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.100602453019779</v>
+        <v>1.203802676252768</v>
       </c>
       <c r="F1950" t="n">
         <v>0.3928531924678376</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.793884053507962</v>
+        <v>2.897084276740951</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.396527858027912</v>
+        <v>2.499728081260901</v>
       </c>
       <c r="D1951" t="n">
         <v>-3.72603443275961</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.905757660610321</v>
+        <v>1.00895788384331</v>
       </c>
       <c r="F1951" t="n">
         <v>0.3742823079406638</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.62109724279231</v>
+        <v>2.7242974660253</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.516677518747118</v>
+        <v>2.619877741980107</v>
       </c>
       <c r="D1952" t="n">
         <v>-3.834648511202941</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9824616899521941</v>
+        <v>1.085661913185183</v>
       </c>
       <c r="F1952" t="n">
         <v>0.3742823079406638</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.741246903511516</v>
+        <v>2.844447126744505</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.531190544849441</v>
+        <v>2.63439076808243</v>
       </c>
       <c r="D1953" t="n">
         <v>-3.799239472954798</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.011138331353774</v>
+        <v>1.114338554586763</v>
       </c>
       <c r="F1953" t="n">
         <v>0.3742823079406638</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.755759929613839</v>
+        <v>2.858960152846828</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.528609986191809</v>
+        <v>2.631810209424799</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.760855810396647</v>
+        <v>-3.654822127655307</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.023911237719403</v>
+        <v>1.169524934048928</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.412665970498815</v>
+        <v>0.5186996532401547</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.776209568491099</v>
+        <v>2.943030001368891</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.525339015037112</v>
+        <v>2.6285392382701</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.583739480361481</v>
+        <v>-3.477705797620141</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.091486798578772</v>
+        <v>1.237100494908297</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.412665970498815</v>
+        <v>0.5186996532401547</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.772938597336401</v>
+        <v>2.939759030214193</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.526022406799025</v>
+        <v>2.629222630032014</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.628831725195027</v>
+        <v>-3.522798042453687</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.074133292407267</v>
+        <v>1.219746988736792</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3507699273294252</v>
+        <v>0.4568036100707649</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.73648436319668</v>
+        <v>2.903304796074473</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.519809382105439</v>
+        <v>2.623009605338428</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.449456303956259</v>
+        <v>-3.343422621214919</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.139670436209189</v>
+        <v>1.285284132538713</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5075466855001438</v>
+        <v>0.6135803682414835</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.824337393405526</v>
+        <v>2.991157826283318</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.500616837437029</v>
+        <v>2.603817060670018</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.494470517476865</v>
+        <v>-3.388436834735525</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.102472206132536</v>
+        <v>1.24808590246206</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4771977901855392</v>
+        <v>0.5832314729268789</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.786935511548353</v>
+        <v>2.953755944426145</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.506308399775975</v>
+        <v>2.609508623008963</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.761475027749301</v>
+        <v>-3.655441345007961</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.001361964362507</v>
+        <v>1.146975660692032</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2828347521425906</v>
+        <v>0.3888684348839304</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.676009251061529</v>
+        <v>2.842829683939322</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.505512321672476</v>
+        <v>2.608712544905465</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.862672809186473</v>
+        <v>-3.756639126445133</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9600867736841396</v>
+        <v>1.105700470013664</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2144259385972714</v>
+        <v>0.3204596213386112</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.634167884830839</v>
+        <v>2.800988317708632</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.503112283226793</v>
+        <v>2.606312506459782</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.856161842572161</v>
+        <v>-3.750128159830821</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9602911218841814</v>
+        <v>1.105904818213706</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2144259385972714</v>
+        <v>0.3204596213386112</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.631767846385156</v>
+        <v>2.798588279262948</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.499637002435038</v>
+        <v>2.602837225668027</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.837123714864863</v>
+        <v>-3.731090032123523</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9644310921753452</v>
+        <v>1.11004478850487</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1562423272660769</v>
+        <v>0.2622760100074166</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.593382398794684</v>
+        <v>2.760202831672477</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.677218871373718</v>
+        <v>2.780419094606707</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.868250346015481</v>
+        <v>-3.762216663274141</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.129562308653778</v>
+        <v>1.275176004983303</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1562423272660769</v>
+        <v>0.2622760100074166</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.770964267733365</v>
+        <v>2.937784700611157</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.678052200359852</v>
+        <v>2.781252423592841</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.882117107349399</v>
+        <v>-3.776083424608059</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.124848933106345</v>
+        <v>1.27046262943587</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.118384410532254</v>
+        <v>0.2244180932735937</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.749082846679205</v>
+        <v>2.915903279556997</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.684060730756778</v>
+        <v>2.787260953989767</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.837312935809469</v>
+        <v>-3.731279253068129</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.148779132119243</v>
+        <v>1.294392828448768</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.118384410532254</v>
+        <v>0.2244180932735937</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.75509137707613</v>
+        <v>2.921911809953923</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.78150125051991</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.582010952033977</v>
+        <v>2.685211175266966</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.689569965574467</v>
+        <v>-3.583536282833127</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.105826541490443</v>
+        <v>1.251440237819968</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2861917677671371</v>
+        <v>0.3922254505084768</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.75372601269426</v>
+        <v>2.920546445572052</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.584804573565458</v>
+        <v>2.688004796798447</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.791584648105688</v>
+        <v>-3.685550965364348</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.067814290009436</v>
+        <v>1.213427986338961</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2861917677671371</v>
+        <v>0.3922254505084768</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.756519634225741</v>
+        <v>2.923340067103533</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.585466921957117</v>
+        <v>2.688667145190105</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.785431942052903</v>
+        <v>-3.679398259311563</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.070937720822208</v>
+        <v>1.216551417151733</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2923444738199214</v>
+        <v>0.3983781565612611</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.76087360624907</v>
+        <v>2.927694039126862</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.584547398697227</v>
+        <v>2.687747621930216</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.802241240203405</v>
+        <v>-3.696207557462065</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.063294478302118</v>
+        <v>1.208908174631643</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2755351756694198</v>
+        <v>0.3815688584107595</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.749868504098879</v>
+        <v>2.916688936976672</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.650882952494048</v>
+        <v>2.754083175727037</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.739943241427283</v>
+        <v>-3.633909558685943</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.154549231609387</v>
+        <v>1.300162927938912</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2755351756694198</v>
+        <v>0.3815688584107595</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.8162040578957</v>
+        <v>2.983024490773492</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.453174954208175</v>
+        <v>2.556375177441164</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.538153043762125</v>
+        <v>-3.432119361020785</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.037557312389578</v>
+        <v>1.183171008719102</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4735533678385742</v>
+        <v>0.5795870505799139</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.737306974911319</v>
+        <v>2.904127407789112</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.52346518653035</v>
+        <v>2.626665409763339</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.464774946673388</v>
+        <v>-3.358741263932048</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.137198783547247</v>
+        <v>1.282812479876772</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5469314649273107</v>
+        <v>0.6529651476686504</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.851624065486737</v>
+        <v>3.018444498364529</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.538092922646394</v>
+        <v>2.641293145879382</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.562515491298363</v>
+        <v>-3.456481808557023</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.112730301813301</v>
+        <v>1.258343998142826</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5310421867943305</v>
+        <v>0.6370758695356702</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.856718234722992</v>
+        <v>3.023538667600785</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.536628903471065</v>
+        <v>2.639829126704054</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.738853251421292</v>
+        <v>-3.632819568679952</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.040731178588801</v>
+        <v>1.186344874918326</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3547044266714011</v>
+        <v>0.4607381094127408</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.749451559473906</v>
+        <v>2.916271992351699</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.535120521510994</v>
+        <v>2.638320744743983</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.662431204989365</v>
+        <v>-3.556397522248025</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.069791615201501</v>
+        <v>1.215405311531025</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3547044266714011</v>
+        <v>0.4607381094127408</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.747943177513835</v>
+        <v>2.914763610391628</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.53498338894643</v>
+        <v>2.638183612179419</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.618058073350797</v>
+        <v>-3.512024390609457</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.087403735292364</v>
+        <v>1.233017431621889</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.3990775583099697</v>
+        <v>0.5051112410513094</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.774429923932412</v>
+        <v>2.941250356810205</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.529377183085021</v>
+        <v>2.632577406318009</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.495223852463629</v>
+        <v>-3.389190169722289</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.130931217785822</v>
+        <v>1.276544914115346</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.3990775583099697</v>
+        <v>0.5051112410513094</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.768823718071003</v>
+        <v>2.935644150948795</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.535758940112825</v>
+        <v>2.638959163345814</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.447568121902574</v>
+        <v>-3.341534439161234</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.156375267038048</v>
+        <v>1.301988963367573</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4467332888710253</v>
+        <v>0.5527669716123651</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.803798913435441</v>
+        <v>2.970619346313233</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.54065131348755</v>
+        <v>2.643851536720539</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.347049963403819</v>
+        <v>-3.241016280662479</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.201474903812275</v>
+        <v>1.3470886001418</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5472514473697798</v>
+        <v>0.6532851301111197</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.869002181909418</v>
+        <v>3.035822614787211</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.82880887755729</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.527405985963422</v>
+        <v>2.630606209196411</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.407716553806208</v>
+        <v>-3.301682871064868</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.163962940127192</v>
+        <v>1.309576636456717</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.4655531306512461</v>
+        <v>0.571586813392586</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.80673786435417</v>
+        <v>2.973558297231963</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.531503688574051</v>
+        <v>2.63470391180704</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.36287815219781</v>
+        <v>-3.25684446945647</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.18599600338118</v>
+        <v>1.331609699710704</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4700965635961156</v>
+        <v>0.5761302463374555</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.813561626731721</v>
+        <v>2.980382059609513</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.81793235491705</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.535664628205129</v>
+        <v>2.638864851438118</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.463636787954809</v>
+        <v>-3.357603105213469</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.149853488709458</v>
+        <v>1.295467185038983</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.3812709948691102</v>
+        <v>0.48730467761045</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.764427225126595</v>
+        <v>2.931247658004388</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.541544230732966</v>
+        <v>2.644744453965955</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.419433950868908</v>
+        <v>-3.313400268127568</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.173414226071656</v>
+        <v>1.31902792240118</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4254738319550107</v>
+        <v>0.5315075146963505</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.796828529905973</v>
+        <v>2.963648962783765</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.539954231202214</v>
+        <v>2.643154454435202</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.456412978532351</v>
+        <v>-3.350379295791011</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.157032615475526</v>
+        <v>1.30264631180505</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.4624477337463412</v>
+        <v>0.568481416487681</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.817422871450018</v>
+        <v>2.984243304327811</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.591201996385253</v>
+        <v>2.694402219618242</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.298121560993079</v>
+        <v>-3.192087878251739</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.271596947674274</v>
+        <v>1.417210644003799</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.4624477337463412</v>
+        <v>0.568481416487681</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.868670636633058</v>
+        <v>3.035491069510851</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321018</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.589642700979506</v>
+        <v>2.692842924212495</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.090479557358603</v>
+        <v>-2.984445874617263</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.353094453722318</v>
+        <v>1.498708150051843</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.6700897373808173</v>
+        <v>0.7761234201221572</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.991696543407997</v>
+        <v>3.15851697628579</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.584590929217776</v>
+        <v>2.687791152450765</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.039447464636075</v>
+        <v>-2.933413781894735</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.368455519049599</v>
+        <v>1.514069215379124</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7211218301033453</v>
+        <v>0.8271555128446851</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.017264027279784</v>
+        <v>3.184084460157576</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.601778333310481</v>
+        <v>2.70497855654347</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.974223283508869</v>
+        <v>-2.868189600767529</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.411732595593187</v>
+        <v>1.557346291922711</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.7863460112305509</v>
+        <v>0.8923796939718908</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.073585940048812</v>
+        <v>3.240406372926605</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.597739305609762</v>
+        <v>2.70093952884275</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.936796263437735</v>
+        <v>-2.830762580696395</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.42266437592092</v>
+        <v>1.568278072250445</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.7915975492597326</v>
+        <v>0.8976312320010724</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.072697835165601</v>
+        <v>3.239518268043394</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.598996097941002</v>
+        <v>2.702196321173991</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.956907919472444</v>
+        <v>-2.850874236731104</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.415876505838277</v>
+        <v>1.561490202167802</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.8026248942571518</v>
+        <v>0.9086585769984916</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.080571034495293</v>
+        <v>3.247391467373086</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.759553868962213</v>
+        <v>2.862754092195201</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.903163105045239</v>
+        <v>-2.797129422303899</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.59793220263037</v>
+        <v>1.743545898959895</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8126882036976137</v>
+        <v>0.9187218864389536</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.247166791180781</v>
+        <v>3.413987224058574</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957621</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.87966677818003</v>
+        <v>2.982867001413019</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.879371536439097</v>
+        <v>-2.773337853697757</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.727561739290644</v>
+        <v>1.873175435620169</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.836479772303756</v>
+        <v>0.9425134550450959</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.381554641562284</v>
+        <v>3.548375074440076</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.871374754193889</v>
+        <v>2.974574977426878</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.853287452175289</v>
+        <v>-2.747253769433949</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.729703349010026</v>
+        <v>1.875317045339551</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.836479772303756</v>
+        <v>0.9425134550450959</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.373262617576143</v>
+        <v>3.540083050453935</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896924</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.869567949777668</v>
+        <v>2.972768173010657</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.775156271326342</v>
+        <v>-2.669122588585002</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.759149016933385</v>
+        <v>1.904762713262909</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.9106565831874406</v>
+        <v>1.01669026592878</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.415961899690133</v>
+        <v>3.582782332567926</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959853</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.88712235550446</v>
+        <v>2.990322578737449</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.766263809933059</v>
+        <v>-2.660230127191719</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.780260407217489</v>
+        <v>1.925874103547014</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.9106565831874406</v>
+        <v>1.01669026592878</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.433516305416925</v>
+        <v>3.600336738294717</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.878977402909044</v>
+        <v>2.982177626142033</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.934739926902937</v>
+        <v>-2.828706244161597</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.704725007834122</v>
+        <v>1.850338704163647</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.8827087474708598</v>
+        <v>0.9887424302121997</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.40860265139156</v>
+        <v>3.575423084269353</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782703</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.860247100096906</v>
+        <v>2.963447323329894</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.236940398041353</v>
+        <v>-2.130906715300013</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.965114516566617</v>
+        <v>2.110728212896142</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.812360688100449</v>
+        <v>0.918394370841789</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.347663512957175</v>
+        <v>3.514483945834968</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632631</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.85091112259381</v>
+        <v>2.954111345826799</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.214219294358201</v>
+        <v>-2.108185611616861</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.964866980536783</v>
+        <v>2.110480676866307</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.812360688100449</v>
+        <v>0.918394370841789</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.33832753545408</v>
+        <v>3.505147968331872</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.009817248444979</v>
+        <v>3.113017471677968</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.212494251068157</v>
+        <v>-2.106460568326817</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.124463123703969</v>
+        <v>2.270076820033494</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8140857313904928</v>
+        <v>0.9201194141318327</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.498268687279275</v>
+        <v>3.665089120157068</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.046895070938626</v>
+        <v>3.150095294171614</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.367275257846412</v>
+        <v>-2.261241575105072</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.099628543486314</v>
+        <v>2.245242239815838</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7807180573360166</v>
+        <v>0.8867517400773566</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.515325905340236</v>
+        <v>3.682146338218029</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.043570426928171</v>
+        <v>3.14677065016116</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.315839924461752</v>
+        <v>-2.209806241720413</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.116878032829723</v>
+        <v>2.262491729159247</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.8321533907206763</v>
+        <v>0.9381870734620162</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.542862461360577</v>
+        <v>3.709682894238369</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.053576580572912</v>
+        <v>3.156776803805901</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.288888700135264</v>
+        <v>-2.182855017393925</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.13766467620506</v>
+        <v>2.283278372534584</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.8470337367483954</v>
+        <v>0.9530674194897354</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.56179682262195</v>
+        <v>3.728617255499743</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784103</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.237679712717872</v>
+        <v>3.340879935950861</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.424841708191581</v>
+        <v>-2.318808025450241</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.267386605127493</v>
+        <v>2.413000301457017</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.8470337367483954</v>
+        <v>0.9530674194897354</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.74589995476691</v>
+        <v>3.912720387644702</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.229796407620865</v>
+        <v>3.332996630853854</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.447249825996453</v>
+        <v>-2.341216143255113</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.250540052908537</v>
+        <v>2.396153749238062</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.8470337367483954</v>
+        <v>0.9530674194897354</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.738016649669903</v>
+        <v>3.904837082547695</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.231850407170503</v>
+        <v>3.335050630403491</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.595255593475852</v>
+        <v>-2.489221910734512</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.193391745466415</v>
+        <v>2.339005441795939</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.760306727884854</v>
+        <v>0.8663404106261939</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.688034443901415</v>
+        <v>3.854854876779208</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161973</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.28810412489235</v>
+        <v>3.391304348125339</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.604696519364382</v>
+        <v>-2.498662836623042</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.24586909283285</v>
+        <v>2.391482789162374</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.8827338454282454</v>
+        <v>0.9887675281695854</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.817744432149297</v>
+        <v>3.98456486502709</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.290995219437651</v>
+        <v>3.39419544267064</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.603409755824826</v>
+        <v>-2.497376073083486</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.249274892793973</v>
+        <v>2.394888589123498</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.884020608967802</v>
+        <v>0.9900542917091419</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.821407584818332</v>
+        <v>3.988228017696125</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347699</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.289107032331426</v>
+        <v>3.392307255564415</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.604966809814117</v>
+        <v>-2.498933127072777</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.246763884092032</v>
+        <v>2.392377580421557</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.884020608967802</v>
+        <v>0.9900542917091419</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.819519397712107</v>
+        <v>3.9863398305899</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.283927261934288</v>
+        <v>3.387127485167277</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.612238695337582</v>
+        <v>-2.506205012596242</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.238675359485509</v>
+        <v>2.384289055815033</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8767487234443372</v>
+        <v>0.9827824061856771</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.809976496000891</v>
+        <v>3.976796928878684</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.282361272144441</v>
+        <v>3.385561495377429</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.610397676279331</v>
+        <v>-2.504363993537991</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.237845777318961</v>
+        <v>2.383459473648486</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8780169501158056</v>
+        <v>0.9840506328571456</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.809171442213924</v>
+        <v>3.975991875091717</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647105</v>
+        <v>3.754911907647101</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.295434679010359</v>
+        <v>3.398634902243348</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.617306381779011</v>
+        <v>-2.511272699037671</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.248155701985008</v>
+        <v>2.393769398314532</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8780169501158056</v>
+        <v>0.9840506328571456</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.822244849079843</v>
+        <v>3.989065281957636</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.749896851763528</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.295434679010359</v>
+        <v>3.398634902243348</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.618868024593871</v>
+        <v>-2.512834341852531</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.247531044859064</v>
+        <v>2.393144741188588</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8780169501158056</v>
+        <v>0.9840506328571456</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.822244849079843</v>
+        <v>3.989065281957636</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392111</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.293958720137361</v>
+        <v>3.39715894337035</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.646768811703344</v>
+        <v>-2.540735128962004</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.234894771142276</v>
+        <v>2.380508467471801</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8434200259728708</v>
+        <v>0.9494537087142108</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.800010735721084</v>
+        <v>3.966831168598876</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.684909939172523</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.29072316411456</v>
+        <v>3.393923387347549</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.649801809216018</v>
+        <v>-2.543768126474678</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.230446016114406</v>
+        <v>2.37605971244393</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8403870284601969</v>
+        <v>0.9464207112015368</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.794955381190678</v>
+        <v>3.961775814068471</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971079</v>
+        <v>3.619362241971075</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.357429123705064</v>
+        <v>3.460629346938052</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.669863130492525</v>
+        <v>-2.563829447751185</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.289127447194307</v>
+        <v>2.434741143523831</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.8203257071836898</v>
+        <v>0.9263593899250298</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.849624548015278</v>
+        <v>4.016444980893071</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.640764248199802</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.497740842706911</v>
+        <v>3.600941065939899</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.926583948487349</v>
+        <v>-2.820550265746009</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.326750838998224</v>
+        <v>2.472364535327749</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.711911133039875</v>
+        <v>0.8179448157812149</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.924887522530836</v>
+        <v>4.091707955408629</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622237</v>
+        <v>3.668303164622233</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.566721111852551</v>
+        <v>3.669921335085539</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.080570366263489</v>
+        <v>-2.974536683522149</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.334136541033407</v>
+        <v>2.479750237362932</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.711911133039875</v>
+        <v>0.8179448157812149</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.993867791676476</v>
+        <v>4.160688224554269</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808529</v>
+        <v>3.619937176808525</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.552772313972671</v>
+        <v>3.65597253720566</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.030048462435823</v>
+        <v>-2.924014779694483</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.340396504684595</v>
+        <v>2.486010201014119</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.711911133039875</v>
+        <v>0.8179448157812149</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.979918993796597</v>
+        <v>4.146739426674389</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,45 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.7599301064677</v>
+        <v>3.656346893994891</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.564642803028085</v>
+        <v>3.667843026261074</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.282523616443548</v>
+        <v>-3.176489933702208</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.251276932136919</v>
+        <v>2.396890628466444</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.711911133039875</v>
+        <v>0.8179448157812149</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.991789482852011</v>
+        <v>4.158609915729803</v>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" s="2" t="n">
+        <v>45482</v>
+      </c>
+      <c r="B2020" t="n">
+        <v>3.407480912882261</v>
+      </c>
+      <c r="C2020" t="n">
+        <v>3.562937844561854</v>
+      </c>
+      <c r="D2020" t="n">
+        <v>-3.176489933702208</v>
+      </c>
+      <c r="E2020" t="n">
+        <v>2.396890628466444</v>
+      </c>
+      <c r="F2020" t="n">
+        <v>0.8179448157812149</v>
+      </c>
+      <c r="G2020" t="n">
+        <v>3.556001641548221</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240709.xlsx
+++ b/tame_output/ON/bt/strategyON_20240709.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>49.0%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>83.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>38.9%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>38.1%</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>36.4%</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-29.9%</t>
+          <t>-40.2%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>65.7%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.4%</t>
+          <t>-70.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.4%</t>
+          <t>109.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.9%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-644.5%</t>
+          <t>-629.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-49.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.9%</t>
+          <t>-65.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.5%</t>
+          <t>457.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-479.2%</t>
+          <t>-465.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-258.2%</t>
+          <t>-252.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.4%</t>
+          <t>-38.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-14.4%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-136.5%</t>
+          <t>-141.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-263.7%</t>
+          <t>-256.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-29.3%</t>
+          <t>-28.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-121.3%</t>
+          <t>-112.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-142.2%</t>
+          <t>-159.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>94.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-158.6%</t>
+          <t>-154.3%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-90.4%</t>
+          <t>-69.4%</t>
         </is>
       </c>
     </row>
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.829620226279244</v>
+        <v>-4.677837200458727</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.18015179420743</v>
+        <v>1.240865004535636</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.3971565031282979</v>
+        <v>-0.3257115125878244</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.874062407155896</v>
+        <v>2.91692940148018</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.165282873509696</v>
+        <v>-5.01349984768918</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.044467326971214</v>
+        <v>1.10518053729942</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.4650874886172027</v>
+        <v>-0.3936424980767292</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.831884407518518</v>
+        <v>2.874751401842802</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.528909118410009</v>
+        <v>-5.377126092589493</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.9055043892453303</v>
+        <v>0.9662175995735369</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.5633091254843285</v>
+        <v>-0.4918641349438551</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.779438985632484</v>
+        <v>2.822305979956768</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.894036501048756</v>
+        <v>-5.74225347522824</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7587079511956629</v>
+        <v>0.8194211615238696</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.859619909783341</v>
+        <v>-0.7881749192428675</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.600907030058909</v>
+        <v>2.643774024383192</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.302625278229435</v>
+        <v>-6.150842252408918</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5940339843381501</v>
+        <v>0.6547471946663572</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.268208686964019</v>
+        <v>-1.196763696423546</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.354515307765261</v>
+        <v>2.397382302089544</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.579201378545267</v>
+        <v>-6.42741835272475</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.478588976683278</v>
+        <v>0.5393021870114847</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.268208686964019</v>
+        <v>-1.196763696423546</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.349700740236721</v>
+        <v>2.392567734561005</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.995593252832265</v>
+        <v>-6.843810227011748</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.3100262775773563</v>
+        <v>0.3707394879055634</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.268208686964019</v>
+        <v>-1.196763696423546</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.347694790845599</v>
+        <v>2.390561785169882</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.239864653559335</v>
+        <v>-7.088081627738817</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.2225764079552075</v>
+        <v>0.2832896182834146</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.268208686964019</v>
+        <v>-1.196763696423546</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.357953481514278</v>
+        <v>2.400820475838561</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.445115672796095</v>
+        <v>-7.293332646975577</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.1365755654061984</v>
+        <v>0.1972887757344055</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.268208686964019</v>
+        <v>-1.196763696423546</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.354053046659972</v>
+        <v>2.396920040984257</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.608695550980478</v>
+        <v>-7.456912525159961</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.069548534187446</v>
+        <v>0.1302617445156531</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.268208686964019</v>
+        <v>-1.196763696423546</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.352457966714973</v>
+        <v>2.395324961039258</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.905356892790675</v>
+        <v>-7.753573866970158</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.04533702660742467</v>
+        <v>0.01537618372078242</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.336951822697898</v>
+        <v>-1.265506832157425</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.314991061203854</v>
+        <v>2.357858055528139</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.092076601099977</v>
+        <v>-7.940293575279461</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.1240512144655486</v>
+        <v>-0.06333800413734192</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.336951822697898</v>
+        <v>-1.265506832157425</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.310964756669451</v>
+        <v>2.353831750993735</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.475077989842609</v>
+        <v>-8.323294964022091</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.277353871284185</v>
+        <v>-0.2166406609559779</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.336951822697898</v>
+        <v>-1.265506832157425</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.310862655347867</v>
+        <v>2.353729649672151</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.656947780827643</v>
+        <v>-8.505164755007126</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.3475302717067685</v>
+        <v>-0.2868170613785619</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.518821613682933</v>
+        <v>-1.44737662314246</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.204312296728276</v>
+        <v>2.24717929105256</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.016478103331645</v>
+        <v>-8.864695077511128</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.4859920974103193</v>
+        <v>-0.4252788870821123</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.518821613682933</v>
+        <v>-1.44737662314246</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.209662600026327</v>
+        <v>2.252529594350611</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.066827166785867</v>
+        <v>-8.91504414096535</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.4982157028348304</v>
+        <v>-0.4375024925066238</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.569170677137155</v>
+        <v>-1.497725686596682</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.187369181910971</v>
+        <v>2.230236176235255</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.164446444207263</v>
+        <v>-9.012663418386746</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.5342216631816199</v>
+        <v>-0.4735084528534133</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.666789954558552</v>
+        <v>-1.595344964018078</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.131839366079902</v>
+        <v>2.174706360404186</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.311972532212906</v>
+        <v>-9.160189506392388</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.5903385420623048</v>
+        <v>-0.5296253317340982</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.814316042564195</v>
+        <v>-1.742871052023722</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.046217269598088</v>
+        <v>2.089084263922372</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.516230707542769</v>
+        <v>-9.364447681722252</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.6665286150756082</v>
+        <v>-0.6058154047474011</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.941954987178184</v>
+        <v>-1.870509996637711</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.975147099948336</v>
+        <v>2.018014094272621</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.549883546051243</v>
+        <v>-9.398100520230726</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.6755071959945615</v>
+        <v>-0.6147939856663545</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.042368355095221</v>
+        <v>-1.970923364554748</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.91938163368255</v>
+        <v>1.962248628006835</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.476413714383794</v>
+        <v>-9.324630688563277</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.6307475618341609</v>
+        <v>-0.5700343515059538</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.968898523427773</v>
+        <v>-1.8974535328873</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.978835234176441</v>
+        <v>2.021702228500724</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.651538131770337</v>
+        <v>-9.49975510594982</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.6862421080412613</v>
+        <v>-0.6255288977130542</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.144022940814317</v>
+        <v>-2.072577950273844</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.888315804492031</v>
+        <v>1.931182798816315</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.885990225784827</v>
+        <v>-9.73420719996431</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.7872421105486533</v>
+        <v>-0.7265289002204462</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.144022940814317</v>
+        <v>-2.072577950273844</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.881096639590435</v>
+        <v>1.923963633914719</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.990364956811273</v>
+        <v>-9.838581930990756</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.8356641937332081</v>
+        <v>-0.774950983405001</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.248397671840763</v>
+        <v>-2.17695268130029</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.811799610200591</v>
+        <v>1.854666604524875</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.0431511124116</v>
+        <v>-9.891368086591083</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.8556628661347823</v>
+        <v>-0.7949496558065752</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.34407315842316</v>
+        <v>-2.272628167882687</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.75551010808971</v>
+        <v>1.798377102413993</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.16918790577989</v>
+        <v>-10.01740487995937</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.9033838548529833</v>
+        <v>-0.8426706445247762</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.318821535613417</v>
+        <v>-2.247376545072944</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.77335481040467</v>
+        <v>1.816221804728954</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.11211613388396</v>
+        <v>-9.960333108063441</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.87656481040821</v>
+        <v>-0.8158516000800033</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.318821535613417</v>
+        <v>-2.247376545072944</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.777345146091071</v>
+        <v>1.820212140415354</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.25378797560808</v>
+        <v>-10.10200494978756</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.9347087739965998</v>
+        <v>-0.8739955636683927</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.318821535613417</v>
+        <v>-2.247376545072944</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.775869919192329</v>
+        <v>1.818736913516613</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.20419713118324</v>
+        <v>-10.05241410536273</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.899819026061794</v>
+        <v>-0.8391058157335869</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.269230691188584</v>
+        <v>-2.19778570064811</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.820677836012101</v>
+        <v>1.863544830336385</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.05527879671139</v>
+        <v>-9.903495770890871</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.8533028259197342</v>
+        <v>-0.7925896155915275</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.23798110045341</v>
+        <v>-2.166536109912937</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.826376456806522</v>
+        <v>1.869243451130806</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.829433643991976</v>
+        <v>-9.677650618171459</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.7533856917957609</v>
+        <v>-0.6926724814675542</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.196054424866247</v>
+        <v>-2.124609434325774</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.861111535195029</v>
+        <v>1.903978529519313</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.704854987654384</v>
+        <v>-9.553071961833867</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.7024150847046653</v>
+        <v>-0.6417018743764582</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.196054424866247</v>
+        <v>-2.124609434325774</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.862250679751088</v>
+        <v>1.905117674075372</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.757750275698671</v>
+        <v>-9.605967249878153</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.7209394257602724</v>
+        <v>-0.6602262154320653</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.191099078777801</v>
+        <v>-2.119654088237327</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.867857661566263</v>
+        <v>1.910724655890547</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.68561710041079</v>
+        <v>-9.533834074590272</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.6863524514064832</v>
+        <v>-0.6256392410782765</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.191099078777801</v>
+        <v>-2.119654088237327</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.8735913658049</v>
+        <v>1.916458360129184</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.47971056860494</v>
+        <v>-9.462467681980625</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.6137271010780085</v>
+        <v>-0.6068299464282827</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.985192546971951</v>
+        <v>-2.04828769562768</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.987398022494544</v>
+        <v>1.949540933301107</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.386251534619715</v>
+        <v>-9.3690086479954</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.5862269687968262</v>
+        <v>-0.5793298141471004</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.985192546971951</v>
+        <v>-2.04828769562768</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.977514541181637</v>
+        <v>1.939657451988199</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.119009733751318</v>
+        <v>-9.101766847127003</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.4811648089488409</v>
+        <v>-0.4742676542991151</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.985192546971951</v>
+        <v>-2.04828769562768</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.975679980682263</v>
+        <v>1.937822891488826</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311945</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.021102695074827</v>
+        <v>-9.003859808450512</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.4423023084517057</v>
+        <v>-0.4354051538019799</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.917206797111395</v>
+        <v>-1.980301945767123</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.016171115625136</v>
+        <v>1.978314026431699</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409724</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.997149154098869</v>
+        <v>-8.979906267474554</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.4320523859158287</v>
+        <v>-0.4251552312661029</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.893253256135437</v>
+        <v>-1.956348404791165</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.031211746356204</v>
+        <v>1.993354657162767</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017768</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.733089215776072</v>
+        <v>-8.715846329151757</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.3396887267484621</v>
+        <v>-0.3327915720987362</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.629193317812641</v>
+        <v>-1.692288466468369</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.17638739318813</v>
+        <v>2.138530303994693</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.026009592271235</v>
+        <v>-8.00876670564692</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.05964391100682809</v>
+        <v>-0.0527467563571018</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.629193317812641</v>
+        <v>-1.692288466468369</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.173600359527829</v>
+        <v>2.135743270334392</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.985825293905044</v>
+        <v>-7.96858240728073</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.04322656777251055</v>
+        <v>-0.03632941312278426</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.58900901944645</v>
+        <v>-1.652104168102178</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.198054562435385</v>
+        <v>2.160197473241948</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.822425422965682</v>
+        <v>-7.805182536341367</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.02150020182399137</v>
+        <v>0.02839735647371766</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.425609148507088</v>
+        <v>-1.488704297162816</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.295461306219759</v>
+        <v>2.257604217026322</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.588944200736083</v>
+        <v>-7.571701314111769</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.1228171195536829</v>
+        <v>0.1297142742034092</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.192127926277489</v>
+        <v>-1.255223074933217</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.443474468395371</v>
+        <v>2.405617379201934</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785785</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.439277809728568</v>
+        <v>-7.422034923104254</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.1797914656437301</v>
+        <v>0.1866886202934563</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.099224435034953</v>
+        <v>-1.162319583690681</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.496324352827933</v>
+        <v>2.458467263634496</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390426</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.307002336097682</v>
+        <v>-7.289759449473367</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2280691418431116</v>
+        <v>0.2349662964928378</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.9669489614040665</v>
+        <v>-1.030044110059795</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.571057123753492</v>
+        <v>2.533200034560055</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471879410595</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.15126400353794</v>
+        <v>-7.134021116913625</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.2931795355546449</v>
+        <v>0.3000766902043712</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.8112106288443249</v>
+        <v>-0.8743057775000532</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.667315183976974</v>
+        <v>2.629458094783537</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960984</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.902264204854359</v>
+        <v>-6.885021318230044</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4056857962517362</v>
+        <v>0.4125829509014625</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.8112106288443249</v>
+        <v>-0.8743057775000532</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.680221525200632</v>
+        <v>2.642364436007195</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607642</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.007854194627464</v>
+        <v>-6.990611308003149</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2354738707432755</v>
+        <v>0.2423710253930018</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.9168006186174293</v>
+        <v>-0.9798957672731576</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.488891601737551</v>
+        <v>2.451034512544114</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.02658909674606</v>
+        <v>-7.009346210121746</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2765242517729232</v>
+        <v>0.2834214064226495</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.9223966282775606</v>
+        <v>-0.9854917769332889</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.534078337818559</v>
+        <v>2.496221248625122</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.878649055338461</v>
+        <v>-6.861406168714146</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2158213456477953</v>
+        <v>0.2227185002975216</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.9020757123690031</v>
+        <v>-0.9651708610247314</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.426391964675526</v>
+        <v>2.388534875482089</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.825679533084473</v>
+        <v>-6.808436646460158</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2282951682959125</v>
+        <v>0.2351923229456387</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.8491061901150142</v>
+        <v>-0.9122013387707425</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.449459691774441</v>
+        <v>2.411602602581004</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.782131126313782</v>
+        <v>-6.764888239689467</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2387539189090955</v>
+        <v>0.2456510735588218</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.8491061901150142</v>
+        <v>-0.9122013387707425</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.442499079679348</v>
+        <v>2.404641990485911</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.539982732859924</v>
+        <v>-6.522739846235609</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3500756306717818</v>
+        <v>0.3569727853215081</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.8491061901150142</v>
+        <v>-0.9122013387707425</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.456961434060491</v>
+        <v>2.419104344867054</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.431723595737402</v>
+        <v>-6.414480709113088</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3879114059799855</v>
+        <v>0.3948085606297118</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.8491061901150142</v>
+        <v>-0.9122013387707425</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.451493554519686</v>
+        <v>2.413636465326249</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.308432460920272</v>
+        <v>-6.291189574295957</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4347259539174151</v>
+        <v>0.4416231085671414</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.7258150552978837</v>
+        <v>-0.788910203953612</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.522966329420541</v>
+        <v>2.485109240227104</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.287283262016828</v>
+        <v>-6.270040375392513</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4508866117161174</v>
+        <v>0.4577837663658437</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.7046658563944403</v>
+        <v>-0.7677610050501686</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.543356826999932</v>
+        <v>2.505499737806495</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.043517820033384</v>
+        <v>-6.026274933409069</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5441734968565459</v>
+        <v>0.5510706515062722</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.7046658563944403</v>
+        <v>-0.7677610050501686</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.539137535346983</v>
+        <v>2.501280446153546</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.941754999756089</v>
+        <v>-5.924512113131774</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5870029388874798</v>
+        <v>0.5939000935372061</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.6914467880020116</v>
+        <v>-0.7545419366577399</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.549193290302456</v>
+        <v>2.511336201109019</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279183</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.691904605807014</v>
+        <v>-5.6746617191827</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6796851714508119</v>
+        <v>0.6865823261005382</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.6914467880020116</v>
+        <v>-0.7545419366577399</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.541935365286158</v>
+        <v>2.504078276092721</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.516012513339582</v>
+        <v>-5.498769626715267</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7536411319584335</v>
+        <v>0.7605382866081603</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.6914467880020116</v>
+        <v>-0.7545419366577399</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.545534488806807</v>
+        <v>2.50767739961337</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.344566050317119</v>
+        <v>-5.327323163692803</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8355472232219725</v>
+        <v>0.8424443778716992</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.5200003249795485</v>
+        <v>-0.5830954736352768</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.661729872674838</v>
+        <v>2.623872783481402</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.27027648457878</v>
+        <v>-5.253033597954464</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8642835271336051</v>
+        <v>0.8711806817833319</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.4457107592412092</v>
+        <v>-0.5088059078969376</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.705324089734139</v>
+        <v>2.667467000540702</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.206640742344845</v>
+        <v>-5.18939785572053</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.894432625081496</v>
+        <v>0.9013297797312227</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.3820750170072747</v>
+        <v>-0.445170165663003</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.748200336128817</v>
+        <v>2.71034324693538</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.095213983018925</v>
+        <v>-5.077971096394609</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9201975875956601</v>
+        <v>0.9270947422453863</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.3820750170072747</v>
+        <v>-0.445170165663003</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.729394594912613</v>
+        <v>2.691537505719176</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.854783486214065</v>
+        <v>-4.837540599589749</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.018112862942481</v>
+        <v>1.025010017592208</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.1416445202024144</v>
+        <v>-0.2047396688581428</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.875395969620406</v>
+        <v>2.837538880426969</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.78254091804287</v>
+        <v>-4.765298031418554</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.050939204045779</v>
+        <v>1.057836358695506</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.1416445202024144</v>
+        <v>-0.2047396688581428</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.879325283455227</v>
+        <v>2.84146819426179</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.729542595761482</v>
+        <v>-4.712299709137167</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.072817116875675</v>
+        <v>1.079714271525401</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.08630826120047558</v>
+        <v>-0.1494034098562039</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.91320562277373</v>
+        <v>2.875348533580293</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.620737710281755</v>
+        <v>-4.60349482365744</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.113337142287559</v>
+        <v>1.120234296937286</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.08630826120047558</v>
+        <v>-0.1494034098562039</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.910203693993723</v>
+        <v>2.872346604800286</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.400716912244745</v>
+        <v>-4.383474025620429</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.202924498512977</v>
+        <v>1.209821653162704</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.05491158386750467</v>
+        <v>-0.008183564788223685</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.996514638045126</v>
+        <v>2.958657548851689</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.267849223181467</v>
+        <v>-4.250606336557151</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.271965756940112</v>
+        <v>1.278862911589838</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.05491158386750467</v>
+        <v>-0.008183564788223685</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.012408820846949</v>
+        <v>2.974551731653512</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.147676139816968</v>
+        <v>-4.130433253192653</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.321180834726213</v>
+        <v>1.32807798937594</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.1750846672320036</v>
+        <v>0.1119895185762753</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.08565851530595</v>
+        <v>3.047801426112513</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.003003994717231</v>
+        <v>-3.985761108092915</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.389137795327548</v>
+        <v>1.396034949977274</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.319756812331741</v>
+        <v>0.2566616636760127</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.182549904927233</v>
+        <v>3.144692815733795</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.7358392229421</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.062878822074923</v>
+        <v>-4.045635935450608</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.351225355785897</v>
+        <v>1.358122510435623</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.2598819849740489</v>
+        <v>0.1967868363183206</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.132662499914043</v>
+        <v>3.094805410720606</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.943058591164086</v>
+        <v>-3.92581570453977</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.41444261738444</v>
+        <v>1.421339772034167</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.2598819849740489</v>
+        <v>0.1967868363183206</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.147951669148251</v>
+        <v>3.110094579954815</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914639843069</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.945528297625892</v>
+        <v>-3.928285411001576</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.321098934122159</v>
+        <v>1.327996088771886</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.2574122785122427</v>
+        <v>0.1943171298565144</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.054114044593609</v>
+        <v>3.016256955400172</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.013898483949902</v>
+        <v>-3.996655597325586</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.213012721077857</v>
+        <v>1.219909875727583</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.2666879775484577</v>
+        <v>0.2035928288927293</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.97894132550064</v>
+        <v>2.941084236307203</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.027686536796948</v>
+        <v>-4.010443650172633</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.197934208570929</v>
+        <v>1.204831363220656</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.2666879775484577</v>
+        <v>0.2035928288927293</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.969378034132531</v>
+        <v>2.931520944939094</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.737275035876832</v>
+        <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.058679696125654</v>
+        <v>-3.819714480922205</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.113446733112823</v>
+        <v>1.105832595961214</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.2666879775484577</v>
+        <v>0.2035928288927293</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.897287822405907</v>
+        <v>2.756230509979481</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.74184226786862</v>
+        <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.883205436333184</v>
+        <v>-3.644240221129736</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.188203669021599</v>
+        <v>1.180589531869989</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.2666879775484577</v>
+        <v>0.2035928288927293</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.901855054397695</v>
+        <v>2.760797741971269</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.717584296629827</v>
+        <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.994141688974433</v>
+        <v>-3.755176473770985</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.119571196726306</v>
+        <v>1.111957059574697</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.2666879775484577</v>
+        <v>0.2035928288927293</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.877597083158902</v>
+        <v>2.736539770732476</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.720715681849732</v>
+        <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.960478143502151</v>
+        <v>-3.721512928298703</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.136168000135125</v>
+        <v>1.128553862983515</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.3003515230207395</v>
+        <v>0.2372563743650112</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.900926595662177</v>
+        <v>2.75986928323575</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.730888068281865</v>
+        <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.900625524298428</v>
+        <v>-3.66166030909498</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.170281434248746</v>
+        <v>1.162667297097137</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.3003515230207395</v>
+        <v>0.2372563743650112</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.911098982094309</v>
+        <v>2.770041669667882</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.725834338855725</v>
+        <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.814382061272051</v>
+        <v>-3.575416846068602</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.199725090033158</v>
+        <v>1.192110952881548</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.3003515230207395</v>
+        <v>0.2372563743650112</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.906045252668169</v>
+        <v>2.764987940241743</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.717610114300251</v>
+        <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.859688880671031</v>
+        <v>-3.620723665467582</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.173378137718091</v>
+        <v>1.165764000566482</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.2595413600115087</v>
+        <v>0.1964462113557804</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.873334930307156</v>
+        <v>2.73227761788073</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.718161987333352</v>
+        <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.888721985373332</v>
+        <v>-3.649756770169884</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.162316768870272</v>
+        <v>1.154702631718663</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.2595413600115087</v>
+        <v>0.1964462113557804</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.873886803340258</v>
+        <v>2.732829490913832</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.647434679224718</v>
+        <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.795911503922473</v>
+        <v>-3.556946288719025</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.128713653341981</v>
+        <v>1.121099516190372</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.3523518414623681</v>
+        <v>0.2892566928066397</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.858845784102139</v>
+        <v>2.717788471675713</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.649308155149319</v>
+        <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.8403009732519</v>
+        <v>-3.601335758048452</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.112831341534811</v>
+        <v>1.105217204383202</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.3079623721329404</v>
+        <v>0.2448672234772121</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.834085578429083</v>
+        <v>2.693028266002657</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.644383863661042</v>
+        <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.72762975501565</v>
+        <v>-3.488664539812202</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.152975537341034</v>
+        <v>1.145361400189425</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4206335903691906</v>
+        <v>0.3575384417134623</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.896764017882556</v>
+        <v>2.75570670545613</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.649875159491709</v>
+        <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.615252753832978</v>
+        <v>-3.376287538629529</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.203417633644771</v>
+        <v>1.195803496493161</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4206335903691906</v>
+        <v>0.3575384417134623</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.902255313713224</v>
+        <v>2.761198001286798</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.661372361260248</v>
+        <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.643033151734331</v>
+        <v>-3.404067936530883</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.203802676252768</v>
+        <v>1.196188539101159</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.3928531924678376</v>
+        <v>0.3297580438121092</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.897084276740951</v>
+        <v>2.756026964314525</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.499728081260901</v>
+        <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.72603443275961</v>
+        <v>-3.487069217556162</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.00895788384331</v>
+        <v>1.001343746691701</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3742823079406638</v>
+        <v>0.3111871592849355</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.7242974660253</v>
+        <v>2.583240153598874</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.619877741980107</v>
+        <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.834648511202941</v>
+        <v>-3.595683295999493</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.085661913185183</v>
+        <v>1.078047776033574</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3742823079406638</v>
+        <v>0.3111871592849355</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.844447126744505</v>
+        <v>2.703389814318079</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.63439076808243</v>
+        <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.799239472954798</v>
+        <v>-3.56027425775135</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.114338554586763</v>
+        <v>1.106724417435154</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3742823079406638</v>
+        <v>0.3111871592849355</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.858960152846828</v>
+        <v>2.717902840420402</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.631810209424799</v>
+        <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.654822127655307</v>
+        <v>-3.521890595193199</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.169524934048928</v>
+        <v>1.119497323800783</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.5186996532401547</v>
+        <v>0.3495708218430866</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.943030001368891</v>
+        <v>2.738352479297662</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.6285392382701</v>
+        <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.477705797620141</v>
+        <v>-3.344774265158033</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.237100494908297</v>
+        <v>1.187072884660152</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.5186996532401547</v>
+        <v>0.3495708218430866</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.939759030214193</v>
+        <v>2.735081508142964</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.629222630032014</v>
+        <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.522798042453687</v>
+        <v>-3.389866509991578</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.219746988736792</v>
+        <v>1.169719378488647</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4568036100707649</v>
+        <v>0.2876747786736968</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.903304796074473</v>
+        <v>2.698627274003243</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.623009605338428</v>
+        <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.343422621214919</v>
+        <v>-3.210491088752811</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.285284132538713</v>
+        <v>1.235256522290568</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6135803682414835</v>
+        <v>0.4444515368444155</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.991157826283318</v>
+        <v>2.786480304212089</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.603817060670018</v>
+        <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.388436834735525</v>
+        <v>-3.255505302273417</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.24808590246206</v>
+        <v>1.198058292213915</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5832314729268789</v>
+        <v>0.4141026415298109</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.953755944426145</v>
+        <v>2.749078422354916</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.609508623008963</v>
+        <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.655441345007961</v>
+        <v>-3.522509812545852</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.146975660692032</v>
+        <v>1.096948050443887</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3888684348839304</v>
+        <v>0.2197396034868623</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.842829683939322</v>
+        <v>2.638152161868093</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.608712544905465</v>
+        <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.756639126445133</v>
+        <v>-3.623707593983025</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.105700470013664</v>
+        <v>1.055672859765519</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3204596213386112</v>
+        <v>0.1513307899415431</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.800988317708632</v>
+        <v>2.596310795637403</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.606312506459782</v>
+        <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.750128159830821</v>
+        <v>-3.617196627368712</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.105904818213706</v>
+        <v>1.055877207965561</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3204596213386112</v>
+        <v>0.1513307899415431</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.798588279262948</v>
+        <v>2.593910757191719</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.602837225668027</v>
+        <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.731090032123523</v>
+        <v>-3.598158499661415</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.11004478850487</v>
+        <v>1.060017178256725</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2622760100074166</v>
+        <v>0.0931471786103486</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.760202831672477</v>
+        <v>2.555525309601247</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.780419094606707</v>
+        <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.762216663274141</v>
+        <v>-3.629285130812033</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.275176004983303</v>
+        <v>1.225148394735158</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2622760100074166</v>
+        <v>0.0931471786103486</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.937784700611157</v>
+        <v>2.733107178539928</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.781252423592841</v>
+        <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.776083424608059</v>
+        <v>-3.64315189214595</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.27046262943587</v>
+        <v>1.220435019187725</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2244180932735937</v>
+        <v>0.05528926187652566</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.915903279556997</v>
+        <v>2.711225757485768</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.787260953989767</v>
+        <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.731279253068129</v>
+        <v>-3.598347720606021</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.294392828448768</v>
+        <v>1.244365218200623</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2244180932735937</v>
+        <v>0.05528926187652566</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.921911809953923</v>
+        <v>2.717234287882694</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.685211175266966</v>
+        <v>2.582010952033977</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.583536282833127</v>
+        <v>-3.450604750371018</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.251440237819968</v>
+        <v>1.201412627571823</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3922254505084768</v>
+        <v>0.2230966191114088</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.920546445572052</v>
+        <v>2.715868923500823</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.688004796798447</v>
+        <v>2.584804573565458</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.685550965364348</v>
+        <v>-3.552619432902239</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.213427986338961</v>
+        <v>1.163400376090816</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3922254505084768</v>
+        <v>0.2230966191114088</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.923340067103533</v>
+        <v>2.718662545032304</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.688667145190105</v>
+        <v>2.585466921957117</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.679398259311563</v>
+        <v>-3.546466726849455</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.216551417151733</v>
+        <v>1.166523806903588</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3983781565612611</v>
+        <v>0.2292493251641931</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.927694039126862</v>
+        <v>2.723016517055633</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.687747621930216</v>
+        <v>2.584547398697227</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.696207557462065</v>
+        <v>-3.563276024999956</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.208908174631643</v>
+        <v>1.158880564383497</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3815688584107595</v>
+        <v>0.2124400270136915</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.916688936976672</v>
+        <v>2.712011414905442</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.754083175727037</v>
+        <v>2.650882952494048</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.633909558685943</v>
+        <v>-3.500978026223835</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.300162927938912</v>
+        <v>1.250135317690767</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3815688584107595</v>
+        <v>0.2124400270136915</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.983024490773492</v>
+        <v>2.778346968702263</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.556375177441164</v>
+        <v>2.453174954208175</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.432119361020785</v>
+        <v>-3.299187828558677</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.183171008719102</v>
+        <v>1.133143398470957</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5795870505799139</v>
+        <v>0.4104582191828459</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.904127407789112</v>
+        <v>2.699449885717883</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.626665409763339</v>
+        <v>2.52346518653035</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.358741263932048</v>
+        <v>-3.22580973146994</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.282812479876772</v>
+        <v>1.232784869628627</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6529651476686504</v>
+        <v>0.4838363162715824</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.018444498364529</v>
+        <v>2.8137669762933</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.641293145879382</v>
+        <v>2.538092922646394</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.456481808557023</v>
+        <v>-3.323550276094914</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.258343998142826</v>
+        <v>1.208316387894681</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6370758695356702</v>
+        <v>0.4679470381386022</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.023538667600785</v>
+        <v>2.818861145529556</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.639829126704054</v>
+        <v>2.536628903471065</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.632819568679952</v>
+        <v>-3.499888036217844</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.186344874918326</v>
+        <v>1.136317264670181</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4607381094127408</v>
+        <v>0.2916092780156728</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.916271992351699</v>
+        <v>2.71159447028047</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.638320744743983</v>
+        <v>2.535120521510994</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.556397522248025</v>
+        <v>-3.423465989785917</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.215405311531025</v>
+        <v>1.16537770128288</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4607381094127408</v>
+        <v>0.2916092780156728</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.914763610391628</v>
+        <v>2.710086088320398</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.638183612179419</v>
+        <v>2.53498338894643</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.512024390609457</v>
+        <v>-3.379092858147348</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.233017431621889</v>
+        <v>1.182989821373744</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5051112410513094</v>
+        <v>0.3359824096542414</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.941250356810205</v>
+        <v>2.736572834738976</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.632577406318009</v>
+        <v>2.529377183085021</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.389190169722289</v>
+        <v>-3.256258637260181</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.276544914115346</v>
+        <v>1.226517303867201</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5051112410513094</v>
+        <v>0.3359824096542414</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.935644150948795</v>
+        <v>2.730966628877566</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.638959163345814</v>
+        <v>2.535758940112825</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.341534439161234</v>
+        <v>-3.208602906699126</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.301988963367573</v>
+        <v>1.251961353119428</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5527669716123651</v>
+        <v>0.3836381402152971</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.970619346313233</v>
+        <v>2.765941824242004</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.643851536720539</v>
+        <v>2.54065131348755</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.241016280662479</v>
+        <v>-3.108084748200371</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.3470886001418</v>
+        <v>1.297060989893655</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6532851301111197</v>
+        <v>0.4841562987140516</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.035822614787211</v>
+        <v>2.831145092715981</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82880887755729</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.630606209196411</v>
+        <v>2.527405985963422</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.301682871064868</v>
+        <v>-3.16875133860276</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.309576636456717</v>
+        <v>1.259549026208572</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.571586813392586</v>
+        <v>0.402457981995518</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.973558297231963</v>
+        <v>2.768880775160734</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.63470391180704</v>
+        <v>2.531503688574051</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.25684446945647</v>
+        <v>-3.123912936994362</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.331609699710704</v>
+        <v>1.281582089462559</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5761302463374555</v>
+        <v>0.4070014149403874</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.980382059609513</v>
+        <v>2.775704537538284</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.81793235491705</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.638864851438118</v>
+        <v>2.535664628205129</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.357603105213469</v>
+        <v>-3.22467157275136</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.295467185038983</v>
+        <v>1.245439574790838</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.48730467761045</v>
+        <v>0.318175846213382</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.931247658004388</v>
+        <v>2.726570135933159</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.644744453965955</v>
+        <v>2.541544230732966</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.313400268127568</v>
+        <v>-3.18046873566546</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.31902792240118</v>
+        <v>1.269000312153035</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5315075146963505</v>
+        <v>0.3623786832992825</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.963648962783765</v>
+        <v>2.758971440712536</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.643154454435202</v>
+        <v>2.539954231202214</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.350379295791011</v>
+        <v>-3.217447763328903</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.30264631180505</v>
+        <v>1.252618701556905</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.568481416487681</v>
+        <v>0.399352585090613</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.984243304327811</v>
+        <v>2.779565782256582</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.694402219618242</v>
+        <v>2.591201996385253</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.192087878251739</v>
+        <v>-3.059156345789631</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.417210644003799</v>
+        <v>1.367183033755654</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.568481416487681</v>
+        <v>0.399352585090613</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.035491069510851</v>
+        <v>2.830813547439621</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321018</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.692842924212495</v>
+        <v>2.589642700979506</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.984445874617263</v>
+        <v>-2.851514342155155</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.498708150051843</v>
+        <v>1.448680539803698</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.7761234201221572</v>
+        <v>0.6069945887250892</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.15851697628579</v>
+        <v>2.95383945421456</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.687791152450765</v>
+        <v>2.584590929217776</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.933413781894735</v>
+        <v>-2.800482249432627</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.514069215379124</v>
+        <v>1.464041605130979</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8271555128446851</v>
+        <v>0.6580266814476171</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.184084460157576</v>
+        <v>2.979406938086347</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404849</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.70497855654347</v>
+        <v>2.601778333310481</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.868189600767529</v>
+        <v>-2.735258068305421</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.557346291922711</v>
+        <v>1.507318681674566</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.8923796939718908</v>
+        <v>0.7232508625748227</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.240406372926605</v>
+        <v>3.035728850855375</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882553</v>
+        <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.70093952884275</v>
+        <v>2.597739305609762</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.830762580696395</v>
+        <v>-2.697831048234287</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.568278072250445</v>
+        <v>1.5182504620023</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.8976312320010724</v>
+        <v>0.7285024006040044</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.239518268043394</v>
+        <v>3.034840745972164</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992656</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.702196321173991</v>
+        <v>2.598996097941002</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.850874236731104</v>
+        <v>-2.717942704268995</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.561490202167802</v>
+        <v>1.511462591919657</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9086585769984916</v>
+        <v>0.7395297456014236</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.247391467373086</v>
+        <v>3.042713945301856</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.862754092195201</v>
+        <v>2.759553868962213</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.797129422303899</v>
+        <v>-2.664197889841791</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.743545898959895</v>
+        <v>1.69351828871175</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9187218864389536</v>
+        <v>0.7495930550418856</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.413987224058574</v>
+        <v>3.209309701987344</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957621</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.982867001413019</v>
+        <v>2.87966677818003</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.773337853697757</v>
+        <v>-2.640406321235648</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.873175435620169</v>
+        <v>1.823147825372024</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9425134550450959</v>
+        <v>0.7733846236480278</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.548375074440076</v>
+        <v>3.343697552368847</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.974574977426878</v>
+        <v>2.871374754193889</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.747253769433949</v>
+        <v>-2.61432223697184</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.875317045339551</v>
+        <v>1.825289435091406</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9425134550450959</v>
+        <v>0.7733846236480278</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.540083050453935</v>
+        <v>3.335405528382706</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896924</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.972768173010657</v>
+        <v>2.869567949777668</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.669122588585002</v>
+        <v>-2.536191056122894</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.904762713262909</v>
+        <v>1.854735103014764</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.01669026592878</v>
+        <v>0.8475614345317124</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.582782332567926</v>
+        <v>3.378104810496696</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959853</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.990322578737449</v>
+        <v>2.88712235550446</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.660230127191719</v>
+        <v>-2.52729859472961</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.925874103547014</v>
+        <v>1.875846493298869</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.01669026592878</v>
+        <v>0.8475614345317124</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.600336738294717</v>
+        <v>3.395659216223487</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.982177626142033</v>
+        <v>2.878977402909044</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.828706244161597</v>
+        <v>-2.695774711699488</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.850338704163647</v>
+        <v>1.800311093915502</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.9887424302121997</v>
+        <v>0.8196135988151316</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.575423084269353</v>
+        <v>3.370745562198123</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782703</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.963447323329894</v>
+        <v>2.860247100096906</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.130906715300013</v>
+        <v>-1.997975182837905</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.110728212896142</v>
+        <v>2.060700602647997</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.918394370841789</v>
+        <v>0.749265539444721</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.514483945834968</v>
+        <v>3.309806423763738</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632631</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.954111345826799</v>
+        <v>2.85091112259381</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.108185611616861</v>
+        <v>-1.975254079154753</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.110480676866307</v>
+        <v>2.060453066618162</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.918394370841789</v>
+        <v>0.749265539444721</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.505147968331872</v>
+        <v>3.300470446260643</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777669</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.113017471677968</v>
+        <v>3.009817248444979</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.106460568326817</v>
+        <v>-1.973529035864709</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.270076820033494</v>
+        <v>2.220049209785349</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9201194141318327</v>
+        <v>0.7509905827347647</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.665089120157068</v>
+        <v>3.460411598085838</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.150095294171614</v>
+        <v>3.046895070938626</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.261241575105072</v>
+        <v>-2.128310042642964</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.245242239815838</v>
+        <v>2.195214629567693</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.8867517400773566</v>
+        <v>0.7176229086802886</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.682146338218029</v>
+        <v>3.477468816146799</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.14677065016116</v>
+        <v>3.043570426928171</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.209806241720413</v>
+        <v>-2.076874709258305</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.262491729159247</v>
+        <v>2.212464118911102</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9381870734620162</v>
+        <v>0.7690582420649482</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.709682894238369</v>
+        <v>3.50500537216714</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.156776803805901</v>
+        <v>3.053576580572912</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.182855017393925</v>
+        <v>-2.049923484931817</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.283278372534584</v>
+        <v>2.233250762286439</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9530674194897354</v>
+        <v>0.7839385880926674</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.728617255499743</v>
+        <v>3.523939733428513</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784103</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.340879935950861</v>
+        <v>3.237679712717872</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.318808025450241</v>
+        <v>-2.185876492988132</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.413000301457017</v>
+        <v>2.362972691208872</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9530674194897354</v>
+        <v>0.7839385880926674</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.912720387644702</v>
+        <v>3.708042865573473</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.332996630853854</v>
+        <v>3.229796407620865</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.341216143255113</v>
+        <v>-2.208284610793005</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.396153749238062</v>
+        <v>2.346126138989917</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9530674194897354</v>
+        <v>0.7839385880926674</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.904837082547695</v>
+        <v>3.700159560476466</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.335050630403491</v>
+        <v>3.231850407170503</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.489221910734512</v>
+        <v>-2.356290378272404</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.339005441795939</v>
+        <v>2.288977831547794</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.8663404106261939</v>
+        <v>0.6972115792291259</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.854854876779208</v>
+        <v>3.650177354707979</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161973</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.391304348125339</v>
+        <v>3.28810412489235</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.498662836623042</v>
+        <v>-2.365731304160934</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.391482789162374</v>
+        <v>2.341455178914229</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.9887675281695854</v>
+        <v>0.8196386967725173</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.98456486502709</v>
+        <v>3.779887342955861</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.71494119332163</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.39419544267064</v>
+        <v>3.290995219437651</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.497376073083486</v>
+        <v>-2.364444540621378</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.394888589123498</v>
+        <v>2.344860978875353</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9900542917091419</v>
+        <v>0.8209254603120739</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.988228017696125</v>
+        <v>3.783550495624895</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347699</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.392307255564415</v>
+        <v>3.289107032331426</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.498933127072777</v>
+        <v>-2.366001594610669</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.392377580421557</v>
+        <v>2.342349970173411</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9900542917091419</v>
+        <v>0.8209254603120739</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.9863398305899</v>
+        <v>3.78166230851867</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887743</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.387127485167277</v>
+        <v>3.283927261934288</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.506205012596242</v>
+        <v>-2.373273480134134</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.384289055815033</v>
+        <v>2.334261445566888</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9827824061856771</v>
+        <v>0.8136535747886091</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.976796928878684</v>
+        <v>3.772119406807454</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.385561495377429</v>
+        <v>3.282361272144441</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.504363993537991</v>
+        <v>-2.371432461075882</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.383459473648486</v>
+        <v>2.333431863400341</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9840506328571456</v>
+        <v>0.8149218014600775</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.975991875091717</v>
+        <v>3.771314353020487</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647101</v>
+        <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.398634902243348</v>
+        <v>3.295434679010359</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.511272699037671</v>
+        <v>-2.378341166575563</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.393769398314532</v>
+        <v>2.343741788066387</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9840506328571456</v>
+        <v>0.8149218014600775</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.989065281957636</v>
+        <v>3.784387759886406</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763528</v>
+        <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.398634902243348</v>
+        <v>3.295434679010359</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.512834341852531</v>
+        <v>-2.379902809390423</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.393144741188588</v>
+        <v>2.343117130940443</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9840506328571456</v>
+        <v>0.8149218014600775</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.989065281957636</v>
+        <v>3.784387759886406</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392111</v>
+        <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.39715894337035</v>
+        <v>3.293958720137361</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.540735128962004</v>
+        <v>-2.407803596499896</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.380508467471801</v>
+        <v>2.330480857223656</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9494537087142108</v>
+        <v>0.7803248773171427</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.966831168598876</v>
+        <v>3.762153646527647</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172523</v>
+        <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.393923387347549</v>
+        <v>3.29072316411456</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.543768126474678</v>
+        <v>-2.41083659401257</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.37605971244393</v>
+        <v>2.326032102195785</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9464207112015368</v>
+        <v>0.7772918798044688</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.961775814068471</v>
+        <v>3.757098291997242</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971075</v>
+        <v>3.619362241971079</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.460629346938052</v>
+        <v>3.357429123705064</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.563829447751185</v>
+        <v>-2.430897915289076</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.434741143523831</v>
+        <v>2.384713533275686</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.9263593899250298</v>
+        <v>0.7572305585279617</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.016444980893071</v>
+        <v>3.811767458821841</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199802</v>
+        <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.600941065939899</v>
+        <v>3.497740842706911</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.820550265746009</v>
+        <v>-2.6876187332839</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.472364535327749</v>
+        <v>2.422336925079604</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.8179448157812149</v>
+        <v>0.6488159843841469</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.091707955408629</v>
+        <v>3.887030433337399</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622233</v>
+        <v>3.668303164622237</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.669921335085539</v>
+        <v>3.566721111852551</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.974536683522149</v>
+        <v>-2.841605151060041</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.479750237362932</v>
+        <v>2.429722627114788</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.8179448157812149</v>
+        <v>0.6488159843841469</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.160688224554269</v>
+        <v>3.956010702483039</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808525</v>
+        <v>3.619937176808529</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.65597253720566</v>
+        <v>3.552772313972671</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.924014779694483</v>
+        <v>-2.791083247232375</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.486010201014119</v>
+        <v>2.435982590765975</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.8179448157812149</v>
+        <v>0.6488159843841469</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.146739426674389</v>
+        <v>3.94206190460316</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994891</v>
+        <v>3.656346893994893</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.667843026261074</v>
+        <v>3.564642803028085</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.176489933702208</v>
+        <v>-3.0435584012401</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.396890628466444</v>
+        <v>2.346863018218299</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.8179448157812149</v>
+        <v>0.6488159843841469</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.158609915729803</v>
+        <v>3.953932393658574</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.407480912882261</v>
+        <v>3.771019590570411</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.562937844561854</v>
+        <v>3.773602792038294</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.176489933702208</v>
+        <v>-3.0435584012401</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.396890628466444</v>
+        <v>2.346863018218299</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.8179448157812149</v>
+        <v>0.6488159843841469</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.556001641548221</v>
+        <v>3.766666589024661</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240709.xlsx
+++ b/tame_output/ON/bt/strategyON_20240709.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-71.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.9%</t>
+          <t>110.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-629.4%</t>
+          <t>-644.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.5%</t>
+          <t>-50.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-65.2%</t>
+          <t>-66.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.2%</t>
+          <t>457.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-465.9%</t>
+          <t>-480.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-252.1%</t>
+          <t>-258.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.0%</t>
+          <t>-38.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-18.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-141.5%</t>
+          <t>-147.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-13.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-256.6%</t>
+          <t>-263.7%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-28.9%</t>
+          <t>-29.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-112.9%</t>
+          <t>-73.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-159.1%</t>
+          <t>-166.3%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>94.8%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-154.3%</t>
+          <t>-158.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.677837200458727</v>
+        <v>-4.829620226279244</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.240865004535636</v>
+        <v>1.18015179420743</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.3257115125878244</v>
+        <v>-0.3971565031282979</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.91692940148018</v>
+        <v>2.874062407155896</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.01349984768918</v>
+        <v>-5.165282873509696</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.10518053729942</v>
+        <v>1.044467326971214</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.3936424980767292</v>
+        <v>-0.4650874886172027</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.874751401842802</v>
+        <v>2.831884407518518</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.377126092589493</v>
+        <v>-5.528909118410009</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.9662175995735369</v>
+        <v>0.9055043892453303</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.4918641349438551</v>
+        <v>-0.5633091254843285</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.822305979956768</v>
+        <v>2.779438985632484</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.74225347522824</v>
+        <v>-5.894036501048756</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8194211615238696</v>
+        <v>0.7587079511956629</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.7881749192428675</v>
+        <v>-0.859619909783341</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.643774024383192</v>
+        <v>2.600907030058909</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.150842252408918</v>
+        <v>-6.302625278229435</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.6547471946663572</v>
+        <v>0.5940339843381501</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.196763696423546</v>
+        <v>-1.268208686964019</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.397382302089544</v>
+        <v>2.354515307765261</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.42741835272475</v>
+        <v>-6.579201378545267</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.5393021870114847</v>
+        <v>0.478588976683278</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.196763696423546</v>
+        <v>-1.268208686964019</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.392567734561005</v>
+        <v>2.349700740236721</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.843810227011748</v>
+        <v>-6.995593252832265</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.3707394879055634</v>
+        <v>0.3100262775773563</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.196763696423546</v>
+        <v>-1.268208686964019</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.390561785169882</v>
+        <v>2.347694790845599</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.088081627738817</v>
+        <v>-7.239864653559335</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.2832896182834146</v>
+        <v>0.2225764079552075</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.196763696423546</v>
+        <v>-1.268208686964019</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.400820475838561</v>
+        <v>2.357953481514278</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.293332646975577</v>
+        <v>-7.445115672796095</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.1972887757344055</v>
+        <v>0.1365755654061984</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.196763696423546</v>
+        <v>-1.268208686964019</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.396920040984257</v>
+        <v>2.354053046659972</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.456912525159961</v>
+        <v>-7.608695550980478</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.1302617445156531</v>
+        <v>0.069548534187446</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.196763696423546</v>
+        <v>-1.268208686964019</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.395324961039258</v>
+        <v>2.352457966714973</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.753573866970158</v>
+        <v>-7.905356892790675</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.01537618372078242</v>
+        <v>-0.04533702660742467</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.265506832157425</v>
+        <v>-1.336951822697898</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.357858055528139</v>
+        <v>2.314991061203854</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.940293575279461</v>
+        <v>-8.092076601099977</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.06333800413734192</v>
+        <v>-0.1240512144655486</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.265506832157425</v>
+        <v>-1.336951822697898</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.353831750993735</v>
+        <v>2.310964756669451</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.323294964022091</v>
+        <v>-8.475077989842609</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.2166406609559779</v>
+        <v>-0.277353871284185</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.265506832157425</v>
+        <v>-1.336951822697898</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.353729649672151</v>
+        <v>2.310862655347867</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.505164755007126</v>
+        <v>-8.656947780827643</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.2868170613785619</v>
+        <v>-0.3475302717067685</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.44737662314246</v>
+        <v>-1.518821613682933</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.24717929105256</v>
+        <v>2.204312296728276</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.864695077511128</v>
+        <v>-9.016478103331645</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.4252788870821123</v>
+        <v>-0.4859920974103193</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.44737662314246</v>
+        <v>-1.518821613682933</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.252529594350611</v>
+        <v>2.209662600026327</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.91504414096535</v>
+        <v>-9.066827166785867</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.4375024925066238</v>
+        <v>-0.4982157028348304</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.497725686596682</v>
+        <v>-1.569170677137155</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.230236176235255</v>
+        <v>2.187369181910971</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.012663418386746</v>
+        <v>-9.164446444207263</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.4735084528534133</v>
+        <v>-0.5342216631816199</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.595344964018078</v>
+        <v>-1.666789954558552</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.174706360404186</v>
+        <v>2.131839366079902</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.160189506392388</v>
+        <v>-9.311972532212906</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.5296253317340982</v>
+        <v>-0.5903385420623048</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.742871052023722</v>
+        <v>-1.814316042564195</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.089084263922372</v>
+        <v>2.046217269598088</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.364447681722252</v>
+        <v>-9.516230707542769</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.6058154047474011</v>
+        <v>-0.6665286150756082</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.870509996637711</v>
+        <v>-1.941954987178184</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.018014094272621</v>
+        <v>1.975147099948336</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.398100520230726</v>
+        <v>-9.549883546051243</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.6147939856663545</v>
+        <v>-0.6755071959945615</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.970923364554748</v>
+        <v>-2.042368355095221</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.962248628006835</v>
+        <v>1.91938163368255</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.324630688563277</v>
+        <v>-9.476413714383794</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.5700343515059538</v>
+        <v>-0.6307475618341609</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.8974535328873</v>
+        <v>-1.968898523427773</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.021702228500724</v>
+        <v>1.978835234176441</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.49975510594982</v>
+        <v>-9.651538131770337</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.6255288977130542</v>
+        <v>-0.6862421080412613</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.072577950273844</v>
+        <v>-2.144022940814317</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.931182798816315</v>
+        <v>1.888315804492031</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.73420719996431</v>
+        <v>-9.885990225784827</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.7265289002204462</v>
+        <v>-0.7872421105486533</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.072577950273844</v>
+        <v>-2.144022940814317</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.923963633914719</v>
+        <v>1.881096639590435</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.838581930990756</v>
+        <v>-9.990364956811273</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.774950983405001</v>
+        <v>-0.8356641937332081</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.17695268130029</v>
+        <v>-2.248397671840763</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.854666604524875</v>
+        <v>1.811799610200591</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.891368086591083</v>
+        <v>-10.0431511124116</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.7949496558065752</v>
+        <v>-0.8556628661347823</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.272628167882687</v>
+        <v>-2.34407315842316</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.798377102413993</v>
+        <v>1.75551010808971</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.01740487995937</v>
+        <v>-10.16918790577989</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.8426706445247762</v>
+        <v>-0.9033838548529833</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.247376545072944</v>
+        <v>-2.318821535613417</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.816221804728954</v>
+        <v>1.77335481040467</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.960333108063441</v>
+        <v>-10.11211613388396</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.8158516000800033</v>
+        <v>-0.87656481040821</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.247376545072944</v>
+        <v>-2.318821535613417</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.820212140415354</v>
+        <v>1.777345146091071</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.10200494978756</v>
+        <v>-10.25378797560808</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.8739955636683927</v>
+        <v>-0.9347087739965998</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.247376545072944</v>
+        <v>-2.318821535613417</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.818736913516613</v>
+        <v>1.775869919192329</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.05241410536273</v>
+        <v>-10.20419713118324</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.8391058157335869</v>
+        <v>-0.899819026061794</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.19778570064811</v>
+        <v>-2.269230691188584</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.863544830336385</v>
+        <v>1.820677836012101</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.903495770890871</v>
+        <v>-10.05527879671139</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.7925896155915275</v>
+        <v>-0.8533028259197342</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.166536109912937</v>
+        <v>-2.23798110045341</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.869243451130806</v>
+        <v>1.826376456806522</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.677650618171459</v>
+        <v>-9.829433643991976</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.6926724814675542</v>
+        <v>-0.7533856917957609</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.124609434325774</v>
+        <v>-2.196054424866247</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.903978529519313</v>
+        <v>1.861111535195029</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.553071961833867</v>
+        <v>-9.704854987654384</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.6417018743764582</v>
+        <v>-0.7024150847046653</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.124609434325774</v>
+        <v>-2.196054424866247</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.905117674075372</v>
+        <v>1.862250679751088</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.605967249878153</v>
+        <v>-9.757750275698671</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.6602262154320653</v>
+        <v>-0.7209394257602724</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.119654088237327</v>
+        <v>-2.191099078777801</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.910724655890547</v>
+        <v>1.867857661566263</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.533834074590272</v>
+        <v>-9.68561710041079</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.6256392410782765</v>
+        <v>-0.6863524514064832</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.119654088237327</v>
+        <v>-2.191099078777801</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.916458360129184</v>
+        <v>1.8735913658049</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.462467681980625</v>
+        <v>-9.614250707801142</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.6068299464282827</v>
+        <v>-0.6675431567564898</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.04828769562768</v>
+        <v>-2.119732686168153</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.949540933301107</v>
+        <v>1.906673938976823</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.3690086479954</v>
+        <v>-9.520791673815918</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.5793298141471004</v>
+        <v>-0.6400430244753075</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.04828769562768</v>
+        <v>-2.119732686168153</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.939657451988199</v>
+        <v>1.896790457663916</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.101766847127003</v>
+        <v>-9.25354987294752</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.4742676542991151</v>
+        <v>-0.5349808646273222</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.04828769562768</v>
+        <v>-2.119732686168153</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.937822891488826</v>
+        <v>1.894955897164542</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.003859808450512</v>
+        <v>-9.155642834271029</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.4354051538019799</v>
+        <v>-0.4961183641301865</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.980301945767123</v>
+        <v>-2.051746936307596</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.978314026431699</v>
+        <v>1.935447032107415</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.80082935409724</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.979906267474554</v>
+        <v>-9.131689293295072</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.4251552312661029</v>
+        <v>-0.48586844159431</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.956348404791165</v>
+        <v>-2.027793395331639</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.993354657162767</v>
+        <v>1.950487662838483</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017768</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.715846329151757</v>
+        <v>-8.867629354972275</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.3327915720987362</v>
+        <v>-0.3935047824269433</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.692288466468369</v>
+        <v>-1.763733457008843</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.138530303994693</v>
+        <v>2.095663309670408</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.00876670564692</v>
+        <v>-8.160549731467437</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.0527467563571018</v>
+        <v>-0.1134599666853093</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.692288466468369</v>
+        <v>-1.763733457008843</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.135743270334392</v>
+        <v>2.092876276010108</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.96858240728073</v>
+        <v>-8.120365433101247</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.03632941312278426</v>
+        <v>-0.09704262345099179</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.652104168102178</v>
+        <v>-1.723549158642652</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.160197473241948</v>
+        <v>2.117330478917664</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.805182536341367</v>
+        <v>-7.956965562161884</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.02839735647371766</v>
+        <v>-0.03231585385448987</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.488704297162816</v>
+        <v>-1.56014928770329</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.257604217026322</v>
+        <v>2.214737222702038</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.571701314111769</v>
+        <v>-7.723484339932286</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.1297142742034092</v>
+        <v>0.06900106387520211</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.255223074933217</v>
+        <v>-1.326668065473691</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.405617379201934</v>
+        <v>2.362750384877649</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.422034923104254</v>
+        <v>-7.573817948924771</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.1866886202934563</v>
+        <v>0.1259754099652488</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.162319583690681</v>
+        <v>-1.233764574231155</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.458467263634496</v>
+        <v>2.415600269310212</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390426</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.289759449473367</v>
+        <v>-7.441542475293884</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2349662964928378</v>
+        <v>0.1742530861646308</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.030044110059795</v>
+        <v>-1.101489100600269</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.533200034560055</v>
+        <v>2.490333040235771</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.78471879410595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.134021116913625</v>
+        <v>-7.285804142734142</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3000766902043712</v>
+        <v>0.2393634798761641</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.8743057775000532</v>
+        <v>-0.9457507680405269</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.629458094783537</v>
+        <v>2.586591100459253</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.885021318230044</v>
+        <v>-7.036804344050561</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4125829509014625</v>
+        <v>0.3518697405732554</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.8743057775000532</v>
+        <v>-0.9457507680405269</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.642364436007195</v>
+        <v>2.599497441682911</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.990611308003149</v>
+        <v>-7.142394333823666</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2423710253930018</v>
+        <v>0.1816578150647947</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.9798957672731576</v>
+        <v>-1.051340757813631</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.451034512544114</v>
+        <v>2.40816751821983</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.009346210121746</v>
+        <v>-7.161129235942263</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2834214064226495</v>
+        <v>0.2227081960944424</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.9854917769332889</v>
+        <v>-1.056936767473763</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.496221248625122</v>
+        <v>2.453354254300837</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.861406168714146</v>
+        <v>-7.013189194534664</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2227185002975216</v>
+        <v>0.1620052899693145</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.9651708610247314</v>
+        <v>-1.036615851565205</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.388534875482089</v>
+        <v>2.345667881157804</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.808436646460158</v>
+        <v>-6.960219672280675</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2351923229456387</v>
+        <v>0.1744791126174317</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.9122013387707425</v>
+        <v>-0.9836463293112162</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.411602602581004</v>
+        <v>2.36873560825672</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.764888239689467</v>
+        <v>-6.916671265509985</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2456510735588218</v>
+        <v>0.1849378632306147</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.9122013387707425</v>
+        <v>-0.9836463293112162</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.404641990485911</v>
+        <v>2.361774996161627</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.522739846235609</v>
+        <v>-6.674522872056126</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3569727853215081</v>
+        <v>0.296259574993301</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.9122013387707425</v>
+        <v>-0.9836463293112162</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.419104344867054</v>
+        <v>2.37623735054277</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.414480709113088</v>
+        <v>-6.566263734933605</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3948085606297118</v>
+        <v>0.3340953503015047</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.9122013387707425</v>
+        <v>-0.9836463293112162</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.413636465326249</v>
+        <v>2.370769471001965</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.291189574295957</v>
+        <v>-6.442972600116474</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4416231085671414</v>
+        <v>0.3809098982389338</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.788910203953612</v>
+        <v>-0.8603551944940857</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.485109240227104</v>
+        <v>2.44224224590282</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.270040375392513</v>
+        <v>-6.421823401213031</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4577837663658437</v>
+        <v>0.3970705560376366</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.7677610050501686</v>
+        <v>-0.8392059955906424</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.505499737806495</v>
+        <v>2.462632743482211</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.026274933409069</v>
+        <v>-6.178057959229586</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5510706515062722</v>
+        <v>0.4903574411780647</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.7677610050501686</v>
+        <v>-0.8392059955906424</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.501280446153546</v>
+        <v>2.458413451829262</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.924512113131774</v>
+        <v>-6.076295138952291</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5939000935372061</v>
+        <v>0.533186883208999</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.7545419366577399</v>
+        <v>-0.8259869271982136</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.511336201109019</v>
+        <v>2.468469206784735</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.6746617191827</v>
+        <v>-5.826444745003217</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6865823261005382</v>
+        <v>0.6258691157723311</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.7545419366577399</v>
+        <v>-0.8259869271982136</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.504078276092721</v>
+        <v>2.461211281768437</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.498769626715267</v>
+        <v>-5.650552652535785</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7605382866081603</v>
+        <v>0.6998250762799523</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.7545419366577399</v>
+        <v>-0.8259869271982136</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.50767739961337</v>
+        <v>2.464810405289086</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.327323163692803</v>
+        <v>-5.479106189513321</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8424443778716992</v>
+        <v>0.7817311675434917</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.5830954736352768</v>
+        <v>-0.6545404641757505</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.623872783481402</v>
+        <v>2.581005789157117</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.253033597954464</v>
+        <v>-5.404816623774982</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8711806817833319</v>
+        <v>0.8104674714551243</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.5088059078969376</v>
+        <v>-0.5802508984374113</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.667467000540702</v>
+        <v>2.624600006216418</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.18939785572053</v>
+        <v>-5.341180881541048</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9013297797312227</v>
+        <v>0.8406165694030152</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.445170165663003</v>
+        <v>-0.5166151562034768</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.71034324693538</v>
+        <v>2.667476252611096</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.077971096394609</v>
+        <v>-5.229754122215128</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9270947422453863</v>
+        <v>0.8663815319171788</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.445170165663003</v>
+        <v>-0.5166151562034768</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.691537505719176</v>
+        <v>2.648670511394891</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.837540599589749</v>
+        <v>-4.989323625410267</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.025010017592208</v>
+        <v>0.9642968072640004</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.2047396688581428</v>
+        <v>-0.2761846593986165</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.837538880426969</v>
+        <v>2.794671886102685</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.765298031418554</v>
+        <v>-4.917081057239073</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.057836358695506</v>
+        <v>0.9971231483672984</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.2047396688581428</v>
+        <v>-0.2761846593986165</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.84146819426179</v>
+        <v>2.798601199937505</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.712299709137167</v>
+        <v>-4.864082734957685</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.079714271525401</v>
+        <v>1.019001061197194</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.1494034098562039</v>
+        <v>-0.2208484003966776</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.875348533580293</v>
+        <v>2.832481539256008</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.60349482365744</v>
+        <v>-4.755277849477958</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.120234296937286</v>
+        <v>1.059521086609078</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.1494034098562039</v>
+        <v>-0.2208484003966776</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.872346604800286</v>
+        <v>2.829479610476002</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.383474025620429</v>
+        <v>-4.535257051440947</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.209821653162704</v>
+        <v>1.149108442834496</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.008183564788223685</v>
+        <v>-0.07962855532869739</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.958657548851689</v>
+        <v>2.915790554527404</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.250606336557151</v>
+        <v>-4.40238936237767</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.278862911589838</v>
+        <v>1.218149701261631</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.008183564788223685</v>
+        <v>-0.07962855532869739</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.974551731653512</v>
+        <v>2.931684737329228</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.130433253192653</v>
+        <v>-4.282216279013171</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.32807798937594</v>
+        <v>1.267364779047732</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.1119895185762753</v>
+        <v>0.04054452803580155</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.047801426112513</v>
+        <v>3.004934431788229</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.985761108092915</v>
+        <v>-4.137544133913433</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.396034949977274</v>
+        <v>1.335321739649067</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.2566616636760127</v>
+        <v>0.185216673135539</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.144692815733795</v>
+        <v>3.101825821409511</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.7358392229421</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.045635935450608</v>
+        <v>-4.197418961271126</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.358122510435623</v>
+        <v>1.297409300107416</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.1967868363183206</v>
+        <v>0.1253418457778468</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.094805410720606</v>
+        <v>3.051938416396322</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.92581570453977</v>
+        <v>-4.077598730360289</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.421339772034167</v>
+        <v>1.360626561705959</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.1967868363183206</v>
+        <v>0.1253418457778468</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.110094579954815</v>
+        <v>3.06722758563053</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.72914639843069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.928285411001576</v>
+        <v>-4.080068436822095</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.327996088771886</v>
+        <v>1.267282878443678</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.1943171298565144</v>
+        <v>0.1228721393160407</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.016256955400172</v>
+        <v>2.973389961075888</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.996655597325586</v>
+        <v>-4.148438623146105</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.219909875727583</v>
+        <v>1.159196665399375</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.2035928288927293</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.941084236307203</v>
+        <v>2.898217241982918</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.010443650172633</v>
+        <v>-4.162226675993152</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.204831363220656</v>
+        <v>1.144118152892448</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.2035928288927293</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.931520944939094</v>
+        <v>2.88865395061481</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.819714480922205</v>
+        <v>-3.964159576340736</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.105832595961214</v>
+        <v>1.048054557793801</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.2035928288927293</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.756230509979481</v>
+        <v>2.713363515655197</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.644240221129736</v>
+        <v>-3.788685316548266</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.180589531869989</v>
+        <v>1.122811493702577</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.2035928288927293</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.760797741971269</v>
+        <v>2.717930747646984</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.755176473770985</v>
+        <v>-3.899621569189515</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.111957059574697</v>
+        <v>1.054179021407285</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.2035928288927293</v>
+        <v>0.1321478383522556</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.736539770732476</v>
+        <v>2.693672776408191</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.721512928298703</v>
+        <v>-3.865958023717233</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.128553862983515</v>
+        <v>1.070775824816103</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.2372563743650112</v>
+        <v>0.1658113838245375</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.75986928323575</v>
+        <v>2.717002288911466</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.66166030909498</v>
+        <v>-3.80610540451351</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.162667297097137</v>
+        <v>1.104889258929724</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.2372563743650112</v>
+        <v>0.1658113838245375</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.770041669667882</v>
+        <v>2.727174675343599</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.575416846068602</v>
+        <v>-3.719861941487133</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.192110952881548</v>
+        <v>1.134332914714136</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.2372563743650112</v>
+        <v>0.1658113838245375</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.764987940241743</v>
+        <v>2.722120945917459</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.620723665467582</v>
+        <v>-3.765168760886112</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.165764000566482</v>
+        <v>1.107985962399069</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.1964462113557804</v>
+        <v>0.1250012208153067</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.73227761788073</v>
+        <v>2.689410623556446</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.649756770169884</v>
+        <v>-3.794201865588414</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.154702631718663</v>
+        <v>1.09692459355125</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.1964462113557804</v>
+        <v>0.1250012208153067</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.732829490913832</v>
+        <v>2.689962496589547</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.556946288719025</v>
+        <v>-3.701391384137555</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.121099516190372</v>
+        <v>1.06332147802296</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.2892566928066397</v>
+        <v>0.217811702266166</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.717788471675713</v>
+        <v>2.674921477351428</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.601335758048452</v>
+        <v>-3.745780853466982</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.105217204383202</v>
+        <v>1.047439166215789</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.2448672234772121</v>
+        <v>0.1734222329367384</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.693028266002657</v>
+        <v>2.650161271678373</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.488664539812202</v>
+        <v>-3.633109635230732</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.145361400189425</v>
+        <v>1.087583362022012</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.3575384417134623</v>
+        <v>0.2860934511729886</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.75570670545613</v>
+        <v>2.712839711131846</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.376287538629529</v>
+        <v>-3.52073263404806</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.195803496493161</v>
+        <v>1.138025458325749</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.3575384417134623</v>
+        <v>0.2860934511729886</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.761198001286798</v>
+        <v>2.718331006962513</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.404067936530883</v>
+        <v>-3.548513031949413</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.196188539101159</v>
+        <v>1.138410500933746</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.3297580438121092</v>
+        <v>0.2583130532716355</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.756026964314525</v>
+        <v>2.71315996999024</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.487069217556162</v>
+        <v>-3.631514312974692</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.001343746691701</v>
+        <v>0.9435657085242881</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3111871592849355</v>
+        <v>0.2397421687444617</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.583240153598874</v>
+        <v>2.540373159274589</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.595683295999493</v>
+        <v>-3.740128391418023</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.078047776033574</v>
+        <v>1.020269737866161</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3111871592849355</v>
+        <v>0.2397421687444617</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.703389814318079</v>
+        <v>2.660522819993795</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.56027425775135</v>
+        <v>-3.70471935316988</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.106724417435154</v>
+        <v>1.048946379267742</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3111871592849355</v>
+        <v>0.2397421687444617</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.717902840420402</v>
+        <v>2.675035846096118</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.521890595193199</v>
+        <v>-3.666335690611729</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.119497323800783</v>
+        <v>1.061719285633371</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.3495708218430866</v>
+        <v>0.2781258313026129</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.738352479297662</v>
+        <v>2.695485484973378</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.344774265158033</v>
+        <v>-3.489219360576563</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.187072884660152</v>
+        <v>1.129294846492739</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.3495708218430866</v>
+        <v>0.2781258313026129</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.735081508142964</v>
+        <v>2.69221451381868</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.389866509991578</v>
+        <v>-3.534311605410108</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.169719378488647</v>
+        <v>1.111941340321234</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.2876747786736968</v>
+        <v>0.2162297881332231</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.698627274003243</v>
+        <v>2.655760279678959</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.210491088752811</v>
+        <v>-3.354936184171341</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.235256522290568</v>
+        <v>1.177478484123156</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.4444515368444155</v>
+        <v>0.3730065463039418</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.786480304212089</v>
+        <v>2.743613309887805</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.255505302273417</v>
+        <v>-3.399950397691947</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.198058292213915</v>
+        <v>1.140280254046503</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4141026415298109</v>
+        <v>0.3426576509893372</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.749078422354916</v>
+        <v>2.706211428030632</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.522509812545852</v>
+        <v>-3.666954907964382</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.096948050443887</v>
+        <v>1.039170012276474</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2197396034868623</v>
+        <v>0.1482946129463886</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.638152161868093</v>
+        <v>2.595285167543808</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.623707593983025</v>
+        <v>-3.768152689401555</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.055672859765519</v>
+        <v>0.9978948215981069</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.1513307899415431</v>
+        <v>0.07988579940106943</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.596310795637403</v>
+        <v>2.553443801313118</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.617196627368712</v>
+        <v>-3.761641722787243</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.055877207965561</v>
+        <v>0.9980991697981487</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.1513307899415431</v>
+        <v>0.07988579940106943</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.593910757191719</v>
+        <v>2.551043762867435</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.598158499661415</v>
+        <v>-3.742603595079945</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.060017178256725</v>
+        <v>1.002239140089312</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.0931471786103486</v>
+        <v>0.02170218806987489</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.555525309601247</v>
+        <v>2.512658315276963</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.629285130812033</v>
+        <v>-3.773730226230563</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.225148394735158</v>
+        <v>1.167370356567746</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.0931471786103486</v>
+        <v>0.02170218806987489</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.733107178539928</v>
+        <v>2.690240184215644</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.64315189214595</v>
+        <v>-3.787596987564481</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.220435019187725</v>
+        <v>1.162656981020312</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.05528926187652566</v>
+        <v>-0.01615572866394804</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.711225757485768</v>
+        <v>2.668358763161483</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.598347720606021</v>
+        <v>-3.742792816024551</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.244365218200623</v>
+        <v>1.18658718003321</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.05528926187652566</v>
+        <v>-0.01615572866394804</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.717234287882694</v>
+        <v>2.674367293558409</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.582010952033977</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.450604750371018</v>
+        <v>-3.595049845789549</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.201412627571823</v>
+        <v>1.143634589404411</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2230966191114088</v>
+        <v>0.1516516285709351</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.715868923500823</v>
+        <v>2.673001929176539</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.584804573565458</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.552619432902239</v>
+        <v>-3.697064528320769</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.163400376090816</v>
+        <v>1.105622337923403</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2230966191114088</v>
+        <v>0.1516516285709351</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.718662545032304</v>
+        <v>2.67579555070802</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.585466921957117</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.546466726849455</v>
+        <v>-3.690911822267985</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.166523806903588</v>
+        <v>1.108745768736175</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2292493251641931</v>
+        <v>0.1578043346237194</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.723016517055633</v>
+        <v>2.680149522731349</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.584547398697227</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.563276024999956</v>
+        <v>-3.707721120418487</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.158880564383497</v>
+        <v>1.101102526216085</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2124400270136915</v>
+        <v>0.1409950364732178</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.712011414905442</v>
+        <v>2.669144420581158</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.650882952494048</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.500978026223835</v>
+        <v>-3.645423121642365</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.250135317690767</v>
+        <v>1.192357279523355</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2124400270136915</v>
+        <v>0.1409950364732178</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.778346968702263</v>
+        <v>2.735479974377979</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.453174954208175</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.299187828558677</v>
+        <v>-3.443632923977207</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.133143398470957</v>
+        <v>1.075365360303545</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4104582191828459</v>
+        <v>0.3390132286423722</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.699449885717883</v>
+        <v>2.656582891393598</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
         <v>2.52346518653035</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.22580973146994</v>
+        <v>-3.37025482688847</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.232784869628627</v>
+        <v>1.175006831461215</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4838363162715824</v>
+        <v>0.4123913257311087</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.8137669762933</v>
+        <v>2.770899981969015</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.538092922646394</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.323550276094914</v>
+        <v>-3.467995371513445</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.208316387894681</v>
+        <v>1.150538349727269</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.4679470381386022</v>
+        <v>0.3965020475981285</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.818861145529556</v>
+        <v>2.775994151205271</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.536628903471065</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.499888036217844</v>
+        <v>-3.644333131636374</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.136317264670181</v>
+        <v>1.078539226502769</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.2916092780156728</v>
+        <v>0.2201642874751991</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.71159447028047</v>
+        <v>2.668727475956185</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.535120521510994</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.423465989785917</v>
+        <v>-3.567911085204447</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.16537770128288</v>
+        <v>1.107599663115468</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.2916092780156728</v>
+        <v>0.2201642874751991</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.710086088320398</v>
+        <v>2.667219093996114</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.53498338894643</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.379092858147348</v>
+        <v>-3.523537953565878</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.182989821373744</v>
+        <v>1.125211783206332</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.3359824096542414</v>
+        <v>0.2645374191137677</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.736572834738976</v>
+        <v>2.693705840414691</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.529377183085021</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.256258637260181</v>
+        <v>-3.400703732678711</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.226517303867201</v>
+        <v>1.168739265699789</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.3359824096542414</v>
+        <v>0.2645374191137677</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.730966628877566</v>
+        <v>2.688099634553282</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
         <v>2.535758940112825</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.208602906699126</v>
+        <v>-3.353048002117656</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.251961353119428</v>
+        <v>1.194183314952016</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.3836381402152971</v>
+        <v>0.3121931496748234</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.765941824242004</v>
+        <v>2.723074829917719</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
         <v>2.54065131348755</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.108084748200371</v>
+        <v>-3.252529843618901</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.297060989893655</v>
+        <v>1.239282951726242</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.4841562987140516</v>
+        <v>0.4127113081735779</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.831145092715981</v>
+        <v>2.788278098391697</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.82880887755729</v>
       </c>
       <c r="C1980" t="n">
         <v>2.527405985963422</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.16875133860276</v>
+        <v>-3.31319643402129</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.259549026208572</v>
+        <v>1.201770988041159</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.402457981995518</v>
+        <v>0.3310129914550443</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.768880775160734</v>
+        <v>2.726013780836449</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.531503688574051</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.123912936994362</v>
+        <v>-3.268358032412892</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.281582089462559</v>
+        <v>1.223804051295147</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4070014149403874</v>
+        <v>0.3355564243999137</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.775704537538284</v>
+        <v>2.732837543214</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.81793235491705</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.535664628205129</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.22467157275136</v>
+        <v>-3.369116668169891</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.245439574790838</v>
+        <v>1.187661536623426</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.318175846213382</v>
+        <v>0.2467308556729083</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.726570135933159</v>
+        <v>2.683703141608874</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
         <v>2.541544230732966</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.18046873566546</v>
+        <v>-3.32491383108399</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.269000312153035</v>
+        <v>1.211222273985623</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.3623786832992825</v>
+        <v>0.2909336927588088</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.758971440712536</v>
+        <v>2.716104446388252</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.539954231202214</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.217447763328903</v>
+        <v>-3.361892858747433</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.252618701556905</v>
+        <v>1.194840663389493</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.399352585090613</v>
+        <v>0.3279075945501393</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.779565782256582</v>
+        <v>2.736698787932298</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.591201996385253</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.059156345789631</v>
+        <v>-3.203601441208161</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.367183033755654</v>
+        <v>1.309404995588242</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.399352585090613</v>
+        <v>0.3279075945501393</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.830813547439621</v>
+        <v>2.787946553115337</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321018</v>
       </c>
       <c r="C1986" t="n">
         <v>2.589642700979506</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.851514342155155</v>
+        <v>-2.995959437573685</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.448680539803698</v>
+        <v>1.390902501636285</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.6069945887250892</v>
+        <v>0.5355495981846154</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.95383945421456</v>
+        <v>2.910972459890276</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.584590929217776</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.800482249432627</v>
+        <v>-2.944927344851157</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.464041605130979</v>
+        <v>1.406263566963567</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.6580266814476171</v>
+        <v>0.5865816909071434</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.979406938086347</v>
+        <v>2.936539943762063</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
         <v>2.601778333310481</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.735258068305421</v>
+        <v>-2.879703163723951</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.507318681674566</v>
+        <v>1.449540643507154</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.7232508625748227</v>
+        <v>0.651805872034349</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.035728850855375</v>
+        <v>2.992861856531091</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882557</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
         <v>2.597739305609762</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.697831048234287</v>
+        <v>-2.842276143652817</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.5182504620023</v>
+        <v>1.460472423834888</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.7285024006040044</v>
+        <v>0.6570574100635307</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.034840745972164</v>
+        <v>2.991973751647881</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
         <v>2.598996097941002</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.717942704268995</v>
+        <v>-2.862387799687526</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.511462591919657</v>
+        <v>1.453684553752245</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.7395297456014236</v>
+        <v>0.6680847550609499</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.042713945301856</v>
+        <v>2.999846950977572</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
         <v>2.759553868962213</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.664197889841791</v>
+        <v>-2.808642985260321</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.69351828871175</v>
+        <v>1.635740250544337</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.7495930550418856</v>
+        <v>0.6781480645014119</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.209309701987344</v>
+        <v>3.16644270766306</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957621</v>
       </c>
       <c r="C1992" t="n">
         <v>2.87966677818003</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.640406321235648</v>
+        <v>-2.784851416654178</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.823147825372024</v>
+        <v>1.765369787204611</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.7733846236480278</v>
+        <v>0.7019396331075541</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.343697552368847</v>
+        <v>3.300830558044563</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>2.871374754193889</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.61432223697184</v>
+        <v>-2.758767332390371</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.825289435091406</v>
+        <v>1.767511396923994</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.7733846236480278</v>
+        <v>0.7019396331075541</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.335405528382706</v>
+        <v>3.292538534058422</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896924</v>
       </c>
       <c r="C1994" t="n">
         <v>2.869567949777668</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.536191056122894</v>
+        <v>-2.680636151541424</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.854735103014764</v>
+        <v>1.796957064847352</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.8475614345317124</v>
+        <v>0.7761164439912387</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.378104810496696</v>
+        <v>3.335237816172412</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959853</v>
       </c>
       <c r="C1995" t="n">
         <v>2.88712235550446</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.52729859472961</v>
+        <v>-2.671743690148141</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.875846493298869</v>
+        <v>1.818068455131456</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.8475614345317124</v>
+        <v>0.7761164439912387</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.395659216223487</v>
+        <v>3.352792221899203</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
         <v>2.878977402909044</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.695774711699488</v>
+        <v>-2.840219807118018</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.800311093915502</v>
+        <v>1.742533055748089</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.8196135988151316</v>
+        <v>0.7481686082746579</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.370745562198123</v>
+        <v>3.327878567873839</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782703</v>
       </c>
       <c r="C1997" t="n">
         <v>2.860247100096906</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.997975182837905</v>
+        <v>-2.142420278256435</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.060700602647997</v>
+        <v>2.002922564480584</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.749265539444721</v>
+        <v>0.6778205489042473</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.309806423763738</v>
+        <v>3.266939429439454</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632631</v>
       </c>
       <c r="C1998" t="n">
         <v>2.85091112259381</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.975254079154753</v>
+        <v>-2.119699174573283</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.060453066618162</v>
+        <v>2.00267502845075</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.749265539444721</v>
+        <v>0.6778205489042473</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.300470446260643</v>
+        <v>3.257603451936359</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
         <v>3.009817248444979</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.973529035864709</v>
+        <v>-2.117974131283239</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.220049209785349</v>
+        <v>2.162271171617936</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.7509905827347647</v>
+        <v>0.679545592194291</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.460411598085838</v>
+        <v>3.417544603761554</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
         <v>3.046895070938626</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.128310042642964</v>
+        <v>-2.272755138061494</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.195214629567693</v>
+        <v>2.137436591400281</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7176229086802886</v>
+        <v>0.6461779181398148</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.477468816146799</v>
+        <v>3.434601821822515</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
         <v>3.043570426928171</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.076874709258305</v>
+        <v>-2.221319804676834</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.212464118911102</v>
+        <v>2.15468608074369</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7690582420649482</v>
+        <v>0.6976132515244745</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.50500537216714</v>
+        <v>3.462138377842856</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>3.053576580572912</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.049923484931817</v>
+        <v>-2.194368580350346</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.233250762286439</v>
+        <v>2.175472724119027</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.7839385880926674</v>
+        <v>0.7124935975521937</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.523939733428513</v>
+        <v>3.481072739104229</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784103</v>
       </c>
       <c r="C2003" t="n">
         <v>3.237679712717872</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.185876492988132</v>
+        <v>-2.330321588406663</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.362972691208872</v>
+        <v>2.30519465304146</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.7839385880926674</v>
+        <v>0.7124935975521937</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.708042865573473</v>
+        <v>3.665175871249189</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.229796407620865</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.208284610793005</v>
+        <v>-2.352729706211535</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.346126138989917</v>
+        <v>2.288348100822504</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.7839385880926674</v>
+        <v>0.7124935975521937</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.700159560476466</v>
+        <v>3.657292566152182</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
         <v>3.231850407170503</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.356290378272404</v>
+        <v>-2.500735473690934</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.288977831547794</v>
+        <v>2.231199793380382</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.6972115792291259</v>
+        <v>0.6257665886886522</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.650177354707979</v>
+        <v>3.607310360383694</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161973</v>
       </c>
       <c r="C2006" t="n">
         <v>3.28810412489235</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.365731304160934</v>
+        <v>-2.510176399579464</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.341455178914229</v>
+        <v>2.283677140746817</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.8196386967725173</v>
+        <v>0.7481937062320436</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.779887342955861</v>
+        <v>3.737020348631576</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
         <v>3.290995219437651</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.364444540621378</v>
+        <v>-2.508889636039908</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.344860978875353</v>
+        <v>2.287082940707941</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.8209254603120739</v>
+        <v>0.7494804697716002</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.783550495624895</v>
+        <v>3.740683501300611</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347699</v>
       </c>
       <c r="C2008" t="n">
         <v>3.289107032331426</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.366001594610669</v>
+        <v>-2.510446690029199</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.342349970173411</v>
+        <v>2.284571932005999</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.8209254603120739</v>
+        <v>0.7494804697716002</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.78166230851867</v>
+        <v>3.738795314194387</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
         <v>3.283927261934288</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.373273480134134</v>
+        <v>-2.517718575552664</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.334261445566888</v>
+        <v>2.276483407399476</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8136535747886091</v>
+        <v>0.7422085842481354</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.772119406807454</v>
+        <v>3.72925241248317</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.282361272144441</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.371432461075882</v>
+        <v>-2.515877556494412</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.333431863400341</v>
+        <v>2.275653825232928</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8149218014600775</v>
+        <v>0.7434768109196038</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.771314353020487</v>
+        <v>3.728447358696203</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647105</v>
+        <v>3.754911907647101</v>
       </c>
       <c r="C2011" t="n">
         <v>3.295434679010359</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.378341166575563</v>
+        <v>-2.522786261994093</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.343741788066387</v>
+        <v>2.285963749898975</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8149218014600775</v>
+        <v>0.7434768109196038</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.784387759886406</v>
+        <v>3.741520765562122</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.749896851763528</v>
       </c>
       <c r="C2012" t="n">
         <v>3.295434679010359</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.379902809390423</v>
+        <v>-2.524347904808953</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.343117130940443</v>
+        <v>2.285339092773031</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8149218014600775</v>
+        <v>0.7434768109196038</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.784387759886406</v>
+        <v>3.741520765562122</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392111</v>
       </c>
       <c r="C2013" t="n">
         <v>3.293958720137361</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.407803596499896</v>
+        <v>-2.552248691918426</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.330480857223656</v>
+        <v>2.272702819056244</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7803248773171427</v>
+        <v>0.708879886776669</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.762153646527647</v>
+        <v>3.719286652203363</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.684909939172523</v>
       </c>
       <c r="C2014" t="n">
         <v>3.29072316411456</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.41083659401257</v>
+        <v>-2.5552816894311</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.326032102195785</v>
+        <v>2.268254064028373</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7772918798044688</v>
+        <v>0.7058468892639951</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.757098291997242</v>
+        <v>3.714231297672957</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971079</v>
+        <v>3.619362241971075</v>
       </c>
       <c r="C2015" t="n">
         <v>3.357429123705064</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.430897915289076</v>
+        <v>-2.575343010707607</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.384713533275686</v>
+        <v>2.326935495108274</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.7572305585279617</v>
+        <v>0.685785567987488</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.811767458821841</v>
+        <v>3.768900464497557</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.640764248199802</v>
       </c>
       <c r="C2016" t="n">
         <v>3.497740842706911</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.6876187332839</v>
+        <v>-2.83206382870243</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.422336925079604</v>
+        <v>2.364558886912191</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.6488159843841469</v>
+        <v>0.5773709938436732</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.887030433337399</v>
+        <v>3.844163439013115</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622237</v>
+        <v>3.668303164622233</v>
       </c>
       <c r="C2017" t="n">
         <v>3.566721111852551</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.841605151060041</v>
+        <v>-2.986050246478571</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.429722627114788</v>
+        <v>2.371944588947375</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.6488159843841469</v>
+        <v>0.5773709938436732</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.956010702483039</v>
+        <v>3.913143708158755</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808529</v>
+        <v>3.619937176808525</v>
       </c>
       <c r="C2018" t="n">
         <v>3.552772313972671</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.791083247232375</v>
+        <v>-2.935528342650905</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.435982590765975</v>
+        <v>2.378204552598562</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.6488159843841469</v>
+        <v>0.5773709938436732</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.94206190460316</v>
+        <v>3.899194910278875</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994893</v>
+        <v>3.65634689399489</v>
       </c>
       <c r="C2019" t="n">
         <v>3.564642803028085</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.0435584012401</v>
+        <v>-3.18800349665863</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.346863018218299</v>
+        <v>2.289084980050886</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.6488159843841469</v>
+        <v>0.5773709938436732</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.953932393658574</v>
+        <v>3.91106539933429</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,19 +48005,19 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.771019590570411</v>
+        <v>3.771019590570408</v>
       </c>
       <c r="C2020" t="n">
         <v>3.773602792038294</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.0435584012401</v>
+        <v>-3.18800349665863</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.346863018218299</v>
+        <v>2.289084980050886</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.6488159843841469</v>
+        <v>0.5773709938436732</v>
       </c>
       <c r="G2020" t="n">
         <v>3.766666589024661</v>

--- a/tame_output/ON/bt/strategyON_20240709.xlsx
+++ b/tame_output/ON/bt/strategyON_20240709.xlsx
@@ -48008,7 +48008,7 @@
         <v>3.771019590570408</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.773602792038294</v>
+        <v>3.773602792038293</v>
       </c>
       <c r="D2020" t="n">
         <v>-3.18800349665863</v>

--- a/tame_output/ON/bt/strategyON_20240709.xlsx
+++ b/tame_output/ON/bt/strategyON_20240709.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.4%</t>
+          <t>-71.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.3%</t>
+          <t>110.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.9%</t>
+          <t>124.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-50.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.1%</t>
+          <t>457.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-480.4%</t>
+          <t>-483.0%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-147.3%</t>
+          <t>-127.5%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-69.4%</t>
+          <t>-34.0%</t>
         </is>
       </c>
     </row>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.229754122215128</v>
+        <v>-5.122940342039185</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8663815319171788</v>
+        <v>0.9091070439875559</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.5166151562034768</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.989323625410267</v>
+        <v>-4.882509845234325</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9642968072640004</v>
+        <v>1.007022319334377</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.2761846593986165</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.917081057239073</v>
+        <v>-4.81026727706313</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9971231483672984</v>
+        <v>1.039848660437675</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.2761846593986165</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.864082734957685</v>
+        <v>-4.757268954781742</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.019001061197194</v>
+        <v>1.06172657326757</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.2208484003966776</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.755277849477958</v>
+        <v>-4.648464069302015</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.059521086609078</v>
+        <v>1.102246598679455</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.2208484003966776</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.535257051440947</v>
+        <v>-4.428443271265005</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.149108442834496</v>
+        <v>1.191833954904873</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.07962855532869739</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.40238936237767</v>
+        <v>-4.295575582201727</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.218149701261631</v>
+        <v>1.260875213332008</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.07962855532869739</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.282216279013171</v>
+        <v>-4.175402498837228</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.267364779047732</v>
+        <v>1.310090291118109</v>
       </c>
       <c r="F1931" t="n">
         <v>0.04054452803580155</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.137544133913433</v>
+        <v>-4.030730353737491</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.335321739649067</v>
+        <v>1.378047251719444</v>
       </c>
       <c r="F1932" t="n">
         <v>0.185216673135539</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.197418961271126</v>
+        <v>-4.090605181095183</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.297409300107416</v>
+        <v>1.340134812177793</v>
       </c>
       <c r="F1933" t="n">
         <v>0.1253418457778468</v>
@@ -46033,10 +46033,10 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.077598730360289</v>
+        <v>-3.970784950184346</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.360626561705959</v>
+        <v>1.403352073776336</v>
       </c>
       <c r="F1934" t="n">
         <v>0.1253418457778468</v>
@@ -46056,10 +46056,10 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.080068436822095</v>
+        <v>-3.973254656646152</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.267282878443678</v>
+        <v>1.310008390514055</v>
       </c>
       <c r="F1935" t="n">
         <v>0.1228721393160407</v>
@@ -46079,10 +46079,10 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.148438623146105</v>
+        <v>-4.041624842970162</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.159196665399375</v>
+        <v>1.201922177469753</v>
       </c>
       <c r="F1936" t="n">
         <v>0.1321478383522556</v>
@@ -46102,10 +46102,10 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.162226675993152</v>
+        <v>-4.055412895817208</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.144118152892448</v>
+        <v>1.186843664962825</v>
       </c>
       <c r="F1937" t="n">
         <v>0.1321478383522556</v>
@@ -46125,10 +46125,10 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.964159576340736</v>
+        <v>-3.857345796164792</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.048054557793801</v>
+        <v>1.090780069864179</v>
       </c>
       <c r="F1938" t="n">
         <v>0.1321478383522556</v>
@@ -46148,10 +46148,10 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.788685316548266</v>
+        <v>-3.681871536372323</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.122811493702577</v>
+        <v>1.165537005772954</v>
       </c>
       <c r="F1939" t="n">
         <v>0.1321478383522556</v>
@@ -46171,10 +46171,10 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.899621569189515</v>
+        <v>-3.792807789013572</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.054179021407285</v>
+        <v>1.096904533477662</v>
       </c>
       <c r="F1940" t="n">
         <v>0.1321478383522556</v>
@@ -46194,10 +46194,10 @@
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.865958023717233</v>
+        <v>-3.75914424354129</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.070775824816103</v>
+        <v>1.11350133688648</v>
       </c>
       <c r="F1941" t="n">
         <v>0.1658113838245375</v>
@@ -46217,10 +46217,10 @@
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.80610540451351</v>
+        <v>-3.699291624337567</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.104889258929724</v>
+        <v>1.147614771000102</v>
       </c>
       <c r="F1942" t="n">
         <v>0.1658113838245375</v>
@@ -46240,10 +46240,10 @@
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.719861941487133</v>
+        <v>-3.613048161311189</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.134332914714136</v>
+        <v>1.177058426784513</v>
       </c>
       <c r="F1943" t="n">
         <v>0.1658113838245375</v>
@@ -46263,10 +46263,10 @@
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.765168760886112</v>
+        <v>-3.658354980710169</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.107985962399069</v>
+        <v>1.150711474469447</v>
       </c>
       <c r="F1944" t="n">
         <v>0.1250012208153067</v>
@@ -46286,10 +46286,10 @@
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.794201865588414</v>
+        <v>-3.687388085412471</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.09692459355125</v>
+        <v>1.139650105621627</v>
       </c>
       <c r="F1945" t="n">
         <v>0.1250012208153067</v>
@@ -46309,10 +46309,10 @@
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.701391384137555</v>
+        <v>-3.594577603961612</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.06332147802296</v>
+        <v>1.106046990093337</v>
       </c>
       <c r="F1946" t="n">
         <v>0.217811702266166</v>
@@ -46332,10 +46332,10 @@
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.745780853466982</v>
+        <v>-3.638967073291039</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.047439166215789</v>
+        <v>1.090164678286167</v>
       </c>
       <c r="F1947" t="n">
         <v>0.1734222329367384</v>
@@ -46355,10 +46355,10 @@
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.633109635230732</v>
+        <v>-3.526295855054789</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.087583362022012</v>
+        <v>1.13030887409239</v>
       </c>
       <c r="F1948" t="n">
         <v>0.2860934511729886</v>
@@ -46378,10 +46378,10 @@
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.52073263404806</v>
+        <v>-3.413918853872116</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.138025458325749</v>
+        <v>1.180750970396126</v>
       </c>
       <c r="F1949" t="n">
         <v>0.2860934511729886</v>
@@ -46401,10 +46401,10 @@
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.548513031949413</v>
+        <v>-3.441699251773469</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.138410500933746</v>
+        <v>1.181136013004124</v>
       </c>
       <c r="F1950" t="n">
         <v>0.2583130532716355</v>
@@ -46424,10 +46424,10 @@
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.631514312974692</v>
+        <v>-3.524700532798748</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9435657085242881</v>
+        <v>0.9862912205946655</v>
       </c>
       <c r="F1951" t="n">
         <v>0.2397421687444617</v>
@@ -46447,10 +46447,10 @@
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.740128391418023</v>
+        <v>-3.63331461124208</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.020269737866161</v>
+        <v>1.062995249936539</v>
       </c>
       <c r="F1952" t="n">
         <v>0.2397421687444617</v>
@@ -46470,10 +46470,10 @@
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.70471935316988</v>
+        <v>-3.597905572993937</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.048946379267742</v>
+        <v>1.091671891338119</v>
       </c>
       <c r="F1953" t="n">
         <v>0.2397421687444617</v>
@@ -46493,10 +46493,10 @@
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.666335690611729</v>
+        <v>-3.559521910435786</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.061719285633371</v>
+        <v>1.104444797703748</v>
       </c>
       <c r="F1954" t="n">
         <v>0.2781258313026129</v>
@@ -46516,10 +46516,10 @@
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.489219360576563</v>
+        <v>-3.382405580400619</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.129294846492739</v>
+        <v>1.172020358563117</v>
       </c>
       <c r="F1955" t="n">
         <v>0.2781258313026129</v>
@@ -46539,10 +46539,10 @@
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.534311605410108</v>
+        <v>-3.427497825234165</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.111941340321234</v>
+        <v>1.154666852391611</v>
       </c>
       <c r="F1956" t="n">
         <v>0.2162297881332231</v>
@@ -46562,10 +46562,10 @@
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.354936184171341</v>
+        <v>-3.248122403995398</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.177478484123156</v>
+        <v>1.220203996193533</v>
       </c>
       <c r="F1957" t="n">
         <v>0.3730065463039418</v>
@@ -46585,10 +46585,10 @@
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.399950397691947</v>
+        <v>-3.293136617516004</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.140280254046503</v>
+        <v>1.18300576611688</v>
       </c>
       <c r="F1958" t="n">
         <v>0.3426576509893372</v>
@@ -46608,10 +46608,10 @@
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.666954907964382</v>
+        <v>-3.560141127788439</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.039170012276474</v>
+        <v>1.081895524346852</v>
       </c>
       <c r="F1959" t="n">
         <v>0.1482946129463886</v>
@@ -46631,10 +46631,10 @@
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.768152689401555</v>
+        <v>-3.661338909225612</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9978948215981069</v>
+        <v>1.040620333668484</v>
       </c>
       <c r="F1960" t="n">
         <v>0.07988579940106943</v>
@@ -46654,10 +46654,10 @@
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.761641722787243</v>
+        <v>-3.654827942611299</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9980991697981487</v>
+        <v>1.040824681868526</v>
       </c>
       <c r="F1961" t="n">
         <v>0.07988579940106943</v>
@@ -46677,10 +46677,10 @@
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.742603595079945</v>
+        <v>-3.635789814904002</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.002239140089312</v>
+        <v>1.04496465215969</v>
       </c>
       <c r="F1962" t="n">
         <v>0.02170218806987489</v>
@@ -46700,10 +46700,10 @@
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.773730226230563</v>
+        <v>-3.66691644605462</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.167370356567746</v>
+        <v>1.210095868638123</v>
       </c>
       <c r="F1963" t="n">
         <v>0.02170218806987489</v>
@@ -46723,10 +46723,10 @@
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.787596987564481</v>
+        <v>-3.680783207388537</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.162656981020312</v>
+        <v>1.20538249309069</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.01615572866394804</v>
@@ -46746,10 +46746,10 @@
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.742792816024551</v>
+        <v>-3.635979035848607</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.18658718003321</v>
+        <v>1.229312692103588</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.01615572866394804</v>
@@ -46769,10 +46769,10 @@
         <v>2.582010952033977</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.595049845789549</v>
+        <v>-3.488236065613605</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.143634589404411</v>
+        <v>1.186360101474788</v>
       </c>
       <c r="F1966" t="n">
         <v>0.1516516285709351</v>
@@ -46792,10 +46792,10 @@
         <v>2.584804573565458</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.697064528320769</v>
+        <v>-3.590250748144826</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.105622337923403</v>
+        <v>1.14834784999378</v>
       </c>
       <c r="F1967" t="n">
         <v>0.1516516285709351</v>
@@ -46815,10 +46815,10 @@
         <v>2.585466921957117</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.690911822267985</v>
+        <v>-3.584098042092042</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.108745768736175</v>
+        <v>1.151471280806553</v>
       </c>
       <c r="F1968" t="n">
         <v>0.1578043346237194</v>
@@ -46838,10 +46838,10 @@
         <v>2.584547398697227</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.707721120418487</v>
+        <v>-3.600907340242543</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.101102526216085</v>
+        <v>1.143828038286462</v>
       </c>
       <c r="F1969" t="n">
         <v>0.1409950364732178</v>
@@ -46861,10 +46861,10 @@
         <v>2.650882952494048</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.645423121642365</v>
+        <v>-3.538609341466421</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.192357279523355</v>
+        <v>1.235082791593732</v>
       </c>
       <c r="F1970" t="n">
         <v>0.1409950364732178</v>
@@ -46884,10 +46884,10 @@
         <v>2.453174954208175</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.443632923977207</v>
+        <v>-3.336819143801264</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.075365360303545</v>
+        <v>1.118090872373922</v>
       </c>
       <c r="F1971" t="n">
         <v>0.3390132286423722</v>
@@ -46907,10 +46907,10 @@
         <v>2.52346518653035</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.37025482688847</v>
+        <v>-3.263441046712527</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.175006831461215</v>
+        <v>1.217732343531592</v>
       </c>
       <c r="F1972" t="n">
         <v>0.4123913257311087</v>
@@ -46930,10 +46930,10 @@
         <v>2.538092922646394</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.467995371513445</v>
+        <v>-3.361181591337501</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.150538349727269</v>
+        <v>1.193263861797646</v>
       </c>
       <c r="F1973" t="n">
         <v>0.3965020475981285</v>
@@ -46953,10 +46953,10 @@
         <v>2.536628903471065</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.644333131636374</v>
+        <v>-3.537519351460431</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.078539226502769</v>
+        <v>1.121264738573146</v>
       </c>
       <c r="F1974" t="n">
         <v>0.2201642874751991</v>
@@ -46976,10 +46976,10 @@
         <v>2.535120521510994</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.567911085204447</v>
+        <v>-3.461097305028504</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.107599663115468</v>
+        <v>1.150325175185845</v>
       </c>
       <c r="F1975" t="n">
         <v>0.2201642874751991</v>
@@ -46999,10 +46999,10 @@
         <v>2.53498338894643</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.523537953565878</v>
+        <v>-3.416724173389935</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.125211783206332</v>
+        <v>1.167937295276709</v>
       </c>
       <c r="F1976" t="n">
         <v>0.2645374191137677</v>
@@ -47022,10 +47022,10 @@
         <v>2.529377183085021</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.400703732678711</v>
+        <v>-3.293889952502768</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.168739265699789</v>
+        <v>1.211464777770166</v>
       </c>
       <c r="F1977" t="n">
         <v>0.2645374191137677</v>
@@ -47045,10 +47045,10 @@
         <v>2.535758940112825</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.353048002117656</v>
+        <v>-3.246234221941712</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.194183314952016</v>
+        <v>1.236908827022393</v>
       </c>
       <c r="F1978" t="n">
         <v>0.3121931496748234</v>
@@ -47068,10 +47068,10 @@
         <v>2.54065131348755</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.252529843618901</v>
+        <v>-3.145716063442958</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.239282951726242</v>
+        <v>1.28200846379662</v>
       </c>
       <c r="F1979" t="n">
         <v>0.4127113081735779</v>
@@ -47091,10 +47091,10 @@
         <v>2.527405985963422</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.31319643402129</v>
+        <v>-3.206382653845347</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.201770988041159</v>
+        <v>1.244496500111536</v>
       </c>
       <c r="F1980" t="n">
         <v>0.3310129914550443</v>
@@ -47114,10 +47114,10 @@
         <v>2.531503688574051</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.268358032412892</v>
+        <v>-3.161544252236949</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.223804051295147</v>
+        <v>1.266529563365524</v>
       </c>
       <c r="F1981" t="n">
         <v>0.3355564243999137</v>
@@ -47137,10 +47137,10 @@
         <v>2.535664628205129</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.369116668169891</v>
+        <v>-3.262302887993947</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.187661536623426</v>
+        <v>1.230387048693803</v>
       </c>
       <c r="F1982" t="n">
         <v>0.2467308556729083</v>
@@ -47160,10 +47160,10 @@
         <v>2.541544230732966</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.32491383108399</v>
+        <v>-3.218100050908047</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.211222273985623</v>
+        <v>1.253947786056</v>
       </c>
       <c r="F1983" t="n">
         <v>0.2909336927588088</v>
@@ -47183,10 +47183,10 @@
         <v>2.539954231202214</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.361892858747433</v>
+        <v>-3.25507907857149</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.194840663389493</v>
+        <v>1.23756617545987</v>
       </c>
       <c r="F1984" t="n">
         <v>0.3279075945501393</v>
@@ -47206,10 +47206,10 @@
         <v>2.591201996385253</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.203601441208161</v>
+        <v>-3.096787661032218</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.309404995588242</v>
+        <v>1.352130507658619</v>
       </c>
       <c r="F1985" t="n">
         <v>0.3279075945501393</v>
@@ -47229,10 +47229,10 @@
         <v>2.589642700979506</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.995959437573685</v>
+        <v>-2.889145657397742</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.390902501636285</v>
+        <v>1.433628013706663</v>
       </c>
       <c r="F1986" t="n">
         <v>0.5355495981846154</v>
@@ -47252,10 +47252,10 @@
         <v>2.584590929217776</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.944927344851157</v>
+        <v>-2.838113564675214</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.406263566963567</v>
+        <v>1.448989079033944</v>
       </c>
       <c r="F1987" t="n">
         <v>0.5865816909071434</v>
@@ -47275,10 +47275,10 @@
         <v>2.601778333310481</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.879703163723951</v>
+        <v>-2.772889383548008</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.449540643507154</v>
+        <v>1.492266155577531</v>
       </c>
       <c r="F1988" t="n">
         <v>0.651805872034349</v>
@@ -47298,10 +47298,10 @@
         <v>2.597739305609762</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.842276143652817</v>
+        <v>-2.735462363476874</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.460472423834888</v>
+        <v>1.503197935905265</v>
       </c>
       <c r="F1989" t="n">
         <v>0.6570574100635307</v>
@@ -47321,10 +47321,10 @@
         <v>2.598996097941002</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.862387799687526</v>
+        <v>-2.755574019511582</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.453684553752245</v>
+        <v>1.496410065822622</v>
       </c>
       <c r="F1990" t="n">
         <v>0.6680847550609499</v>
@@ -47344,10 +47344,10 @@
         <v>2.759553868962213</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.808642985260321</v>
+        <v>-2.701829205084378</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.635740250544337</v>
+        <v>1.678465762614715</v>
       </c>
       <c r="F1991" t="n">
         <v>0.6781480645014119</v>
@@ -47367,10 +47367,10 @@
         <v>2.87966677818003</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.784851416654178</v>
+        <v>-2.678037636478235</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.765369787204611</v>
+        <v>1.808095299274989</v>
       </c>
       <c r="F1992" t="n">
         <v>0.7019396331075541</v>
@@ -47390,10 +47390,10 @@
         <v>2.871374754193889</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.758767332390371</v>
+        <v>-2.651953552214427</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.767511396923994</v>
+        <v>1.810236908994371</v>
       </c>
       <c r="F1993" t="n">
         <v>0.7019396331075541</v>
@@ -47413,10 +47413,10 @@
         <v>2.869567949777668</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.680636151541424</v>
+        <v>-2.57382237136548</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.796957064847352</v>
+        <v>1.839682576917729</v>
       </c>
       <c r="F1994" t="n">
         <v>0.7761164439912387</v>
@@ -47436,10 +47436,10 @@
         <v>2.88712235550446</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.671743690148141</v>
+        <v>-2.564929909972197</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.818068455131456</v>
+        <v>1.860793967201834</v>
       </c>
       <c r="F1995" t="n">
         <v>0.7761164439912387</v>
@@ -47459,10 +47459,10 @@
         <v>2.878977402909044</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.840219807118018</v>
+        <v>-2.733406026942075</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.742533055748089</v>
+        <v>1.785258567818466</v>
       </c>
       <c r="F1996" t="n">
         <v>0.7481686082746579</v>
@@ -47482,10 +47482,10 @@
         <v>2.860247100096906</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.142420278256435</v>
+        <v>-2.035606498080492</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.002922564480584</v>
+        <v>2.045648076550961</v>
       </c>
       <c r="F1997" t="n">
         <v>0.6778205489042473</v>
@@ -47505,10 +47505,10 @@
         <v>2.85091112259381</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.119699174573283</v>
+        <v>-2.012885394397339</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.00267502845075</v>
+        <v>2.045400540521127</v>
       </c>
       <c r="F1998" t="n">
         <v>0.6778205489042473</v>
@@ -47528,10 +47528,10 @@
         <v>3.009817248444979</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.117974131283239</v>
+        <v>-2.011160351107296</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.162271171617936</v>
+        <v>2.204996683688314</v>
       </c>
       <c r="F1999" t="n">
         <v>0.679545592194291</v>
@@ -47551,10 +47551,10 @@
         <v>3.046895070938626</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.272755138061494</v>
+        <v>-2.165941357885551</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.137436591400281</v>
+        <v>2.180162103470658</v>
       </c>
       <c r="F2000" t="n">
         <v>0.6461779181398148</v>
@@ -47574,10 +47574,10 @@
         <v>3.043570426928171</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.221319804676834</v>
+        <v>-2.114506024500891</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.15468608074369</v>
+        <v>2.197411592814067</v>
       </c>
       <c r="F2001" t="n">
         <v>0.6976132515244745</v>
@@ -47597,10 +47597,10 @@
         <v>3.053576580572912</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.194368580350346</v>
+        <v>-2.087554800174403</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.175472724119027</v>
+        <v>2.218198236189404</v>
       </c>
       <c r="F2002" t="n">
         <v>0.7124935975521937</v>
@@ -47620,10 +47620,10 @@
         <v>3.237679712717872</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.330321588406663</v>
+        <v>-2.223507808230719</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.30519465304146</v>
+        <v>2.347920165111837</v>
       </c>
       <c r="F2003" t="n">
         <v>0.7124935975521937</v>
@@ -47643,10 +47643,10 @@
         <v>3.229796407620865</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.352729706211535</v>
+        <v>-2.245915926035591</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.288348100822504</v>
+        <v>2.331073612892882</v>
       </c>
       <c r="F2004" t="n">
         <v>0.7124935975521937</v>
@@ -47666,10 +47666,10 @@
         <v>3.231850407170503</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.500735473690934</v>
+        <v>-2.393921693514991</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.231199793380382</v>
+        <v>2.273925305450759</v>
       </c>
       <c r="F2005" t="n">
         <v>0.6257665886886522</v>
@@ -47689,10 +47689,10 @@
         <v>3.28810412489235</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.510176399579464</v>
+        <v>-2.403362619403521</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.283677140746817</v>
+        <v>2.326402652817194</v>
       </c>
       <c r="F2006" t="n">
         <v>0.7481937062320436</v>
@@ -47712,10 +47712,10 @@
         <v>3.290995219437651</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.508889636039908</v>
+        <v>-2.402075855863965</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.287082940707941</v>
+        <v>2.329808452778318</v>
       </c>
       <c r="F2007" t="n">
         <v>0.7494804697716002</v>
@@ -47735,10 +47735,10 @@
         <v>3.289107032331426</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.510446690029199</v>
+        <v>-2.403632909853256</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.284571932005999</v>
+        <v>2.327297444076376</v>
       </c>
       <c r="F2008" t="n">
         <v>0.7494804697716002</v>
@@ -47758,10 +47758,10 @@
         <v>3.283927261934288</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.517718575552664</v>
+        <v>-2.41090479537672</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.276483407399476</v>
+        <v>2.319208919469853</v>
       </c>
       <c r="F2009" t="n">
         <v>0.7422085842481354</v>
@@ -47781,10 +47781,10 @@
         <v>3.282361272144441</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.515877556494412</v>
+        <v>-2.409063776318469</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.275653825232928</v>
+        <v>2.318379337303305</v>
       </c>
       <c r="F2010" t="n">
         <v>0.7434768109196038</v>
@@ -47804,10 +47804,10 @@
         <v>3.295434679010359</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.522786261994093</v>
+        <v>-2.41597248181815</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.285963749898975</v>
+        <v>2.328689261969352</v>
       </c>
       <c r="F2011" t="n">
         <v>0.7434768109196038</v>
@@ -47827,10 +47827,10 @@
         <v>3.295434679010359</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.524347904808953</v>
+        <v>-2.41753412463301</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.285339092773031</v>
+        <v>2.328064604843408</v>
       </c>
       <c r="F2012" t="n">
         <v>0.7434768109196038</v>
@@ -47850,10 +47850,10 @@
         <v>3.293958720137361</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.552248691918426</v>
+        <v>-2.445434911742483</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.272702819056244</v>
+        <v>2.315428331126621</v>
       </c>
       <c r="F2013" t="n">
         <v>0.708879886776669</v>
@@ -47873,10 +47873,10 @@
         <v>3.29072316411456</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.5552816894311</v>
+        <v>-2.448467909255156</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.268254064028373</v>
+        <v>2.31097957609875</v>
       </c>
       <c r="F2014" t="n">
         <v>0.7058468892639951</v>
@@ -47896,10 +47896,10 @@
         <v>3.357429123705064</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.575343010707607</v>
+        <v>-2.468529230531663</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.326935495108274</v>
+        <v>2.369661007178651</v>
       </c>
       <c r="F2015" t="n">
         <v>0.685785567987488</v>
@@ -47919,10 +47919,10 @@
         <v>3.497740842706911</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.83206382870243</v>
+        <v>-2.725250048526487</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.364558886912191</v>
+        <v>2.407284398982569</v>
       </c>
       <c r="F2016" t="n">
         <v>0.5773709938436732</v>
@@ -47942,10 +47942,10 @@
         <v>3.566721111852551</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.986050246478571</v>
+        <v>-2.879236466302628</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.371944588947375</v>
+        <v>2.414670101017752</v>
       </c>
       <c r="F2017" t="n">
         <v>0.5773709938436732</v>
@@ -47965,10 +47965,10 @@
         <v>3.552772313972671</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.935528342650905</v>
+        <v>-2.828714562474962</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.378204552598562</v>
+        <v>2.42093006466894</v>
       </c>
       <c r="F2018" t="n">
         <v>0.5773709938436732</v>
@@ -47988,10 +47988,10 @@
         <v>3.564642803028085</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.18800349665863</v>
+        <v>-3.081189716482687</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.289084980050886</v>
+        <v>2.331810492121264</v>
       </c>
       <c r="F2019" t="n">
         <v>0.5773709938436732</v>
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.771019590570408</v>
+        <v>3.819092335704252</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.773602792038293</v>
+        <v>3.773602792038294</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.18800349665863</v>
+        <v>-3.214066422229257</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.289084980050886</v>
+        <v>2.487619798832843</v>
       </c>
       <c r="F2020" t="n">
         <v>0.5773709938436732</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.766666589024661</v>
+        <v>4.120025388344498</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240709.xlsx
+++ b/tame_output/ON/bt/strategyON_20240709.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>83.7%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,37 +844,37 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>68.3%</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>30.7%</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>66.4%</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>31.0%</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>56.1%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.6%</t>
+          <t>-70.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.2%</t>
+          <t>124.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.5%</t>
+          <t>-49.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.4%</t>
+          <t>-66.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.4%</t>
+          <t>454.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-483.0%</t>
+          <t>-464.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-127.5%</t>
+          <t>-129.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.6%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-73.4%</t>
+          <t>-70.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-166.3%</t>
+          <t>-153.4%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>74.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-18.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-34.0%</t>
+          <t>-35.9%</t>
         </is>
       </c>
     </row>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311945</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409724</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017768</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785785</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390426</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471879410595</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960984</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607642</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279183</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.122940342039185</v>
+        <v>-5.111076555910989</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9091070439875559</v>
+        <v>0.9138525584388342</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.5166151562034768</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.882509845234325</v>
+        <v>-4.870646059106129</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.007022319334377</v>
+        <v>1.011767833785656</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.2761846593986165</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.81026727706313</v>
+        <v>-4.798403490934934</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.039848660437675</v>
+        <v>1.044594174888954</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.2761846593986165</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.757268954781742</v>
+        <v>-4.745405168653546</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.06172657326757</v>
+        <v>1.066472087718849</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.2208484003966776</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.648464069302015</v>
+        <v>-4.636600283173819</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.102246598679455</v>
+        <v>1.106992113130733</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.2208484003966776</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.428443271265005</v>
+        <v>-4.416579485136809</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.191833954904873</v>
+        <v>1.196579469356152</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.07962855532869739</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.295575582201727</v>
+        <v>-4.283711796073531</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.260875213332008</v>
+        <v>1.265620727783286</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.07962855532869739</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.175402498837228</v>
+        <v>-4.163538712709032</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.310090291118109</v>
+        <v>1.314835805569387</v>
       </c>
       <c r="F1931" t="n">
         <v>0.04054452803580155</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.030730353737491</v>
+        <v>-4.018866567609295</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.378047251719444</v>
+        <v>1.382792766170722</v>
       </c>
       <c r="F1932" t="n">
         <v>0.185216673135539</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.7358392229421</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.090605181095183</v>
+        <v>-4.078741394966987</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.340134812177793</v>
+        <v>1.344880326629071</v>
       </c>
       <c r="F1933" t="n">
         <v>0.1253418457778468</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.970784950184346</v>
+        <v>-3.95892116405615</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.403352073776336</v>
+        <v>1.408097588227615</v>
       </c>
       <c r="F1934" t="n">
         <v>0.1253418457778468</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914639843069</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.973254656646152</v>
+        <v>-3.961390870517956</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.310008390514055</v>
+        <v>1.314753904965334</v>
       </c>
       <c r="F1935" t="n">
         <v>0.1228721393160407</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.041624842970162</v>
+        <v>-4.029761056841966</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.201922177469753</v>
+        <v>1.206667691921031</v>
       </c>
       <c r="F1936" t="n">
         <v>0.1321478383522556</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.055412895817208</v>
+        <v>-4.043549109689012</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.186843664962825</v>
+        <v>1.191589179414104</v>
       </c>
       <c r="F1937" t="n">
         <v>0.1321478383522556</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.857345796164792</v>
+        <v>-4.074542269017718</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.090780069864179</v>
+        <v>1.003901480723009</v>
       </c>
       <c r="F1938" t="n">
         <v>0.1321478383522556</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.681871536372323</v>
+        <v>-3.899068009225248</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.165537005772954</v>
+        <v>1.078658416631784</v>
       </c>
       <c r="F1939" t="n">
         <v>0.1321478383522556</v>
@@ -46171,10 +46171,10 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.792807789013572</v>
+        <v>-4.010004261866497</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.096904533477662</v>
+        <v>1.010025944336492</v>
       </c>
       <c r="F1940" t="n">
         <v>0.1321478383522556</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.75914424354129</v>
+        <v>-3.976340716394215</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.11350133688648</v>
+        <v>1.02662274774531</v>
       </c>
       <c r="F1941" t="n">
         <v>0.1658113838245375</v>
@@ -46217,10 +46217,10 @@
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.699291624337567</v>
+        <v>-3.916488097190492</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.147614771000102</v>
+        <v>1.060736181858932</v>
       </c>
       <c r="F1942" t="n">
         <v>0.1658113838245375</v>
@@ -46240,10 +46240,10 @@
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.613048161311189</v>
+        <v>-3.830244634164115</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.177058426784513</v>
+        <v>1.090179837643343</v>
       </c>
       <c r="F1943" t="n">
         <v>0.1658113838245375</v>
@@ -46263,10 +46263,10 @@
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.658354980710169</v>
+        <v>-3.875551453563094</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.150711474469447</v>
+        <v>1.063832885328277</v>
       </c>
       <c r="F1944" t="n">
         <v>0.1250012208153067</v>
@@ -46286,10 +46286,10 @@
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.687388085412471</v>
+        <v>-3.904584558265396</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.139650105621627</v>
+        <v>1.052771516480457</v>
       </c>
       <c r="F1945" t="n">
         <v>0.1250012208153067</v>
@@ -46309,10 +46309,10 @@
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.594577603961612</v>
+        <v>-3.811774076814537</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.106046990093337</v>
+        <v>1.019168400952167</v>
       </c>
       <c r="F1946" t="n">
         <v>0.217811702266166</v>
@@ -46332,10 +46332,10 @@
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.638967073291039</v>
+        <v>-3.856163546143964</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.090164678286167</v>
+        <v>1.003286089144997</v>
       </c>
       <c r="F1947" t="n">
         <v>0.1734222329367384</v>
@@ -46355,10 +46355,10 @@
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.526295855054789</v>
+        <v>-3.743492327907714</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.13030887409239</v>
+        <v>1.04343028495122</v>
       </c>
       <c r="F1948" t="n">
         <v>0.2860934511729886</v>
@@ -46378,10 +46378,10 @@
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.413918853872116</v>
+        <v>-3.631115326725042</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.180750970396126</v>
+        <v>1.093872381254956</v>
       </c>
       <c r="F1949" t="n">
         <v>0.2860934511729886</v>
@@ -46401,10 +46401,10 @@
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.441699251773469</v>
+        <v>-3.658895724626395</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.181136013004124</v>
+        <v>1.094257423862954</v>
       </c>
       <c r="F1950" t="n">
         <v>0.2583130532716355</v>
@@ -46424,10 +46424,10 @@
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.524700532798748</v>
+        <v>-3.741897005651674</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9862912205946655</v>
+        <v>0.8994126314534954</v>
       </c>
       <c r="F1951" t="n">
         <v>0.2397421687444617</v>
@@ -46447,10 +46447,10 @@
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.63331461124208</v>
+        <v>-3.850511084095005</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.062995249936539</v>
+        <v>0.9761166607953686</v>
       </c>
       <c r="F1952" t="n">
         <v>0.2397421687444617</v>
@@ -46470,10 +46470,10 @@
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.597905572993937</v>
+        <v>-3.815102045846862</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.091671891338119</v>
+        <v>1.004793302196949</v>
       </c>
       <c r="F1953" t="n">
         <v>0.2397421687444617</v>
@@ -46493,10 +46493,10 @@
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.559521910435786</v>
+        <v>-3.776718383288711</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.104444797703748</v>
+        <v>1.017566208562578</v>
       </c>
       <c r="F1954" t="n">
         <v>0.2781258313026129</v>
@@ -46516,10 +46516,10 @@
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.382405580400619</v>
+        <v>-3.649761731360096</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.172020358563117</v>
+        <v>1.065077898179326</v>
       </c>
       <c r="F1955" t="n">
         <v>0.2781258313026129</v>
@@ -46539,10 +46539,10 @@
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.427497825234165</v>
+        <v>-3.694853976193642</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.154666852391611</v>
+        <v>1.047724392007821</v>
       </c>
       <c r="F1956" t="n">
         <v>0.2162297881332231</v>
@@ -46562,10 +46562,10 @@
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.248122403995398</v>
+        <v>-3.515478554954874</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.220203996193533</v>
+        <v>1.113261535809742</v>
       </c>
       <c r="F1957" t="n">
         <v>0.3730065463039418</v>
@@ -46585,10 +46585,10 @@
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.293136617516004</v>
+        <v>-3.56049276847548</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.18300576611688</v>
+        <v>1.07606330573309</v>
       </c>
       <c r="F1958" t="n">
         <v>0.3426576509893372</v>
@@ -46608,10 +46608,10 @@
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.560141127788439</v>
+        <v>-3.827497278747916</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.081895524346852</v>
+        <v>0.9749530639630613</v>
       </c>
       <c r="F1959" t="n">
         <v>0.1482946129463886</v>
@@ -46631,10 +46631,10 @@
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.661338909225612</v>
+        <v>-3.928695060185088</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.040620333668484</v>
+        <v>0.9336778732846935</v>
       </c>
       <c r="F1960" t="n">
         <v>0.07988579940106943</v>
@@ -46654,10 +46654,10 @@
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.654827942611299</v>
+        <v>-3.922184093570776</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.040824681868526</v>
+        <v>0.9338822214847353</v>
       </c>
       <c r="F1961" t="n">
         <v>0.07988579940106943</v>
@@ -46677,10 +46677,10 @@
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.635789814904002</v>
+        <v>-3.903145965863478</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.04496465215969</v>
+        <v>0.9380221917758993</v>
       </c>
       <c r="F1962" t="n">
         <v>0.02170218806987489</v>
@@ -46700,10 +46700,10 @@
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.66691644605462</v>
+        <v>-3.934272597014096</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.210095868638123</v>
+        <v>1.103153408254333</v>
       </c>
       <c r="F1963" t="n">
         <v>0.02170218806987489</v>
@@ -46723,10 +46723,10 @@
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.680783207388537</v>
+        <v>-3.948139358348014</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.20538249309069</v>
+        <v>1.098440032706899</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.01615572866394804</v>
@@ -46746,10 +46746,10 @@
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.635979035848607</v>
+        <v>-3.903335186808084</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.229312692103588</v>
+        <v>1.122370231719797</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.01615572866394804</v>
@@ -46769,10 +46769,10 @@
         <v>2.582010952033977</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.488236065613605</v>
+        <v>-3.755592216573082</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.186360101474788</v>
+        <v>1.079417641090997</v>
       </c>
       <c r="F1966" t="n">
         <v>0.1516516285709351</v>
@@ -46792,10 +46792,10 @@
         <v>2.584804573565458</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.590250748144826</v>
+        <v>-3.857606899104303</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.14834784999378</v>
+        <v>1.04140538960999</v>
       </c>
       <c r="F1967" t="n">
         <v>0.1516516285709351</v>
@@ -46815,10 +46815,10 @@
         <v>2.585466921957117</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.584098042092042</v>
+        <v>-3.851454193051518</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.151471280806553</v>
+        <v>1.044528820422762</v>
       </c>
       <c r="F1968" t="n">
         <v>0.1578043346237194</v>
@@ -46838,10 +46838,10 @@
         <v>2.584547398697227</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.600907340242543</v>
+        <v>-3.86826349120202</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.143828038286462</v>
+        <v>1.036885577902672</v>
       </c>
       <c r="F1969" t="n">
         <v>0.1409950364732178</v>
@@ -46861,10 +46861,10 @@
         <v>2.650882952494048</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.538609341466421</v>
+        <v>-3.805965492425898</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.235082791593732</v>
+        <v>1.128140331209941</v>
       </c>
       <c r="F1970" t="n">
         <v>0.1409950364732178</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.453174954208175</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.336819143801264</v>
+        <v>-3.60417529476074</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.118090872373922</v>
+        <v>1.011148411990132</v>
       </c>
       <c r="F1971" t="n">
         <v>0.3390132286423722</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.52346518653035</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.263441046712527</v>
+        <v>-3.530797197672003</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.217732343531592</v>
+        <v>1.110789883147802</v>
       </c>
       <c r="F1972" t="n">
         <v>0.4123913257311087</v>
@@ -46930,10 +46930,10 @@
         <v>2.538092922646394</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.361181591337501</v>
+        <v>-3.628537742296978</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.193263861797646</v>
+        <v>1.086321401413855</v>
       </c>
       <c r="F1973" t="n">
         <v>0.3965020475981285</v>
@@ -46953,10 +46953,10 @@
         <v>2.536628903471065</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.537519351460431</v>
+        <v>-3.804875502419907</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.121264738573146</v>
+        <v>1.014322278189355</v>
       </c>
       <c r="F1974" t="n">
         <v>0.2201642874751991</v>
@@ -46976,10 +46976,10 @@
         <v>2.535120521510994</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.461097305028504</v>
+        <v>-3.72845345598798</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.150325175185845</v>
+        <v>1.043382714802055</v>
       </c>
       <c r="F1975" t="n">
         <v>0.2201642874751991</v>
@@ -46999,10 +46999,10 @@
         <v>2.53498338894643</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.416724173389935</v>
+        <v>-3.684080324349412</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.167937295276709</v>
+        <v>1.060994834892918</v>
       </c>
       <c r="F1976" t="n">
         <v>0.2645374191137677</v>
@@ -47022,10 +47022,10 @@
         <v>2.529377183085021</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.293889952502768</v>
+        <v>-3.561246103462244</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.211464777770166</v>
+        <v>1.104522317386376</v>
       </c>
       <c r="F1977" t="n">
         <v>0.2645374191137677</v>
@@ -47045,10 +47045,10 @@
         <v>2.535758940112825</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.246234221941712</v>
+        <v>-3.513590372901189</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.236908827022393</v>
+        <v>1.129966366638603</v>
       </c>
       <c r="F1978" t="n">
         <v>0.3121931496748234</v>
@@ -47068,10 +47068,10 @@
         <v>2.54065131348755</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.145716063442958</v>
+        <v>-3.413072214402434</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.28200846379662</v>
+        <v>1.175066003412829</v>
       </c>
       <c r="F1979" t="n">
         <v>0.4127113081735779</v>
@@ -47091,10 +47091,10 @@
         <v>2.527405985963422</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.206382653845347</v>
+        <v>-3.473738804804823</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.244496500111536</v>
+        <v>1.137554039727746</v>
       </c>
       <c r="F1980" t="n">
         <v>0.3310129914550443</v>
@@ -47114,10 +47114,10 @@
         <v>2.531503688574051</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.161544252236949</v>
+        <v>-3.428900403196425</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.266529563365524</v>
+        <v>1.159587102981734</v>
       </c>
       <c r="F1981" t="n">
         <v>0.3355564243999137</v>
@@ -47137,10 +47137,10 @@
         <v>2.535664628205129</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.262302887993947</v>
+        <v>-3.529659038953424</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.230387048693803</v>
+        <v>1.123444588310012</v>
       </c>
       <c r="F1982" t="n">
         <v>0.2467308556729083</v>
@@ -47160,10 +47160,10 @@
         <v>2.541544230732966</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.218100050908047</v>
+        <v>-3.485456201867523</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.253947786056</v>
+        <v>1.147005325672209</v>
       </c>
       <c r="F1983" t="n">
         <v>0.2909336927588088</v>
@@ -47183,10 +47183,10 @@
         <v>2.539954231202214</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.25507907857149</v>
+        <v>-3.522435229530966</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.23756617545987</v>
+        <v>1.13062371507608</v>
       </c>
       <c r="F1984" t="n">
         <v>0.3279075945501393</v>
@@ -47206,10 +47206,10 @@
         <v>2.591201996385253</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.096787661032218</v>
+        <v>-3.364143811991694</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.352130507658619</v>
+        <v>1.245188047274828</v>
       </c>
       <c r="F1985" t="n">
         <v>0.3279075945501393</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321018</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
         <v>2.589642700979506</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.889145657397742</v>
+        <v>-3.156501808357218</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.433628013706663</v>
+        <v>1.326685553322872</v>
       </c>
       <c r="F1986" t="n">
         <v>0.5355495981846154</v>
@@ -47252,16 +47252,16 @@
         <v>2.584590929217776</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.838113564675214</v>
+        <v>-2.976555208419178</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.448989079033944</v>
+        <v>1.393612421536358</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.5865816909071434</v>
+        <v>0.7154961981226559</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.936539943762063</v>
+        <v>3.01388864809137</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404849</v>
+        <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
         <v>2.601778333310481</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.772889383548008</v>
+        <v>-2.911331027291972</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.492266155577531</v>
+        <v>1.436889498079945</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.651805872034349</v>
+        <v>0.7807203792498615</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.992861856531091</v>
+        <v>3.070210560860398</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882553</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.597739305609762</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.735462363476874</v>
+        <v>-2.873904007220838</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.503197935905265</v>
+        <v>1.447821278407679</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.6570574100635307</v>
+        <v>0.7859719172790431</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.991973751647881</v>
+        <v>3.069322455977188</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992656</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.598996097941002</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.755574019511582</v>
+        <v>-2.894015663255546</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.496410065822622</v>
+        <v>1.441033408325036</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.6680847550609499</v>
+        <v>0.7969992622764623</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.999846950977572</v>
+        <v>3.07719565530688</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
         <v>2.759553868962213</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.701829205084378</v>
+        <v>-2.840270848828342</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.678465762614715</v>
+        <v>1.623089105117129</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.6781480645014119</v>
+        <v>0.8070625717169243</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.16644270766306</v>
+        <v>3.243791411992368</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957621</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.87966677818003</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.678037636478235</v>
+        <v>-2.816479280222199</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.808095299274989</v>
+        <v>1.752718641777403</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.7019396331075541</v>
+        <v>0.8308541403230666</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.300830558044563</v>
+        <v>3.37817926237387</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
         <v>2.871374754193889</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.651953552214427</v>
+        <v>-2.790395195958391</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.810236908994371</v>
+        <v>1.754860251496785</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.7019396331075541</v>
+        <v>0.8308541403230666</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.292538534058422</v>
+        <v>3.369887238387729</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896924</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>2.869567949777668</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.57382237136548</v>
+        <v>-2.712264015109445</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.839682576917729</v>
+        <v>1.784305919420143</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.7761164439912387</v>
+        <v>0.9050309512067511</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.335237816172412</v>
+        <v>3.412586520501719</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959853</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.88712235550446</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.564929909972197</v>
+        <v>-2.703371553716162</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.860793967201834</v>
+        <v>1.805417309704248</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.7761164439912387</v>
+        <v>0.9050309512067511</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.352792221899203</v>
+        <v>3.430140926228511</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.878977402909044</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.733406026942075</v>
+        <v>-2.871847670686039</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.785258567818466</v>
+        <v>1.729881910320881</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.7481686082746579</v>
+        <v>0.8770831154901704</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.327878567873839</v>
+        <v>3.405227272203146</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782703</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.860247100096906</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.035606498080492</v>
+        <v>-2.174048141824456</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.045648076550961</v>
+        <v>1.990271419053376</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.6778205489042473</v>
+        <v>0.8067350561197597</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.266939429439454</v>
+        <v>3.344288133768762</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632631</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.85091112259381</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.012885394397339</v>
+        <v>-2.00602947363767</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.045400540521127</v>
+        <v>2.048142908824995</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.6778205489042473</v>
+        <v>0.8067350561197597</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.257603451936359</v>
+        <v>3.334952156265666</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777669</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>3.009817248444979</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.011160351107296</v>
+        <v>-2.004304430347626</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.204996683688314</v>
+        <v>2.207739051992181</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.679545592194291</v>
+        <v>0.8084600994098035</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.417544603761554</v>
+        <v>3.494893308090862</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>3.046895070938626</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.165941357885551</v>
+        <v>-2.159085437125881</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.180162103470658</v>
+        <v>2.182904471774526</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.6461779181398148</v>
+        <v>0.7750924253553273</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.434601821822515</v>
+        <v>3.511950526151822</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.043570426928171</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.114506024500891</v>
+        <v>-2.107650103741222</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.197411592814067</v>
+        <v>2.200153961117935</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.6976132515244745</v>
+        <v>0.826527758739987</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.462138377842856</v>
+        <v>3.539487082172164</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>3.053576580572912</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.087554800174403</v>
+        <v>-2.080698879414734</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.218198236189404</v>
+        <v>2.220940604493272</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.7124935975521937</v>
+        <v>0.8414081047677061</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.481072739104229</v>
+        <v>3.558421443433536</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784103</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.237679712717872</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.223507808230719</v>
+        <v>-2.21665188747105</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.347920165111837</v>
+        <v>2.350662533415705</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.7124935975521937</v>
+        <v>0.8414081047677061</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.665175871249189</v>
+        <v>3.742524575578496</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.229796407620865</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.245915926035591</v>
+        <v>-2.239060005275922</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.331073612892882</v>
+        <v>2.333815981196749</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.7124935975521937</v>
+        <v>0.8414081047677061</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.657292566152182</v>
+        <v>3.73464127048149</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.231850407170503</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.393921693514991</v>
+        <v>-2.387065772755322</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.273925305450759</v>
+        <v>2.276667673754627</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.6257665886886522</v>
+        <v>0.7546810959041647</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.607310360383694</v>
+        <v>3.684659064713002</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161973</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.28810412489235</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.403362619403521</v>
+        <v>-2.396506698643852</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.326402652817194</v>
+        <v>2.329145021121062</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.7481937062320436</v>
+        <v>0.8771082134475561</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.737020348631576</v>
+        <v>3.814369052960884</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.71494119332163</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
         <v>3.290995219437651</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.402075855863965</v>
+        <v>-2.395219935104295</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.329808452778318</v>
+        <v>2.332550821082186</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7494804697716002</v>
+        <v>0.8783949769871127</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.740683501300611</v>
+        <v>3.818032205629919</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347699</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.289107032331426</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.403632909853256</v>
+        <v>-2.396776989093587</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.327297444076376</v>
+        <v>2.330039812380244</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7494804697716002</v>
+        <v>0.8783949769871127</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.738795314194387</v>
+        <v>3.816144018523694</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887743</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.283927261934288</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.41090479537672</v>
+        <v>-2.404048874617051</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.319208919469853</v>
+        <v>2.321951287773721</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7422085842481354</v>
+        <v>0.8711230914636479</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.72925241248317</v>
+        <v>3.806601116812477</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.282361272144441</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.409063776318469</v>
+        <v>-2.4022078555588</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.318379337303305</v>
+        <v>2.321121705607173</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7434768109196038</v>
+        <v>0.8723913181351163</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.728447358696203</v>
+        <v>3.805796063025511</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647101</v>
+        <v>3.754911907647103</v>
       </c>
       <c r="C2011" t="n">
         <v>3.295434679010359</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.41597248181815</v>
+        <v>-2.409116561058481</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.328689261969352</v>
+        <v>2.33143163027322</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7434768109196038</v>
+        <v>0.8723913181351163</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.741520765562122</v>
+        <v>3.818869469891429</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763528</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
         <v>3.295434679010359</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.41753412463301</v>
+        <v>-2.41067820387334</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.328064604843408</v>
+        <v>2.330806973147276</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7434768109196038</v>
+        <v>0.8723913181351163</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.741520765562122</v>
+        <v>3.818869469891429</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392111</v>
+        <v>3.715834055392113</v>
       </c>
       <c r="C2013" t="n">
         <v>3.293958720137361</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.445434911742483</v>
+        <v>-2.438578990982813</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.315428331126621</v>
+        <v>2.318170699430489</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.708879886776669</v>
+        <v>0.8377943939921815</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.719286652203363</v>
+        <v>3.79663535653267</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172523</v>
+        <v>3.684909939172524</v>
       </c>
       <c r="C2014" t="n">
         <v>3.29072316411456</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.448467909255156</v>
+        <v>-2.441611988495487</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.31097957609875</v>
+        <v>2.313721944402618</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7058468892639951</v>
+        <v>0.8347613964795075</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.714231297672957</v>
+        <v>3.791580002002265</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971075</v>
+        <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
         <v>3.357429123705064</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.468529230531663</v>
+        <v>-2.461673309771994</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.369661007178651</v>
+        <v>2.372403375482519</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.685785567987488</v>
+        <v>0.8147000752030005</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.768900464497557</v>
+        <v>3.846249168826864</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199802</v>
+        <v>3.640764248199804</v>
       </c>
       <c r="C2016" t="n">
         <v>3.497740842706911</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.725250048526487</v>
+        <v>-2.718394127766818</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.407284398982569</v>
+        <v>2.410026767286436</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5773709938436732</v>
+        <v>0.7062855010591856</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.844163439013115</v>
+        <v>3.921512143342422</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622233</v>
+        <v>3.668303164622235</v>
       </c>
       <c r="C2017" t="n">
         <v>3.566721111852551</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.879236466302628</v>
+        <v>-2.872380545542959</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.414670101017752</v>
+        <v>2.41741246932162</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5773709938436732</v>
+        <v>0.7062855010591856</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.913143708158755</v>
+        <v>3.990492412488062</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808525</v>
+        <v>3.619937176808527</v>
       </c>
       <c r="C2018" t="n">
         <v>3.552772313972671</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.828714562474962</v>
+        <v>-2.821858641715293</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.42093006466894</v>
+        <v>2.423672432972807</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5773709938436732</v>
+        <v>0.7062855010591856</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.899194910278875</v>
+        <v>3.976543614608183</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.564642803028085</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.081189716482687</v>
+        <v>-3.074333795723017</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.331810492121264</v>
+        <v>2.334552860425131</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.5773709938436732</v>
+        <v>0.7062855010591856</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.91106539933429</v>
+        <v>3.988414103663597</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.819092335704252</v>
+        <v>3.409962180492527</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.773602792038294</v>
+        <v>3.677124567062215</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.214066422229257</v>
+        <v>-3.027325322774892</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.487619798832843</v>
+        <v>2.465838013638511</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.5773709938436732</v>
+        <v>0.7062855010591856</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.120025388344498</v>
+        <v>4.100895867697727</v>
       </c>
     </row>
   </sheetData>
